--- a/dados/guia-de-swing.xlsx
+++ b/dados/guia-de-swing.xlsx
@@ -10,11 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locais" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horarios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Destaques" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Locais'!$A$1:$Y$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Horarios'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Destaques'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -93,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,6 +125,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -262,47 +267,47 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Itens separados por ponto e vírgula. Ex.: Pista de dança; Bar; Ambientes reservados</t>
+        <t>Logo da casa (ou a imagem que ela escolher para o "perfil"). Aparece na lista e na página da casa. Quadrada, ~300 px, até 200 KB. Ex.: assets/logos/gds-sp-001/logo.png. Sem logo, o site mostra as iniciais do nome.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Formato "Nome: valor", separados por ponto e vírgula. Ex.: Casal: R$ 220; Mulher solteira: R$ 60</t>
+        <t>Itens separados por ponto e vírgula. Ex.: Pista de dança; Bar; Ambientes reservados</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Uma regra por item, separadas por ponto e vírgula. Ex.: Maiores de 18 anos; Documento com foto</t>
+        <t>Formato "Nome: valor", separados por ponto e vírgula. Ex.: Casal: R$ 220; Mulher solteira: R$ 60</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
-        <t>Texto de apresentação (2 a 3 parágrafos). Para pular linha dentro da célula, use Alt+Enter. É o que mais ajuda no Google.</t>
+        <t>Uma regra por item, separadas por ponto e vírgula. Ex.: Maiores de 18 anos; Documento com foto</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>Opcional. Frase de até 155 letras que aparece no Google. Se vazio, o site monta uma sozinho.</t>
+        <t>Texto de apresentação (2 a 3 parágrafos). Para pular linha dentro da célula, use Alt+Enter. É o que mais ajuda no Google.</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>Opcional. Termos que as pessoas buscam, separados por vírgula. Ex.: casa de swing zona sul, swing moema</t>
+        <t>Opcional. Frase de até 155 letras que aparece no Google. Se vazio, o site monta uma sozinho.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>Só números, com 55 e DDD. Ex.: 5511999999999</t>
+        <t>Opcional. Termos que as pessoas buscam, separados por vírgula. Ex.: casa de swing zona sul, swing moema</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>Ex.: (11) 3333-0000</t>
+        <t>Só números, com 55 e DDD. Ex.: 5511999999999</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>Endereço completo, começando com https://</t>
+        <t>Ex.: (11) 3333-0000</t>
       </text>
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
@@ -312,12 +317,12 @@
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
-        <t>Só fachada e ambiente, nunca pessoas. Caminhos separados por ponto e vírgula. Ex.: assets/fotos/gds-sp-001/fachada.jpg</t>
+        <t>Endereço completo, começando com https://</t>
       </text>
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
-        <t>SIM = aparece em "Destaques" no topo da região.</t>
+        <t>Só fachada e ambiente, nunca pessoas. Caminhos separados por ponto e vírgula. Ex.: assets/fotos/gds-sp-001/fachada.jpg</t>
       </text>
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
@@ -368,6 +373,56 @@
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>Opcional. Nome da festa ou observação.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guia de Swing</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>SIM para aparecer no carrossel.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Estado. Ex.: SP</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Etiqueta sobre a imagem. Ex.: Balada, Festa, Evento</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Nome do destaque.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Linha curta. Ex.: Sexta · 23h · Pinheiros</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Imagem horizontal ~800 x 500 px, sem pessoas. Ex.: assets/destaques/festa.jpg</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. id de um lugar da aba Locais (abre a página dele).</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Endereço externo (https://...)</t>
       </text>
     </comment>
   </commentList>
@@ -663,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C51"/>
+  <dimension ref="B1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -752,454 +807,581 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Passo 6</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Quer um lugar, festa ou evento no carrossel "Destaques"? Cadastre na aba Destaques (até 10 por estado).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Aba Horarios</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>id_local</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>O mesmo id do lugar na aba Locais.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>tipo</t>
+          <t>id_local</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>funcionamento = dias em que a casa abre (alimenta o "Funciona hoje" do site). festa = noite temática (escreva o nome da festa em obs). atendimento = reservas e contato.</t>
+          <t>O mesmo id do lugar na aba Locais.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>dias</t>
+          <t>tipo</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>sex-sab   |   dom   |   qua,sex   |   ter-dom   |   todos</t>
+          <t>funcionamento = dias em que a casa abre (alimenta o "Funciona hoje" do site). festa = noite temática (escreva o nome da festa em obs). atendimento = reservas e contato.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>dias</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Abertura e fechamento: 22:00-05:00 (pode virar a madrugada). Só abertura: 22:00. Aceita também 22h-5h.</t>
+          <t>sex-sab   |   dom   |   qua,sex   |   ter-dom   |   todos</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
+          <t>hora</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Abertura e fechamento: 22:00-05:00 (pode virar a madrugada). Só abertura: 22:00. Aceita também 22h-5h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
           <t>obs</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Opcional. Nome da festa, observação, "somente casais"...</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Aba Destaques (carrossel no topo da página do estado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>publicar</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>SIM para aparecer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>uf</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Estado em que o destaque aparece. Ex.: SP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>selo</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Etiqueta sobre a imagem. Ex.: Balada, Festa, Evento, Casa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Nome do destaque. Ex.: Festa Neon</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>legenda</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Linha curta. Ex.: Sexta · 23h · Pinheiros</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>imagem</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Imagem horizontal (~800 x 500 px, até 300 KB), sem pessoas. Ex.: assets/destaques/festa-neon.jpg. Sem imagem, usa a 1ª foto da casa ou um fundo padrão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>id_local</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Opcional. id de um lugar da aba Locais: o destaque abre a página dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Opcional. Endereço externo (https://...) se não houver id_local.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Combinados importantes</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="7" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Só publique casas que autorizaram a divulgação (coluna autorizado = SIM). O site avisa quando faltar.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Logo: use o logo da própria casa, com autorização dela. O logo do Guia de Swing nunca aparece no lugar do logo da casa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Fotos: somente fachada e ambiente vazio. Nunca fotos de pessoas, nem imagens explícitas. Peça autorização à casa e a quem fotografou.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Não registre dados pessoais de frequentadores. Use só informações públicas da casa (WhatsApp e Instagram comerciais).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="7" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Linhas com exemplo = SIM são de teste. Apague essas linhas (ou troque publicar para NÃO) antes de lançar o site.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="7" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Confirme os dados com a casa de tempos em tempos e atualize confirmado_em. O site mostra um selo verde, amarelo ou cinza conforme a data.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="7" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Não mude o nome das abas (Locais, Horarios) nem os títulos da primeira linha, senão o site não encontra os dados.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Colunas da aba Locais</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>publicar  (obrigatória)</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>SIM = aparece no site. NÃO = fica só na planilha (rascunho).</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>id  (obrigatória)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Código único de cada lugar, sem repetir. Ex.: gds-sp-009</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>nome  (obrigatória)</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Nome da casa, balada ou clube.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>tipo  (obrigatória)</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Escolha na lista.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="4" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>uf  (obrigatória)</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Sigla do estado. Ex.: SP</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="4" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>cidade  (obrigatória)</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Ex.: São Paulo</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="4" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>bairro  (obrigatória)</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Ex.: Moema</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="4" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>regiao  (obrigatória)</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Escolha na lista. Precisa ser uma região do estado (ex.: Zona Sul para SP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>endereco</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Rua, número e CEP, se tiver. Usado no mapa e no Waze.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>ambiente</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Itens separados por ponto e vírgula. Ex.: Pista de dança; Bar; Ambientes reservados</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>valores</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Formato "Nome: valor", separados por ponto e vírgula. Ex.: Casal: R$ 220; Mulher solteira: R$ 60</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>regras</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Uma regra por item, separadas por ponto e vírgula. Ex.: Maiores de 18 anos; Documento com foto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>sobre</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Texto de apresentação (2 a 3 parágrafos). Para pular linha dentro da célula, use Alt+Enter. É o que mais ajuda no Google.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>descricao_seo</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Opcional. Frase de até 155 letras que aparece no Google. Se vazio, o site monta uma sozinho.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>palavras_chave</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Opcional. Termos que as pessoas buscam, separados por vírgula. Ex.: casa de swing zona sul, swing moema</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>whatsapp</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Só números, com 55 e DDD. Ex.: 5511999999999</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>telefone</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Ex.: (11) 3333-0000</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Endereço completo, começando com https://</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>instagram</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Endereço completo, começando com https://</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>fotos</t>
+          <t>endereco</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Só fachada e ambiente, nunca pessoas. Caminhos separados por ponto e vírgula. Ex.: assets/fotos/gds-sp-001/fachada.jpg</t>
+          <t>Rua, número e CEP, se tiver. Usado no mapa e no Waze.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>destaque</t>
+          <t>logo</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>SIM = aparece em "Destaques" no topo da região.</t>
+          <t>Logo da casa (ou a imagem que ela escolher para o "perfil"). Aparece na lista e na página da casa. Quadrada, ~300 px, até 200 KB. Ex.: assets/logos/gds-sp-001/logo.png. Sem logo, o site mostra as iniciais do nome.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>confirmado_em</t>
+          <t>ambiente</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Data em que a casa confirmou as informações. Ex.: 20/10/2026</t>
+          <t>Itens separados por ponto e vírgula. Ex.: Pista de dança; Bar; Ambientes reservados</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>autorizado</t>
+          <t>valores</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>SIM = a casa autorizou a divulgação. O site avisa se faltar.</t>
+          <t>Formato "Nome: valor", separados por ponto e vírgula. Ex.: Casal: R$ 220; Mulher solteira: R$ 60</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="8" t="inlineStr">
         <is>
+          <t>regras</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Uma regra por item, separadas por ponto e vírgula. Ex.: Maiores de 18 anos; Documento com foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>sobre</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Texto de apresentação (2 a 3 parágrafos). Para pular linha dentro da célula, use Alt+Enter. É o que mais ajuda no Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>descricao_seo</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Opcional. Frase de até 155 letras que aparece no Google. Se vazio, o site monta uma sozinho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>palavras_chave</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Opcional. Termos que as pessoas buscam, separados por vírgula. Ex.: casa de swing zona sul, swing moema</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Só números, com 55 e DDD. Ex.: 5511999999999</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>telefone</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Ex.: (11) 3333-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Endereço completo, começando com https://</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Endereço completo, começando com https://</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>fotos</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Só fachada e ambiente, nunca pessoas. Caminhos separados por ponto e vírgula. Ex.: assets/fotos/gds-sp-001/fachada.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>confirmado_em</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Data em que a casa confirmou as informações. Ex.: 20/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>autorizado</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>SIM = a casa autorizou a divulgação. O site avisa se faltar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="8" t="inlineStr">
+        <is>
           <t>exemplo</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>SIM = dado de teste (a página mostra aviso e não vai para o Google). Apague ou deixe vazio nos lugares reais.</t>
         </is>
@@ -1228,19 +1410,19 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="30" customWidth="1" min="20" max="20"/>
-    <col width="36" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
@@ -1294,67 +1476,67 @@
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
+          <t>logo</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
           <t>ambiente</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>valores</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>regras</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>sobre</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>descricao_seo</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>palavras_chave</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="T1" s="10" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="U1" s="10" t="inlineStr">
         <is>
           <t>instagram</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="V1" s="10" t="inlineStr">
         <is>
           <t>fotos</t>
-        </is>
-      </c>
-      <c r="V1" s="10" t="inlineStr">
-        <is>
-          <t>destaque</t>
         </is>
       </c>
       <c r="W1" s="10" t="inlineStr">
@@ -1421,50 +1603,50 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
+          <t>assets/logos/exemplo/veludo.svg</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
           <t>Pista de dança; Bar; Ambientes reservados; Fumódromo</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Casal: R$ 220; Mulher solteira: R$ 60; Homem solteiro: consulte a casa</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Somente maiores de 18 anos, com documento com foto; Casais e mulheres solteiras: entrada livre; Homens solteiros: mediante aprovação da casa; Fotos e filmagens proibidas nas áreas internas; Respeito e consentimento sempre</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>A Casa Exemplo Veludo é uma casa de swing em Moema, na Zona Sul de São Paulo. O espaço recebe casais e solteiros em um ambiente reservado, com atendimento discreto e foco no respeito e no consentimento.
 Aqui você confere os dias e horários de funcionamento, valores de entrada, regras da casa e como chegar. Este é um texto de exemplo, escrito apenas para testar o site.</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>casa de swing zona sul, swing moema, casa liberal são paulo</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="Q2" s="11" t="inlineStr">
         <is>
           <t>5511999999999</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr"/>
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr">
         <is>
           <t>https://www.instagram.com/exemplo</t>
         </is>
       </c>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="V2" s="5" t="inlineStr"/>
       <c r="W2" s="12" t="n">
         <v>46315</v>
       </c>
@@ -1527,46 +1709,46 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
+          <t>assets/logos/exemplo/neon.svg</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
           <t>Pista de dança; Bar; Camarotes</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Casal: R$ 180; Mulher: R$ 40; Homem: R$ 120</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Somente maiores de 18 anos, com documento com foto; Traje esporte fino; Reservas de camarote pelo WhatsApp</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>A Balada Exemplo Neon é uma balada liberal em Pinheiros, na Zona Oeste de São Paulo. O espaço recebe casais e solteiros em um ambiente reservado, com atendimento discreto e foco no respeito e no consentimento.
 Aqui você confere os dias e horários de funcionamento, valores de entrada, regras da casa e como chegar. Este é um texto de exemplo, escrito apenas para testar o site.</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>balada liberal pinheiros, balada liberal zona oeste</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="Q3" s="11" t="inlineStr">
         <is>
           <t>5511999999999</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr"/>
       <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr"/>
       <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="V3" s="5" t="inlineStr"/>
       <c r="W3" s="12" t="n">
         <v>46313</v>
       </c>
@@ -1627,35 +1809,35 @@
           <t>Rua Exemplo, 75 - Tatuapé, São Paulo - SP</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Lounge; Bar; Ambientes reservados</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Casal: R$ 200; Mulher solteira: R$ 50</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Somente maiores de 18 anos, com documento com foto; Entrada de solteiros somente em noites específicas</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>A Clube Exemplo Reservado é uma clube liberal em Tatuapé, na Zona Leste de São Paulo. O espaço recebe casais e solteiros em um ambiente reservado, com atendimento discreto e foco no respeito e no consentimento.
 Aqui você confere os dias e horários de funcionamento, valores de entrada, regras da casa e como chegar. Este é um texto de exemplo, escrito apenas para testar o site.</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="11" t="inlineStr">
         <is>
           <t>5511999999999</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
@@ -1721,31 +1903,31 @@
           <t>Av. Exemplo, 500 - Santana, São Paulo - SP</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Sauna; Piscina; Bar</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Entrada: R$ 90</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Somente maiores de 18 anos, com documento com foto; Toalha e chinelo à venda no local</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>A Sauna Exemplo Fênix é uma sauna liberal em Santana, na Zona Norte de São Paulo. O espaço recebe casais e solteiros em um ambiente reservado, com atendimento discreto e foco no respeito e no consentimento.
 Aqui você confere os dias e horários de funcionamento, valores de entrada, regras da casa e como chegar. Este é um texto de exemplo, escrito apenas para testar o site.</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr"/>
       <c r="O5" s="5" t="inlineStr"/>
-      <c r="P5" s="11" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="11" t="inlineStr"/>
       <c r="R5" s="5" t="inlineStr"/>
       <c r="S5" s="5" t="inlineStr"/>
       <c r="T5" s="5" t="inlineStr"/>
@@ -1805,35 +1987,35 @@
           <t>Rua Exemplo, 33 - República, São Paulo - SP</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Ambientes reservados; Bar</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Casal: R$ 160</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Somente maiores de 18 anos, com documento com foto; Reserva antecipada pelo WhatsApp</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>A Privê Exemplo Cetim é uma privê em República, na Centro de São Paulo. O espaço recebe casais e solteiros em um ambiente reservado, com atendimento discreto e foco no respeito e no consentimento.
 Aqui você confere os dias e horários de funcionamento, valores de entrada, regras da casa e como chegar. Este é um texto de exemplo, escrito apenas para testar o site.</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="11" t="inlineStr">
         <is>
           <t>5511999999999</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
@@ -1899,48 +2081,44 @@
           <t>Rua Exemplo, 900 - Santo André - SP</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Pista de dança; Bar; Piscina; Ambientes reservados</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Casal: R$ 190; Mulher solteira: R$ 50; Homem solteiro: consulte a casa</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Somente maiores de 18 anos, com documento com foto; Fotos e filmagens proibidas</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>A Casa Exemplo Mirante é uma casa de swing em Jardim Exemplo, na ABC de São Paulo. O espaço recebe casais e solteiros em um ambiente reservado, com atendimento discreto e foco no respeito e no consentimento.
 Aqui você confere os dias e horários de funcionamento, valores de entrada, regras da casa e como chegar. Este é um texto de exemplo, escrito apenas para testar o site.</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>casa de swing abc, swing santo andré</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="Q7" s="11" t="inlineStr">
         <is>
           <t>5511999999999</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr"/>
       <c r="R7" s="5" t="inlineStr"/>
       <c r="S7" s="5" t="inlineStr"/>
       <c r="T7" s="5" t="inlineStr"/>
       <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="V7" s="5" t="inlineStr"/>
       <c r="W7" s="12" t="n">
         <v>46320</v>
       </c>
@@ -2001,31 +2179,31 @@
           <t>Av. Exemplo, 1500 - Santo Amaro, São Paulo - SP</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Pista de dança; Bar</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Casal: R$ 150; Mulher: R$ 30; Homem: R$ 100</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Somente maiores de 18 anos, com documento com foto</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>A Balada Exemplo Aurora é uma balada liberal em Santo Amaro, na Zona Sul de São Paulo. O espaço recebe casais e solteiros em um ambiente reservado, com atendimento discreto e foco no respeito e no consentimento.
 Aqui você confere os dias e horários de funcionamento, valores de entrada, regras da casa e como chegar. Este é um texto de exemplo, escrito apenas para testar o site.</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr"/>
       <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="11" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="11" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr"/>
       <c r="S8" s="5" t="inlineStr"/>
       <c r="T8" s="5" t="inlineStr"/>
@@ -2091,31 +2269,31 @@
           <t>Av. Exemplo, 2000 - Guarulhos - SP</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Suítes temáticas; Reservas</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Suítes: a partir de R$ 120 (período)</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Somente maiores de 18 anos, com documento com foto</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>A Motel Exemplo Liberal é uma motel com ambiente liberal em Vila Exemplo, na Guarulhos de São Paulo. O espaço recebe casais e solteiros em um ambiente reservado, com atendimento discreto e foco no respeito e no consentimento.
 Aqui você confere os dias e horários de funcionamento, valores de entrada, regras da casa e como chegar. Este é um texto de exemplo, escrito apenas para testar o site.</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr"/>
       <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="11" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="11" t="inlineStr"/>
       <c r="R9" s="5" t="inlineStr"/>
       <c r="S9" s="5" t="inlineStr"/>
       <c r="T9" s="5" t="inlineStr"/>
@@ -2151,8 +2329,8 @@
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="n"/>
       <c r="O10" s="5" t="n"/>
-      <c r="P10" s="11" t="n"/>
-      <c r="Q10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="11" t="n"/>
       <c r="R10" s="5" t="n"/>
       <c r="S10" s="5" t="n"/>
       <c r="T10" s="5" t="n"/>
@@ -2178,8 +2356,8 @@
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="n"/>
-      <c r="P11" s="11" t="n"/>
-      <c r="Q11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="11" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="5" t="n"/>
       <c r="T11" s="5" t="n"/>
@@ -2205,8 +2383,8 @@
       <c r="M12" s="5" t="n"/>
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="5" t="n"/>
-      <c r="P12" s="11" t="n"/>
-      <c r="Q12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="11" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="5" t="n"/>
       <c r="T12" s="5" t="n"/>
@@ -2232,8 +2410,8 @@
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
-      <c r="P13" s="11" t="n"/>
-      <c r="Q13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="11" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
       <c r="T13" s="5" t="n"/>
@@ -2259,8 +2437,8 @@
       <c r="M14" s="5" t="n"/>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
-      <c r="P14" s="11" t="n"/>
-      <c r="Q14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="11" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
       <c r="T14" s="5" t="n"/>
@@ -2286,8 +2464,8 @@
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
-      <c r="P15" s="11" t="n"/>
-      <c r="Q15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="11" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
       <c r="T15" s="5" t="n"/>
@@ -2313,8 +2491,8 @@
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
-      <c r="P16" s="11" t="n"/>
-      <c r="Q16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="11" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
       <c r="T16" s="5" t="n"/>
@@ -2340,8 +2518,8 @@
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
-      <c r="P17" s="11" t="n"/>
-      <c r="Q17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="11" t="n"/>
       <c r="R17" s="5" t="n"/>
       <c r="S17" s="5" t="n"/>
       <c r="T17" s="5" t="n"/>
@@ -2367,8 +2545,8 @@
       <c r="M18" s="5" t="n"/>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
-      <c r="P18" s="11" t="n"/>
-      <c r="Q18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="11" t="n"/>
       <c r="R18" s="5" t="n"/>
       <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
@@ -2394,8 +2572,8 @@
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="11" t="n"/>
       <c r="R19" s="5" t="n"/>
       <c r="S19" s="5" t="n"/>
       <c r="T19" s="5" t="n"/>
@@ -2421,8 +2599,8 @@
       <c r="M20" s="5" t="n"/>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="n"/>
-      <c r="P20" s="11" t="n"/>
-      <c r="Q20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="11" t="n"/>
       <c r="R20" s="5" t="n"/>
       <c r="S20" s="5" t="n"/>
       <c r="T20" s="5" t="n"/>
@@ -2448,8 +2626,8 @@
       <c r="M21" s="5" t="n"/>
       <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="n"/>
-      <c r="P21" s="11" t="n"/>
-      <c r="Q21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="11" t="n"/>
       <c r="R21" s="5" t="n"/>
       <c r="S21" s="5" t="n"/>
       <c r="T21" s="5" t="n"/>
@@ -2475,8 +2653,8 @@
       <c r="M22" s="5" t="n"/>
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="5" t="n"/>
-      <c r="P22" s="11" t="n"/>
-      <c r="Q22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="11" t="n"/>
       <c r="R22" s="5" t="n"/>
       <c r="S22" s="5" t="n"/>
       <c r="T22" s="5" t="n"/>
@@ -2502,8 +2680,8 @@
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="n"/>
-      <c r="P23" s="11" t="n"/>
-      <c r="Q23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="11" t="n"/>
       <c r="R23" s="5" t="n"/>
       <c r="S23" s="5" t="n"/>
       <c r="T23" s="5" t="n"/>
@@ -2529,8 +2707,8 @@
       <c r="M24" s="5" t="n"/>
       <c r="N24" s="5" t="n"/>
       <c r="O24" s="5" t="n"/>
-      <c r="P24" s="11" t="n"/>
-      <c r="Q24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="11" t="n"/>
       <c r="R24" s="5" t="n"/>
       <c r="S24" s="5" t="n"/>
       <c r="T24" s="5" t="n"/>
@@ -2556,8 +2734,8 @@
       <c r="M25" s="5" t="n"/>
       <c r="N25" s="5" t="n"/>
       <c r="O25" s="5" t="n"/>
-      <c r="P25" s="11" t="n"/>
-      <c r="Q25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="11" t="n"/>
       <c r="R25" s="5" t="n"/>
       <c r="S25" s="5" t="n"/>
       <c r="T25" s="5" t="n"/>
@@ -2583,8 +2761,8 @@
       <c r="M26" s="5" t="n"/>
       <c r="N26" s="5" t="n"/>
       <c r="O26" s="5" t="n"/>
-      <c r="P26" s="11" t="n"/>
-      <c r="Q26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="11" t="n"/>
       <c r="R26" s="5" t="n"/>
       <c r="S26" s="5" t="n"/>
       <c r="T26" s="5" t="n"/>
@@ -2610,8 +2788,8 @@
       <c r="M27" s="5" t="n"/>
       <c r="N27" s="5" t="n"/>
       <c r="O27" s="5" t="n"/>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="11" t="n"/>
       <c r="R27" s="5" t="n"/>
       <c r="S27" s="5" t="n"/>
       <c r="T27" s="5" t="n"/>
@@ -2637,8 +2815,8 @@
       <c r="M28" s="5" t="n"/>
       <c r="N28" s="5" t="n"/>
       <c r="O28" s="5" t="n"/>
-      <c r="P28" s="11" t="n"/>
-      <c r="Q28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="11" t="n"/>
       <c r="R28" s="5" t="n"/>
       <c r="S28" s="5" t="n"/>
       <c r="T28" s="5" t="n"/>
@@ -2664,8 +2842,8 @@
       <c r="M29" s="5" t="n"/>
       <c r="N29" s="5" t="n"/>
       <c r="O29" s="5" t="n"/>
-      <c r="P29" s="11" t="n"/>
-      <c r="Q29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
+      <c r="Q29" s="11" t="n"/>
       <c r="R29" s="5" t="n"/>
       <c r="S29" s="5" t="n"/>
       <c r="T29" s="5" t="n"/>
@@ -2691,8 +2869,8 @@
       <c r="M30" s="5" t="n"/>
       <c r="N30" s="5" t="n"/>
       <c r="O30" s="5" t="n"/>
-      <c r="P30" s="11" t="n"/>
-      <c r="Q30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+      <c r="Q30" s="11" t="n"/>
       <c r="R30" s="5" t="n"/>
       <c r="S30" s="5" t="n"/>
       <c r="T30" s="5" t="n"/>
@@ -2718,8 +2896,8 @@
       <c r="M31" s="5" t="n"/>
       <c r="N31" s="5" t="n"/>
       <c r="O31" s="5" t="n"/>
-      <c r="P31" s="11" t="n"/>
-      <c r="Q31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
+      <c r="Q31" s="11" t="n"/>
       <c r="R31" s="5" t="n"/>
       <c r="S31" s="5" t="n"/>
       <c r="T31" s="5" t="n"/>
@@ -2745,8 +2923,8 @@
       <c r="M32" s="5" t="n"/>
       <c r="N32" s="5" t="n"/>
       <c r="O32" s="5" t="n"/>
-      <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+      <c r="Q32" s="11" t="n"/>
       <c r="R32" s="5" t="n"/>
       <c r="S32" s="5" t="n"/>
       <c r="T32" s="5" t="n"/>
@@ -2772,8 +2950,8 @@
       <c r="M33" s="5" t="n"/>
       <c r="N33" s="5" t="n"/>
       <c r="O33" s="5" t="n"/>
-      <c r="P33" s="11" t="n"/>
-      <c r="Q33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
+      <c r="Q33" s="11" t="n"/>
       <c r="R33" s="5" t="n"/>
       <c r="S33" s="5" t="n"/>
       <c r="T33" s="5" t="n"/>
@@ -2799,8 +2977,8 @@
       <c r="M34" s="5" t="n"/>
       <c r="N34" s="5" t="n"/>
       <c r="O34" s="5" t="n"/>
-      <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+      <c r="Q34" s="11" t="n"/>
       <c r="R34" s="5" t="n"/>
       <c r="S34" s="5" t="n"/>
       <c r="T34" s="5" t="n"/>
@@ -2826,8 +3004,8 @@
       <c r="M35" s="5" t="n"/>
       <c r="N35" s="5" t="n"/>
       <c r="O35" s="5" t="n"/>
-      <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
+      <c r="Q35" s="11" t="n"/>
       <c r="R35" s="5" t="n"/>
       <c r="S35" s="5" t="n"/>
       <c r="T35" s="5" t="n"/>
@@ -2853,8 +3031,8 @@
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="n"/>
       <c r="O36" s="5" t="n"/>
-      <c r="P36" s="11" t="n"/>
-      <c r="Q36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
+      <c r="Q36" s="11" t="n"/>
       <c r="R36" s="5" t="n"/>
       <c r="S36" s="5" t="n"/>
       <c r="T36" s="5" t="n"/>
@@ -2880,8 +3058,8 @@
       <c r="M37" s="5" t="n"/>
       <c r="N37" s="5" t="n"/>
       <c r="O37" s="5" t="n"/>
-      <c r="P37" s="11" t="n"/>
-      <c r="Q37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
+      <c r="Q37" s="11" t="n"/>
       <c r="R37" s="5" t="n"/>
       <c r="S37" s="5" t="n"/>
       <c r="T37" s="5" t="n"/>
@@ -2907,8 +3085,8 @@
       <c r="M38" s="5" t="n"/>
       <c r="N38" s="5" t="n"/>
       <c r="O38" s="5" t="n"/>
-      <c r="P38" s="11" t="n"/>
-      <c r="Q38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
+      <c r="Q38" s="11" t="n"/>
       <c r="R38" s="5" t="n"/>
       <c r="S38" s="5" t="n"/>
       <c r="T38" s="5" t="n"/>
@@ -2934,8 +3112,8 @@
       <c r="M39" s="5" t="n"/>
       <c r="N39" s="5" t="n"/>
       <c r="O39" s="5" t="n"/>
-      <c r="P39" s="11" t="n"/>
-      <c r="Q39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
+      <c r="Q39" s="11" t="n"/>
       <c r="R39" s="5" t="n"/>
       <c r="S39" s="5" t="n"/>
       <c r="T39" s="5" t="n"/>
@@ -2961,8 +3139,8 @@
       <c r="M40" s="5" t="n"/>
       <c r="N40" s="5" t="n"/>
       <c r="O40" s="5" t="n"/>
-      <c r="P40" s="11" t="n"/>
-      <c r="Q40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
+      <c r="Q40" s="11" t="n"/>
       <c r="R40" s="5" t="n"/>
       <c r="S40" s="5" t="n"/>
       <c r="T40" s="5" t="n"/>
@@ -2988,8 +3166,8 @@
       <c r="M41" s="5" t="n"/>
       <c r="N41" s="5" t="n"/>
       <c r="O41" s="5" t="n"/>
-      <c r="P41" s="11" t="n"/>
-      <c r="Q41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
+      <c r="Q41" s="11" t="n"/>
       <c r="R41" s="5" t="n"/>
       <c r="S41" s="5" t="n"/>
       <c r="T41" s="5" t="n"/>
@@ -3015,8 +3193,8 @@
       <c r="M42" s="5" t="n"/>
       <c r="N42" s="5" t="n"/>
       <c r="O42" s="5" t="n"/>
-      <c r="P42" s="11" t="n"/>
-      <c r="Q42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
+      <c r="Q42" s="11" t="n"/>
       <c r="R42" s="5" t="n"/>
       <c r="S42" s="5" t="n"/>
       <c r="T42" s="5" t="n"/>
@@ -3042,8 +3220,8 @@
       <c r="M43" s="5" t="n"/>
       <c r="N43" s="5" t="n"/>
       <c r="O43" s="5" t="n"/>
-      <c r="P43" s="11" t="n"/>
-      <c r="Q43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
+      <c r="Q43" s="11" t="n"/>
       <c r="R43" s="5" t="n"/>
       <c r="S43" s="5" t="n"/>
       <c r="T43" s="5" t="n"/>
@@ -3069,8 +3247,8 @@
       <c r="M44" s="5" t="n"/>
       <c r="N44" s="5" t="n"/>
       <c r="O44" s="5" t="n"/>
-      <c r="P44" s="11" t="n"/>
-      <c r="Q44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
+      <c r="Q44" s="11" t="n"/>
       <c r="R44" s="5" t="n"/>
       <c r="S44" s="5" t="n"/>
       <c r="T44" s="5" t="n"/>
@@ -3096,8 +3274,8 @@
       <c r="M45" s="5" t="n"/>
       <c r="N45" s="5" t="n"/>
       <c r="O45" s="5" t="n"/>
-      <c r="P45" s="11" t="n"/>
-      <c r="Q45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
+      <c r="Q45" s="11" t="n"/>
       <c r="R45" s="5" t="n"/>
       <c r="S45" s="5" t="n"/>
       <c r="T45" s="5" t="n"/>
@@ -3123,8 +3301,8 @@
       <c r="M46" s="5" t="n"/>
       <c r="N46" s="5" t="n"/>
       <c r="O46" s="5" t="n"/>
-      <c r="P46" s="11" t="n"/>
-      <c r="Q46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
+      <c r="Q46" s="11" t="n"/>
       <c r="R46" s="5" t="n"/>
       <c r="S46" s="5" t="n"/>
       <c r="T46" s="5" t="n"/>
@@ -3150,8 +3328,8 @@
       <c r="M47" s="5" t="n"/>
       <c r="N47" s="5" t="n"/>
       <c r="O47" s="5" t="n"/>
-      <c r="P47" s="11" t="n"/>
-      <c r="Q47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
+      <c r="Q47" s="11" t="n"/>
       <c r="R47" s="5" t="n"/>
       <c r="S47" s="5" t="n"/>
       <c r="T47" s="5" t="n"/>
@@ -3177,8 +3355,8 @@
       <c r="M48" s="5" t="n"/>
       <c r="N48" s="5" t="n"/>
       <c r="O48" s="5" t="n"/>
-      <c r="P48" s="11" t="n"/>
-      <c r="Q48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
+      <c r="Q48" s="11" t="n"/>
       <c r="R48" s="5" t="n"/>
       <c r="S48" s="5" t="n"/>
       <c r="T48" s="5" t="n"/>
@@ -3204,8 +3382,8 @@
       <c r="M49" s="5" t="n"/>
       <c r="N49" s="5" t="n"/>
       <c r="O49" s="5" t="n"/>
-      <c r="P49" s="11" t="n"/>
-      <c r="Q49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
+      <c r="Q49" s="11" t="n"/>
       <c r="R49" s="5" t="n"/>
       <c r="S49" s="5" t="n"/>
       <c r="T49" s="5" t="n"/>
@@ -3231,8 +3409,8 @@
       <c r="M50" s="5" t="n"/>
       <c r="N50" s="5" t="n"/>
       <c r="O50" s="5" t="n"/>
-      <c r="P50" s="11" t="n"/>
-      <c r="Q50" s="5" t="n"/>
+      <c r="P50" s="5" t="n"/>
+      <c r="Q50" s="11" t="n"/>
       <c r="R50" s="5" t="n"/>
       <c r="S50" s="5" t="n"/>
       <c r="T50" s="5" t="n"/>
@@ -3258,8 +3436,8 @@
       <c r="M51" s="5" t="n"/>
       <c r="N51" s="5" t="n"/>
       <c r="O51" s="5" t="n"/>
-      <c r="P51" s="11" t="n"/>
-      <c r="Q51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
+      <c r="Q51" s="11" t="n"/>
       <c r="R51" s="5" t="n"/>
       <c r="S51" s="5" t="n"/>
       <c r="T51" s="5" t="n"/>
@@ -3285,8 +3463,8 @@
       <c r="M52" s="5" t="n"/>
       <c r="N52" s="5" t="n"/>
       <c r="O52" s="5" t="n"/>
-      <c r="P52" s="11" t="n"/>
-      <c r="Q52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
+      <c r="Q52" s="11" t="n"/>
       <c r="R52" s="5" t="n"/>
       <c r="S52" s="5" t="n"/>
       <c r="T52" s="5" t="n"/>
@@ -3312,8 +3490,8 @@
       <c r="M53" s="5" t="n"/>
       <c r="N53" s="5" t="n"/>
       <c r="O53" s="5" t="n"/>
-      <c r="P53" s="11" t="n"/>
-      <c r="Q53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
+      <c r="Q53" s="11" t="n"/>
       <c r="R53" s="5" t="n"/>
       <c r="S53" s="5" t="n"/>
       <c r="T53" s="5" t="n"/>
@@ -3339,8 +3517,8 @@
       <c r="M54" s="5" t="n"/>
       <c r="N54" s="5" t="n"/>
       <c r="O54" s="5" t="n"/>
-      <c r="P54" s="11" t="n"/>
-      <c r="Q54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
+      <c r="Q54" s="11" t="n"/>
       <c r="R54" s="5" t="n"/>
       <c r="S54" s="5" t="n"/>
       <c r="T54" s="5" t="n"/>
@@ -3366,8 +3544,8 @@
       <c r="M55" s="5" t="n"/>
       <c r="N55" s="5" t="n"/>
       <c r="O55" s="5" t="n"/>
-      <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
+      <c r="Q55" s="11" t="n"/>
       <c r="R55" s="5" t="n"/>
       <c r="S55" s="5" t="n"/>
       <c r="T55" s="5" t="n"/>
@@ -3393,8 +3571,8 @@
       <c r="M56" s="5" t="n"/>
       <c r="N56" s="5" t="n"/>
       <c r="O56" s="5" t="n"/>
-      <c r="P56" s="11" t="n"/>
-      <c r="Q56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
+      <c r="Q56" s="11" t="n"/>
       <c r="R56" s="5" t="n"/>
       <c r="S56" s="5" t="n"/>
       <c r="T56" s="5" t="n"/>
@@ -3420,8 +3598,8 @@
       <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="n"/>
       <c r="O57" s="5" t="n"/>
-      <c r="P57" s="11" t="n"/>
-      <c r="Q57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
+      <c r="Q57" s="11" t="n"/>
       <c r="R57" s="5" t="n"/>
       <c r="S57" s="5" t="n"/>
       <c r="T57" s="5" t="n"/>
@@ -3447,8 +3625,8 @@
       <c r="M58" s="5" t="n"/>
       <c r="N58" s="5" t="n"/>
       <c r="O58" s="5" t="n"/>
-      <c r="P58" s="11" t="n"/>
-      <c r="Q58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
+      <c r="Q58" s="11" t="n"/>
       <c r="R58" s="5" t="n"/>
       <c r="S58" s="5" t="n"/>
       <c r="T58" s="5" t="n"/>
@@ -3474,8 +3652,8 @@
       <c r="M59" s="5" t="n"/>
       <c r="N59" s="5" t="n"/>
       <c r="O59" s="5" t="n"/>
-      <c r="P59" s="11" t="n"/>
-      <c r="Q59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
+      <c r="Q59" s="11" t="n"/>
       <c r="R59" s="5" t="n"/>
       <c r="S59" s="5" t="n"/>
       <c r="T59" s="5" t="n"/>
@@ -3501,8 +3679,8 @@
       <c r="M60" s="5" t="n"/>
       <c r="N60" s="5" t="n"/>
       <c r="O60" s="5" t="n"/>
-      <c r="P60" s="11" t="n"/>
-      <c r="Q60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
+      <c r="Q60" s="11" t="n"/>
       <c r="R60" s="5" t="n"/>
       <c r="S60" s="5" t="n"/>
       <c r="T60" s="5" t="n"/>
@@ -3528,8 +3706,8 @@
       <c r="M61" s="5" t="n"/>
       <c r="N61" s="5" t="n"/>
       <c r="O61" s="5" t="n"/>
-      <c r="P61" s="11" t="n"/>
-      <c r="Q61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
+      <c r="Q61" s="11" t="n"/>
       <c r="R61" s="5" t="n"/>
       <c r="S61" s="5" t="n"/>
       <c r="T61" s="5" t="n"/>
@@ -3555,8 +3733,8 @@
       <c r="M62" s="5" t="n"/>
       <c r="N62" s="5" t="n"/>
       <c r="O62" s="5" t="n"/>
-      <c r="P62" s="11" t="n"/>
-      <c r="Q62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
+      <c r="Q62" s="11" t="n"/>
       <c r="R62" s="5" t="n"/>
       <c r="S62" s="5" t="n"/>
       <c r="T62" s="5" t="n"/>
@@ -3582,8 +3760,8 @@
       <c r="M63" s="5" t="n"/>
       <c r="N63" s="5" t="n"/>
       <c r="O63" s="5" t="n"/>
-      <c r="P63" s="11" t="n"/>
-      <c r="Q63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
+      <c r="Q63" s="11" t="n"/>
       <c r="R63" s="5" t="n"/>
       <c r="S63" s="5" t="n"/>
       <c r="T63" s="5" t="n"/>
@@ -3609,8 +3787,8 @@
       <c r="M64" s="5" t="n"/>
       <c r="N64" s="5" t="n"/>
       <c r="O64" s="5" t="n"/>
-      <c r="P64" s="11" t="n"/>
-      <c r="Q64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
+      <c r="Q64" s="11" t="n"/>
       <c r="R64" s="5" t="n"/>
       <c r="S64" s="5" t="n"/>
       <c r="T64" s="5" t="n"/>
@@ -3636,8 +3814,8 @@
       <c r="M65" s="5" t="n"/>
       <c r="N65" s="5" t="n"/>
       <c r="O65" s="5" t="n"/>
-      <c r="P65" s="11" t="n"/>
-      <c r="Q65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
+      <c r="Q65" s="11" t="n"/>
       <c r="R65" s="5" t="n"/>
       <c r="S65" s="5" t="n"/>
       <c r="T65" s="5" t="n"/>
@@ -3663,8 +3841,8 @@
       <c r="M66" s="5" t="n"/>
       <c r="N66" s="5" t="n"/>
       <c r="O66" s="5" t="n"/>
-      <c r="P66" s="11" t="n"/>
-      <c r="Q66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
+      <c r="Q66" s="11" t="n"/>
       <c r="R66" s="5" t="n"/>
       <c r="S66" s="5" t="n"/>
       <c r="T66" s="5" t="n"/>
@@ -3690,8 +3868,8 @@
       <c r="M67" s="5" t="n"/>
       <c r="N67" s="5" t="n"/>
       <c r="O67" s="5" t="n"/>
-      <c r="P67" s="11" t="n"/>
-      <c r="Q67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
+      <c r="Q67" s="11" t="n"/>
       <c r="R67" s="5" t="n"/>
       <c r="S67" s="5" t="n"/>
       <c r="T67" s="5" t="n"/>
@@ -3717,8 +3895,8 @@
       <c r="M68" s="5" t="n"/>
       <c r="N68" s="5" t="n"/>
       <c r="O68" s="5" t="n"/>
-      <c r="P68" s="11" t="n"/>
-      <c r="Q68" s="5" t="n"/>
+      <c r="P68" s="5" t="n"/>
+      <c r="Q68" s="11" t="n"/>
       <c r="R68" s="5" t="n"/>
       <c r="S68" s="5" t="n"/>
       <c r="T68" s="5" t="n"/>
@@ -3744,8 +3922,8 @@
       <c r="M69" s="5" t="n"/>
       <c r="N69" s="5" t="n"/>
       <c r="O69" s="5" t="n"/>
-      <c r="P69" s="11" t="n"/>
-      <c r="Q69" s="5" t="n"/>
+      <c r="P69" s="5" t="n"/>
+      <c r="Q69" s="11" t="n"/>
       <c r="R69" s="5" t="n"/>
       <c r="S69" s="5" t="n"/>
       <c r="T69" s="5" t="n"/>
@@ -3771,8 +3949,8 @@
       <c r="M70" s="5" t="n"/>
       <c r="N70" s="5" t="n"/>
       <c r="O70" s="5" t="n"/>
-      <c r="P70" s="11" t="n"/>
-      <c r="Q70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
+      <c r="Q70" s="11" t="n"/>
       <c r="R70" s="5" t="n"/>
       <c r="S70" s="5" t="n"/>
       <c r="T70" s="5" t="n"/>
@@ -3798,8 +3976,8 @@
       <c r="M71" s="5" t="n"/>
       <c r="N71" s="5" t="n"/>
       <c r="O71" s="5" t="n"/>
-      <c r="P71" s="11" t="n"/>
-      <c r="Q71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
+      <c r="Q71" s="11" t="n"/>
       <c r="R71" s="5" t="n"/>
       <c r="S71" s="5" t="n"/>
       <c r="T71" s="5" t="n"/>
@@ -3825,8 +4003,8 @@
       <c r="M72" s="5" t="n"/>
       <c r="N72" s="5" t="n"/>
       <c r="O72" s="5" t="n"/>
-      <c r="P72" s="11" t="n"/>
-      <c r="Q72" s="5" t="n"/>
+      <c r="P72" s="5" t="n"/>
+      <c r="Q72" s="11" t="n"/>
       <c r="R72" s="5" t="n"/>
       <c r="S72" s="5" t="n"/>
       <c r="T72" s="5" t="n"/>
@@ -3852,8 +4030,8 @@
       <c r="M73" s="5" t="n"/>
       <c r="N73" s="5" t="n"/>
       <c r="O73" s="5" t="n"/>
-      <c r="P73" s="11" t="n"/>
-      <c r="Q73" s="5" t="n"/>
+      <c r="P73" s="5" t="n"/>
+      <c r="Q73" s="11" t="n"/>
       <c r="R73" s="5" t="n"/>
       <c r="S73" s="5" t="n"/>
       <c r="T73" s="5" t="n"/>
@@ -3879,8 +4057,8 @@
       <c r="M74" s="5" t="n"/>
       <c r="N74" s="5" t="n"/>
       <c r="O74" s="5" t="n"/>
-      <c r="P74" s="11" t="n"/>
-      <c r="Q74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
+      <c r="Q74" s="11" t="n"/>
       <c r="R74" s="5" t="n"/>
       <c r="S74" s="5" t="n"/>
       <c r="T74" s="5" t="n"/>
@@ -3906,8 +4084,8 @@
       <c r="M75" s="5" t="n"/>
       <c r="N75" s="5" t="n"/>
       <c r="O75" s="5" t="n"/>
-      <c r="P75" s="11" t="n"/>
-      <c r="Q75" s="5" t="n"/>
+      <c r="P75" s="5" t="n"/>
+      <c r="Q75" s="11" t="n"/>
       <c r="R75" s="5" t="n"/>
       <c r="S75" s="5" t="n"/>
       <c r="T75" s="5" t="n"/>
@@ -3933,8 +4111,8 @@
       <c r="M76" s="5" t="n"/>
       <c r="N76" s="5" t="n"/>
       <c r="O76" s="5" t="n"/>
-      <c r="P76" s="11" t="n"/>
-      <c r="Q76" s="5" t="n"/>
+      <c r="P76" s="5" t="n"/>
+      <c r="Q76" s="11" t="n"/>
       <c r="R76" s="5" t="n"/>
       <c r="S76" s="5" t="n"/>
       <c r="T76" s="5" t="n"/>
@@ -3960,8 +4138,8 @@
       <c r="M77" s="5" t="n"/>
       <c r="N77" s="5" t="n"/>
       <c r="O77" s="5" t="n"/>
-      <c r="P77" s="11" t="n"/>
-      <c r="Q77" s="5" t="n"/>
+      <c r="P77" s="5" t="n"/>
+      <c r="Q77" s="11" t="n"/>
       <c r="R77" s="5" t="n"/>
       <c r="S77" s="5" t="n"/>
       <c r="T77" s="5" t="n"/>
@@ -3987,8 +4165,8 @@
       <c r="M78" s="5" t="n"/>
       <c r="N78" s="5" t="n"/>
       <c r="O78" s="5" t="n"/>
-      <c r="P78" s="11" t="n"/>
-      <c r="Q78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
+      <c r="Q78" s="11" t="n"/>
       <c r="R78" s="5" t="n"/>
       <c r="S78" s="5" t="n"/>
       <c r="T78" s="5" t="n"/>
@@ -4014,8 +4192,8 @@
       <c r="M79" s="5" t="n"/>
       <c r="N79" s="5" t="n"/>
       <c r="O79" s="5" t="n"/>
-      <c r="P79" s="11" t="n"/>
-      <c r="Q79" s="5" t="n"/>
+      <c r="P79" s="5" t="n"/>
+      <c r="Q79" s="11" t="n"/>
       <c r="R79" s="5" t="n"/>
       <c r="S79" s="5" t="n"/>
       <c r="T79" s="5" t="n"/>
@@ -4041,8 +4219,8 @@
       <c r="M80" s="5" t="n"/>
       <c r="N80" s="5" t="n"/>
       <c r="O80" s="5" t="n"/>
-      <c r="P80" s="11" t="n"/>
-      <c r="Q80" s="5" t="n"/>
+      <c r="P80" s="5" t="n"/>
+      <c r="Q80" s="11" t="n"/>
       <c r="R80" s="5" t="n"/>
       <c r="S80" s="5" t="n"/>
       <c r="T80" s="5" t="n"/>
@@ -4068,8 +4246,8 @@
       <c r="M81" s="5" t="n"/>
       <c r="N81" s="5" t="n"/>
       <c r="O81" s="5" t="n"/>
-      <c r="P81" s="11" t="n"/>
-      <c r="Q81" s="5" t="n"/>
+      <c r="P81" s="5" t="n"/>
+      <c r="Q81" s="11" t="n"/>
       <c r="R81" s="5" t="n"/>
       <c r="S81" s="5" t="n"/>
       <c r="T81" s="5" t="n"/>
@@ -4095,8 +4273,8 @@
       <c r="M82" s="5" t="n"/>
       <c r="N82" s="5" t="n"/>
       <c r="O82" s="5" t="n"/>
-      <c r="P82" s="11" t="n"/>
-      <c r="Q82" s="5" t="n"/>
+      <c r="P82" s="5" t="n"/>
+      <c r="Q82" s="11" t="n"/>
       <c r="R82" s="5" t="n"/>
       <c r="S82" s="5" t="n"/>
       <c r="T82" s="5" t="n"/>
@@ -4122,8 +4300,8 @@
       <c r="M83" s="5" t="n"/>
       <c r="N83" s="5" t="n"/>
       <c r="O83" s="5" t="n"/>
-      <c r="P83" s="11" t="n"/>
-      <c r="Q83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
+      <c r="Q83" s="11" t="n"/>
       <c r="R83" s="5" t="n"/>
       <c r="S83" s="5" t="n"/>
       <c r="T83" s="5" t="n"/>
@@ -4149,8 +4327,8 @@
       <c r="M84" s="5" t="n"/>
       <c r="N84" s="5" t="n"/>
       <c r="O84" s="5" t="n"/>
-      <c r="P84" s="11" t="n"/>
-      <c r="Q84" s="5" t="n"/>
+      <c r="P84" s="5" t="n"/>
+      <c r="Q84" s="11" t="n"/>
       <c r="R84" s="5" t="n"/>
       <c r="S84" s="5" t="n"/>
       <c r="T84" s="5" t="n"/>
@@ -4176,8 +4354,8 @@
       <c r="M85" s="5" t="n"/>
       <c r="N85" s="5" t="n"/>
       <c r="O85" s="5" t="n"/>
-      <c r="P85" s="11" t="n"/>
-      <c r="Q85" s="5" t="n"/>
+      <c r="P85" s="5" t="n"/>
+      <c r="Q85" s="11" t="n"/>
       <c r="R85" s="5" t="n"/>
       <c r="S85" s="5" t="n"/>
       <c r="T85" s="5" t="n"/>
@@ -4203,8 +4381,8 @@
       <c r="M86" s="5" t="n"/>
       <c r="N86" s="5" t="n"/>
       <c r="O86" s="5" t="n"/>
-      <c r="P86" s="11" t="n"/>
-      <c r="Q86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
+      <c r="Q86" s="11" t="n"/>
       <c r="R86" s="5" t="n"/>
       <c r="S86" s="5" t="n"/>
       <c r="T86" s="5" t="n"/>
@@ -4230,8 +4408,8 @@
       <c r="M87" s="5" t="n"/>
       <c r="N87" s="5" t="n"/>
       <c r="O87" s="5" t="n"/>
-      <c r="P87" s="11" t="n"/>
-      <c r="Q87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
+      <c r="Q87" s="11" t="n"/>
       <c r="R87" s="5" t="n"/>
       <c r="S87" s="5" t="n"/>
       <c r="T87" s="5" t="n"/>
@@ -4257,8 +4435,8 @@
       <c r="M88" s="5" t="n"/>
       <c r="N88" s="5" t="n"/>
       <c r="O88" s="5" t="n"/>
-      <c r="P88" s="11" t="n"/>
-      <c r="Q88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
+      <c r="Q88" s="11" t="n"/>
       <c r="R88" s="5" t="n"/>
       <c r="S88" s="5" t="n"/>
       <c r="T88" s="5" t="n"/>
@@ -4284,8 +4462,8 @@
       <c r="M89" s="5" t="n"/>
       <c r="N89" s="5" t="n"/>
       <c r="O89" s="5" t="n"/>
-      <c r="P89" s="11" t="n"/>
-      <c r="Q89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
+      <c r="Q89" s="11" t="n"/>
       <c r="R89" s="5" t="n"/>
       <c r="S89" s="5" t="n"/>
       <c r="T89" s="5" t="n"/>
@@ -4311,8 +4489,8 @@
       <c r="M90" s="5" t="n"/>
       <c r="N90" s="5" t="n"/>
       <c r="O90" s="5" t="n"/>
-      <c r="P90" s="11" t="n"/>
-      <c r="Q90" s="5" t="n"/>
+      <c r="P90" s="5" t="n"/>
+      <c r="Q90" s="11" t="n"/>
       <c r="R90" s="5" t="n"/>
       <c r="S90" s="5" t="n"/>
       <c r="T90" s="5" t="n"/>
@@ -4338,8 +4516,8 @@
       <c r="M91" s="5" t="n"/>
       <c r="N91" s="5" t="n"/>
       <c r="O91" s="5" t="n"/>
-      <c r="P91" s="11" t="n"/>
-      <c r="Q91" s="5" t="n"/>
+      <c r="P91" s="5" t="n"/>
+      <c r="Q91" s="11" t="n"/>
       <c r="R91" s="5" t="n"/>
       <c r="S91" s="5" t="n"/>
       <c r="T91" s="5" t="n"/>
@@ -4365,8 +4543,8 @@
       <c r="M92" s="5" t="n"/>
       <c r="N92" s="5" t="n"/>
       <c r="O92" s="5" t="n"/>
-      <c r="P92" s="11" t="n"/>
-      <c r="Q92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
+      <c r="Q92" s="11" t="n"/>
       <c r="R92" s="5" t="n"/>
       <c r="S92" s="5" t="n"/>
       <c r="T92" s="5" t="n"/>
@@ -4392,8 +4570,8 @@
       <c r="M93" s="5" t="n"/>
       <c r="N93" s="5" t="n"/>
       <c r="O93" s="5" t="n"/>
-      <c r="P93" s="11" t="n"/>
-      <c r="Q93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
+      <c r="Q93" s="11" t="n"/>
       <c r="R93" s="5" t="n"/>
       <c r="S93" s="5" t="n"/>
       <c r="T93" s="5" t="n"/>
@@ -4419,8 +4597,8 @@
       <c r="M94" s="5" t="n"/>
       <c r="N94" s="5" t="n"/>
       <c r="O94" s="5" t="n"/>
-      <c r="P94" s="11" t="n"/>
-      <c r="Q94" s="5" t="n"/>
+      <c r="P94" s="5" t="n"/>
+      <c r="Q94" s="11" t="n"/>
       <c r="R94" s="5" t="n"/>
       <c r="S94" s="5" t="n"/>
       <c r="T94" s="5" t="n"/>
@@ -4446,8 +4624,8 @@
       <c r="M95" s="5" t="n"/>
       <c r="N95" s="5" t="n"/>
       <c r="O95" s="5" t="n"/>
-      <c r="P95" s="11" t="n"/>
-      <c r="Q95" s="5" t="n"/>
+      <c r="P95" s="5" t="n"/>
+      <c r="Q95" s="11" t="n"/>
       <c r="R95" s="5" t="n"/>
       <c r="S95" s="5" t="n"/>
       <c r="T95" s="5" t="n"/>
@@ -4473,8 +4651,8 @@
       <c r="M96" s="5" t="n"/>
       <c r="N96" s="5" t="n"/>
       <c r="O96" s="5" t="n"/>
-      <c r="P96" s="11" t="n"/>
-      <c r="Q96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
+      <c r="Q96" s="11" t="n"/>
       <c r="R96" s="5" t="n"/>
       <c r="S96" s="5" t="n"/>
       <c r="T96" s="5" t="n"/>
@@ -4500,8 +4678,8 @@
       <c r="M97" s="5" t="n"/>
       <c r="N97" s="5" t="n"/>
       <c r="O97" s="5" t="n"/>
-      <c r="P97" s="11" t="n"/>
-      <c r="Q97" s="5" t="n"/>
+      <c r="P97" s="5" t="n"/>
+      <c r="Q97" s="11" t="n"/>
       <c r="R97" s="5" t="n"/>
       <c r="S97" s="5" t="n"/>
       <c r="T97" s="5" t="n"/>
@@ -4527,8 +4705,8 @@
       <c r="M98" s="5" t="n"/>
       <c r="N98" s="5" t="n"/>
       <c r="O98" s="5" t="n"/>
-      <c r="P98" s="11" t="n"/>
-      <c r="Q98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
+      <c r="Q98" s="11" t="n"/>
       <c r="R98" s="5" t="n"/>
       <c r="S98" s="5" t="n"/>
       <c r="T98" s="5" t="n"/>
@@ -4554,8 +4732,8 @@
       <c r="M99" s="5" t="n"/>
       <c r="N99" s="5" t="n"/>
       <c r="O99" s="5" t="n"/>
-      <c r="P99" s="11" t="n"/>
-      <c r="Q99" s="5" t="n"/>
+      <c r="P99" s="5" t="n"/>
+      <c r="Q99" s="11" t="n"/>
       <c r="R99" s="5" t="n"/>
       <c r="S99" s="5" t="n"/>
       <c r="T99" s="5" t="n"/>
@@ -4581,8 +4759,8 @@
       <c r="M100" s="5" t="n"/>
       <c r="N100" s="5" t="n"/>
       <c r="O100" s="5" t="n"/>
-      <c r="P100" s="11" t="n"/>
-      <c r="Q100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
+      <c r="Q100" s="11" t="n"/>
       <c r="R100" s="5" t="n"/>
       <c r="S100" s="5" t="n"/>
       <c r="T100" s="5" t="n"/>
@@ -4608,8 +4786,8 @@
       <c r="M101" s="5" t="n"/>
       <c r="N101" s="5" t="n"/>
       <c r="O101" s="5" t="n"/>
-      <c r="P101" s="11" t="n"/>
-      <c r="Q101" s="5" t="n"/>
+      <c r="P101" s="5" t="n"/>
+      <c r="Q101" s="11" t="n"/>
       <c r="R101" s="5" t="n"/>
       <c r="S101" s="5" t="n"/>
       <c r="T101" s="5" t="n"/>
@@ -4635,8 +4813,8 @@
       <c r="M102" s="5" t="n"/>
       <c r="N102" s="5" t="n"/>
       <c r="O102" s="5" t="n"/>
-      <c r="P102" s="11" t="n"/>
-      <c r="Q102" s="5" t="n"/>
+      <c r="P102" s="5" t="n"/>
+      <c r="Q102" s="11" t="n"/>
       <c r="R102" s="5" t="n"/>
       <c r="S102" s="5" t="n"/>
       <c r="T102" s="5" t="n"/>
@@ -4662,8 +4840,8 @@
       <c r="M103" s="5" t="n"/>
       <c r="N103" s="5" t="n"/>
       <c r="O103" s="5" t="n"/>
-      <c r="P103" s="11" t="n"/>
-      <c r="Q103" s="5" t="n"/>
+      <c r="P103" s="5" t="n"/>
+      <c r="Q103" s="11" t="n"/>
       <c r="R103" s="5" t="n"/>
       <c r="S103" s="5" t="n"/>
       <c r="T103" s="5" t="n"/>
@@ -4689,8 +4867,8 @@
       <c r="M104" s="5" t="n"/>
       <c r="N104" s="5" t="n"/>
       <c r="O104" s="5" t="n"/>
-      <c r="P104" s="11" t="n"/>
-      <c r="Q104" s="5" t="n"/>
+      <c r="P104" s="5" t="n"/>
+      <c r="Q104" s="11" t="n"/>
       <c r="R104" s="5" t="n"/>
       <c r="S104" s="5" t="n"/>
       <c r="T104" s="5" t="n"/>
@@ -4716,8 +4894,8 @@
       <c r="M105" s="5" t="n"/>
       <c r="N105" s="5" t="n"/>
       <c r="O105" s="5" t="n"/>
-      <c r="P105" s="11" t="n"/>
-      <c r="Q105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
+      <c r="Q105" s="11" t="n"/>
       <c r="R105" s="5" t="n"/>
       <c r="S105" s="5" t="n"/>
       <c r="T105" s="5" t="n"/>
@@ -4743,8 +4921,8 @@
       <c r="M106" s="5" t="n"/>
       <c r="N106" s="5" t="n"/>
       <c r="O106" s="5" t="n"/>
-      <c r="P106" s="11" t="n"/>
-      <c r="Q106" s="5" t="n"/>
+      <c r="P106" s="5" t="n"/>
+      <c r="Q106" s="11" t="n"/>
       <c r="R106" s="5" t="n"/>
       <c r="S106" s="5" t="n"/>
       <c r="T106" s="5" t="n"/>
@@ -4770,8 +4948,8 @@
       <c r="M107" s="5" t="n"/>
       <c r="N107" s="5" t="n"/>
       <c r="O107" s="5" t="n"/>
-      <c r="P107" s="11" t="n"/>
-      <c r="Q107" s="5" t="n"/>
+      <c r="P107" s="5" t="n"/>
+      <c r="Q107" s="11" t="n"/>
       <c r="R107" s="5" t="n"/>
       <c r="S107" s="5" t="n"/>
       <c r="T107" s="5" t="n"/>
@@ -4797,8 +4975,8 @@
       <c r="M108" s="5" t="n"/>
       <c r="N108" s="5" t="n"/>
       <c r="O108" s="5" t="n"/>
-      <c r="P108" s="11" t="n"/>
-      <c r="Q108" s="5" t="n"/>
+      <c r="P108" s="5" t="n"/>
+      <c r="Q108" s="11" t="n"/>
       <c r="R108" s="5" t="n"/>
       <c r="S108" s="5" t="n"/>
       <c r="T108" s="5" t="n"/>
@@ -4824,8 +5002,8 @@
       <c r="M109" s="5" t="n"/>
       <c r="N109" s="5" t="n"/>
       <c r="O109" s="5" t="n"/>
-      <c r="P109" s="11" t="n"/>
-      <c r="Q109" s="5" t="n"/>
+      <c r="P109" s="5" t="n"/>
+      <c r="Q109" s="11" t="n"/>
       <c r="R109" s="5" t="n"/>
       <c r="S109" s="5" t="n"/>
       <c r="T109" s="5" t="n"/>
@@ -4851,8 +5029,8 @@
       <c r="M110" s="5" t="n"/>
       <c r="N110" s="5" t="n"/>
       <c r="O110" s="5" t="n"/>
-      <c r="P110" s="11" t="n"/>
-      <c r="Q110" s="5" t="n"/>
+      <c r="P110" s="5" t="n"/>
+      <c r="Q110" s="11" t="n"/>
       <c r="R110" s="5" t="n"/>
       <c r="S110" s="5" t="n"/>
       <c r="T110" s="5" t="n"/>
@@ -4878,8 +5056,8 @@
       <c r="M111" s="5" t="n"/>
       <c r="N111" s="5" t="n"/>
       <c r="O111" s="5" t="n"/>
-      <c r="P111" s="11" t="n"/>
-      <c r="Q111" s="5" t="n"/>
+      <c r="P111" s="5" t="n"/>
+      <c r="Q111" s="11" t="n"/>
       <c r="R111" s="5" t="n"/>
       <c r="S111" s="5" t="n"/>
       <c r="T111" s="5" t="n"/>
@@ -4905,8 +5083,8 @@
       <c r="M112" s="5" t="n"/>
       <c r="N112" s="5" t="n"/>
       <c r="O112" s="5" t="n"/>
-      <c r="P112" s="11" t="n"/>
-      <c r="Q112" s="5" t="n"/>
+      <c r="P112" s="5" t="n"/>
+      <c r="Q112" s="11" t="n"/>
       <c r="R112" s="5" t="n"/>
       <c r="S112" s="5" t="n"/>
       <c r="T112" s="5" t="n"/>
@@ -4932,8 +5110,8 @@
       <c r="M113" s="5" t="n"/>
       <c r="N113" s="5" t="n"/>
       <c r="O113" s="5" t="n"/>
-      <c r="P113" s="11" t="n"/>
-      <c r="Q113" s="5" t="n"/>
+      <c r="P113" s="5" t="n"/>
+      <c r="Q113" s="11" t="n"/>
       <c r="R113" s="5" t="n"/>
       <c r="S113" s="5" t="n"/>
       <c r="T113" s="5" t="n"/>
@@ -4959,8 +5137,8 @@
       <c r="M114" s="5" t="n"/>
       <c r="N114" s="5" t="n"/>
       <c r="O114" s="5" t="n"/>
-      <c r="P114" s="11" t="n"/>
-      <c r="Q114" s="5" t="n"/>
+      <c r="P114" s="5" t="n"/>
+      <c r="Q114" s="11" t="n"/>
       <c r="R114" s="5" t="n"/>
       <c r="S114" s="5" t="n"/>
       <c r="T114" s="5" t="n"/>
@@ -4986,8 +5164,8 @@
       <c r="M115" s="5" t="n"/>
       <c r="N115" s="5" t="n"/>
       <c r="O115" s="5" t="n"/>
-      <c r="P115" s="11" t="n"/>
-      <c r="Q115" s="5" t="n"/>
+      <c r="P115" s="5" t="n"/>
+      <c r="Q115" s="11" t="n"/>
       <c r="R115" s="5" t="n"/>
       <c r="S115" s="5" t="n"/>
       <c r="T115" s="5" t="n"/>
@@ -5013,8 +5191,8 @@
       <c r="M116" s="5" t="n"/>
       <c r="N116" s="5" t="n"/>
       <c r="O116" s="5" t="n"/>
-      <c r="P116" s="11" t="n"/>
-      <c r="Q116" s="5" t="n"/>
+      <c r="P116" s="5" t="n"/>
+      <c r="Q116" s="11" t="n"/>
       <c r="R116" s="5" t="n"/>
       <c r="S116" s="5" t="n"/>
       <c r="T116" s="5" t="n"/>
@@ -5040,8 +5218,8 @@
       <c r="M117" s="5" t="n"/>
       <c r="N117" s="5" t="n"/>
       <c r="O117" s="5" t="n"/>
-      <c r="P117" s="11" t="n"/>
-      <c r="Q117" s="5" t="n"/>
+      <c r="P117" s="5" t="n"/>
+      <c r="Q117" s="11" t="n"/>
       <c r="R117" s="5" t="n"/>
       <c r="S117" s="5" t="n"/>
       <c r="T117" s="5" t="n"/>
@@ -5067,8 +5245,8 @@
       <c r="M118" s="5" t="n"/>
       <c r="N118" s="5" t="n"/>
       <c r="O118" s="5" t="n"/>
-      <c r="P118" s="11" t="n"/>
-      <c r="Q118" s="5" t="n"/>
+      <c r="P118" s="5" t="n"/>
+      <c r="Q118" s="11" t="n"/>
       <c r="R118" s="5" t="n"/>
       <c r="S118" s="5" t="n"/>
       <c r="T118" s="5" t="n"/>
@@ -5094,8 +5272,8 @@
       <c r="M119" s="5" t="n"/>
       <c r="N119" s="5" t="n"/>
       <c r="O119" s="5" t="n"/>
-      <c r="P119" s="11" t="n"/>
-      <c r="Q119" s="5" t="n"/>
+      <c r="P119" s="5" t="n"/>
+      <c r="Q119" s="11" t="n"/>
       <c r="R119" s="5" t="n"/>
       <c r="S119" s="5" t="n"/>
       <c r="T119" s="5" t="n"/>
@@ -5121,8 +5299,8 @@
       <c r="M120" s="5" t="n"/>
       <c r="N120" s="5" t="n"/>
       <c r="O120" s="5" t="n"/>
-      <c r="P120" s="11" t="n"/>
-      <c r="Q120" s="5" t="n"/>
+      <c r="P120" s="5" t="n"/>
+      <c r="Q120" s="11" t="n"/>
       <c r="R120" s="5" t="n"/>
       <c r="S120" s="5" t="n"/>
       <c r="T120" s="5" t="n"/>
@@ -5148,8 +5326,8 @@
       <c r="M121" s="5" t="n"/>
       <c r="N121" s="5" t="n"/>
       <c r="O121" s="5" t="n"/>
-      <c r="P121" s="11" t="n"/>
-      <c r="Q121" s="5" t="n"/>
+      <c r="P121" s="5" t="n"/>
+      <c r="Q121" s="11" t="n"/>
       <c r="R121" s="5" t="n"/>
       <c r="S121" s="5" t="n"/>
       <c r="T121" s="5" t="n"/>
@@ -5175,8 +5353,8 @@
       <c r="M122" s="5" t="n"/>
       <c r="N122" s="5" t="n"/>
       <c r="O122" s="5" t="n"/>
-      <c r="P122" s="11" t="n"/>
-      <c r="Q122" s="5" t="n"/>
+      <c r="P122" s="5" t="n"/>
+      <c r="Q122" s="11" t="n"/>
       <c r="R122" s="5" t="n"/>
       <c r="S122" s="5" t="n"/>
       <c r="T122" s="5" t="n"/>
@@ -5202,8 +5380,8 @@
       <c r="M123" s="5" t="n"/>
       <c r="N123" s="5" t="n"/>
       <c r="O123" s="5" t="n"/>
-      <c r="P123" s="11" t="n"/>
-      <c r="Q123" s="5" t="n"/>
+      <c r="P123" s="5" t="n"/>
+      <c r="Q123" s="11" t="n"/>
       <c r="R123" s="5" t="n"/>
       <c r="S123" s="5" t="n"/>
       <c r="T123" s="5" t="n"/>
@@ -5229,8 +5407,8 @@
       <c r="M124" s="5" t="n"/>
       <c r="N124" s="5" t="n"/>
       <c r="O124" s="5" t="n"/>
-      <c r="P124" s="11" t="n"/>
-      <c r="Q124" s="5" t="n"/>
+      <c r="P124" s="5" t="n"/>
+      <c r="Q124" s="11" t="n"/>
       <c r="R124" s="5" t="n"/>
       <c r="S124" s="5" t="n"/>
       <c r="T124" s="5" t="n"/>
@@ -5256,8 +5434,8 @@
       <c r="M125" s="5" t="n"/>
       <c r="N125" s="5" t="n"/>
       <c r="O125" s="5" t="n"/>
-      <c r="P125" s="11" t="n"/>
-      <c r="Q125" s="5" t="n"/>
+      <c r="P125" s="5" t="n"/>
+      <c r="Q125" s="11" t="n"/>
       <c r="R125" s="5" t="n"/>
       <c r="S125" s="5" t="n"/>
       <c r="T125" s="5" t="n"/>
@@ -5283,8 +5461,8 @@
       <c r="M126" s="5" t="n"/>
       <c r="N126" s="5" t="n"/>
       <c r="O126" s="5" t="n"/>
-      <c r="P126" s="11" t="n"/>
-      <c r="Q126" s="5" t="n"/>
+      <c r="P126" s="5" t="n"/>
+      <c r="Q126" s="11" t="n"/>
       <c r="R126" s="5" t="n"/>
       <c r="S126" s="5" t="n"/>
       <c r="T126" s="5" t="n"/>
@@ -5310,8 +5488,8 @@
       <c r="M127" s="5" t="n"/>
       <c r="N127" s="5" t="n"/>
       <c r="O127" s="5" t="n"/>
-      <c r="P127" s="11" t="n"/>
-      <c r="Q127" s="5" t="n"/>
+      <c r="P127" s="5" t="n"/>
+      <c r="Q127" s="11" t="n"/>
       <c r="R127" s="5" t="n"/>
       <c r="S127" s="5" t="n"/>
       <c r="T127" s="5" t="n"/>
@@ -5337,8 +5515,8 @@
       <c r="M128" s="5" t="n"/>
       <c r="N128" s="5" t="n"/>
       <c r="O128" s="5" t="n"/>
-      <c r="P128" s="11" t="n"/>
-      <c r="Q128" s="5" t="n"/>
+      <c r="P128" s="5" t="n"/>
+      <c r="Q128" s="11" t="n"/>
       <c r="R128" s="5" t="n"/>
       <c r="S128" s="5" t="n"/>
       <c r="T128" s="5" t="n"/>
@@ -5364,8 +5542,8 @@
       <c r="M129" s="5" t="n"/>
       <c r="N129" s="5" t="n"/>
       <c r="O129" s="5" t="n"/>
-      <c r="P129" s="11" t="n"/>
-      <c r="Q129" s="5" t="n"/>
+      <c r="P129" s="5" t="n"/>
+      <c r="Q129" s="11" t="n"/>
       <c r="R129" s="5" t="n"/>
       <c r="S129" s="5" t="n"/>
       <c r="T129" s="5" t="n"/>
@@ -5391,8 +5569,8 @@
       <c r="M130" s="5" t="n"/>
       <c r="N130" s="5" t="n"/>
       <c r="O130" s="5" t="n"/>
-      <c r="P130" s="11" t="n"/>
-      <c r="Q130" s="5" t="n"/>
+      <c r="P130" s="5" t="n"/>
+      <c r="Q130" s="11" t="n"/>
       <c r="R130" s="5" t="n"/>
       <c r="S130" s="5" t="n"/>
       <c r="T130" s="5" t="n"/>
@@ -5418,8 +5596,8 @@
       <c r="M131" s="5" t="n"/>
       <c r="N131" s="5" t="n"/>
       <c r="O131" s="5" t="n"/>
-      <c r="P131" s="11" t="n"/>
-      <c r="Q131" s="5" t="n"/>
+      <c r="P131" s="5" t="n"/>
+      <c r="Q131" s="11" t="n"/>
       <c r="R131" s="5" t="n"/>
       <c r="S131" s="5" t="n"/>
       <c r="T131" s="5" t="n"/>
@@ -5445,8 +5623,8 @@
       <c r="M132" s="5" t="n"/>
       <c r="N132" s="5" t="n"/>
       <c r="O132" s="5" t="n"/>
-      <c r="P132" s="11" t="n"/>
-      <c r="Q132" s="5" t="n"/>
+      <c r="P132" s="5" t="n"/>
+      <c r="Q132" s="11" t="n"/>
       <c r="R132" s="5" t="n"/>
       <c r="S132" s="5" t="n"/>
       <c r="T132" s="5" t="n"/>
@@ -5472,8 +5650,8 @@
       <c r="M133" s="5" t="n"/>
       <c r="N133" s="5" t="n"/>
       <c r="O133" s="5" t="n"/>
-      <c r="P133" s="11" t="n"/>
-      <c r="Q133" s="5" t="n"/>
+      <c r="P133" s="5" t="n"/>
+      <c r="Q133" s="11" t="n"/>
       <c r="R133" s="5" t="n"/>
       <c r="S133" s="5" t="n"/>
       <c r="T133" s="5" t="n"/>
@@ -5499,8 +5677,8 @@
       <c r="M134" s="5" t="n"/>
       <c r="N134" s="5" t="n"/>
       <c r="O134" s="5" t="n"/>
-      <c r="P134" s="11" t="n"/>
-      <c r="Q134" s="5" t="n"/>
+      <c r="P134" s="5" t="n"/>
+      <c r="Q134" s="11" t="n"/>
       <c r="R134" s="5" t="n"/>
       <c r="S134" s="5" t="n"/>
       <c r="T134" s="5" t="n"/>
@@ -5526,8 +5704,8 @@
       <c r="M135" s="5" t="n"/>
       <c r="N135" s="5" t="n"/>
       <c r="O135" s="5" t="n"/>
-      <c r="P135" s="11" t="n"/>
-      <c r="Q135" s="5" t="n"/>
+      <c r="P135" s="5" t="n"/>
+      <c r="Q135" s="11" t="n"/>
       <c r="R135" s="5" t="n"/>
       <c r="S135" s="5" t="n"/>
       <c r="T135" s="5" t="n"/>
@@ -5553,8 +5731,8 @@
       <c r="M136" s="5" t="n"/>
       <c r="N136" s="5" t="n"/>
       <c r="O136" s="5" t="n"/>
-      <c r="P136" s="11" t="n"/>
-      <c r="Q136" s="5" t="n"/>
+      <c r="P136" s="5" t="n"/>
+      <c r="Q136" s="11" t="n"/>
       <c r="R136" s="5" t="n"/>
       <c r="S136" s="5" t="n"/>
       <c r="T136" s="5" t="n"/>
@@ -5580,8 +5758,8 @@
       <c r="M137" s="5" t="n"/>
       <c r="N137" s="5" t="n"/>
       <c r="O137" s="5" t="n"/>
-      <c r="P137" s="11" t="n"/>
-      <c r="Q137" s="5" t="n"/>
+      <c r="P137" s="5" t="n"/>
+      <c r="Q137" s="11" t="n"/>
       <c r="R137" s="5" t="n"/>
       <c r="S137" s="5" t="n"/>
       <c r="T137" s="5" t="n"/>
@@ -5607,8 +5785,8 @@
       <c r="M138" s="5" t="n"/>
       <c r="N138" s="5" t="n"/>
       <c r="O138" s="5" t="n"/>
-      <c r="P138" s="11" t="n"/>
-      <c r="Q138" s="5" t="n"/>
+      <c r="P138" s="5" t="n"/>
+      <c r="Q138" s="11" t="n"/>
       <c r="R138" s="5" t="n"/>
       <c r="S138" s="5" t="n"/>
       <c r="T138" s="5" t="n"/>
@@ -5634,8 +5812,8 @@
       <c r="M139" s="5" t="n"/>
       <c r="N139" s="5" t="n"/>
       <c r="O139" s="5" t="n"/>
-      <c r="P139" s="11" t="n"/>
-      <c r="Q139" s="5" t="n"/>
+      <c r="P139" s="5" t="n"/>
+      <c r="Q139" s="11" t="n"/>
       <c r="R139" s="5" t="n"/>
       <c r="S139" s="5" t="n"/>
       <c r="T139" s="5" t="n"/>
@@ -5661,8 +5839,8 @@
       <c r="M140" s="5" t="n"/>
       <c r="N140" s="5" t="n"/>
       <c r="O140" s="5" t="n"/>
-      <c r="P140" s="11" t="n"/>
-      <c r="Q140" s="5" t="n"/>
+      <c r="P140" s="5" t="n"/>
+      <c r="Q140" s="11" t="n"/>
       <c r="R140" s="5" t="n"/>
       <c r="S140" s="5" t="n"/>
       <c r="T140" s="5" t="n"/>
@@ -5688,8 +5866,8 @@
       <c r="M141" s="5" t="n"/>
       <c r="N141" s="5" t="n"/>
       <c r="O141" s="5" t="n"/>
-      <c r="P141" s="11" t="n"/>
-      <c r="Q141" s="5" t="n"/>
+      <c r="P141" s="5" t="n"/>
+      <c r="Q141" s="11" t="n"/>
       <c r="R141" s="5" t="n"/>
       <c r="S141" s="5" t="n"/>
       <c r="T141" s="5" t="n"/>
@@ -5715,8 +5893,8 @@
       <c r="M142" s="5" t="n"/>
       <c r="N142" s="5" t="n"/>
       <c r="O142" s="5" t="n"/>
-      <c r="P142" s="11" t="n"/>
-      <c r="Q142" s="5" t="n"/>
+      <c r="P142" s="5" t="n"/>
+      <c r="Q142" s="11" t="n"/>
       <c r="R142" s="5" t="n"/>
       <c r="S142" s="5" t="n"/>
       <c r="T142" s="5" t="n"/>
@@ -5742,8 +5920,8 @@
       <c r="M143" s="5" t="n"/>
       <c r="N143" s="5" t="n"/>
       <c r="O143" s="5" t="n"/>
-      <c r="P143" s="11" t="n"/>
-      <c r="Q143" s="5" t="n"/>
+      <c r="P143" s="5" t="n"/>
+      <c r="Q143" s="11" t="n"/>
       <c r="R143" s="5" t="n"/>
       <c r="S143" s="5" t="n"/>
       <c r="T143" s="5" t="n"/>
@@ -5769,8 +5947,8 @@
       <c r="M144" s="5" t="n"/>
       <c r="N144" s="5" t="n"/>
       <c r="O144" s="5" t="n"/>
-      <c r="P144" s="11" t="n"/>
-      <c r="Q144" s="5" t="n"/>
+      <c r="P144" s="5" t="n"/>
+      <c r="Q144" s="11" t="n"/>
       <c r="R144" s="5" t="n"/>
       <c r="S144" s="5" t="n"/>
       <c r="T144" s="5" t="n"/>
@@ -5796,8 +5974,8 @@
       <c r="M145" s="5" t="n"/>
       <c r="N145" s="5" t="n"/>
       <c r="O145" s="5" t="n"/>
-      <c r="P145" s="11" t="n"/>
-      <c r="Q145" s="5" t="n"/>
+      <c r="P145" s="5" t="n"/>
+      <c r="Q145" s="11" t="n"/>
       <c r="R145" s="5" t="n"/>
       <c r="S145" s="5" t="n"/>
       <c r="T145" s="5" t="n"/>
@@ -5823,8 +6001,8 @@
       <c r="M146" s="5" t="n"/>
       <c r="N146" s="5" t="n"/>
       <c r="O146" s="5" t="n"/>
-      <c r="P146" s="11" t="n"/>
-      <c r="Q146" s="5" t="n"/>
+      <c r="P146" s="5" t="n"/>
+      <c r="Q146" s="11" t="n"/>
       <c r="R146" s="5" t="n"/>
       <c r="S146" s="5" t="n"/>
       <c r="T146" s="5" t="n"/>
@@ -5850,8 +6028,8 @@
       <c r="M147" s="5" t="n"/>
       <c r="N147" s="5" t="n"/>
       <c r="O147" s="5" t="n"/>
-      <c r="P147" s="11" t="n"/>
-      <c r="Q147" s="5" t="n"/>
+      <c r="P147" s="5" t="n"/>
+      <c r="Q147" s="11" t="n"/>
       <c r="R147" s="5" t="n"/>
       <c r="S147" s="5" t="n"/>
       <c r="T147" s="5" t="n"/>
@@ -5877,8 +6055,8 @@
       <c r="M148" s="5" t="n"/>
       <c r="N148" s="5" t="n"/>
       <c r="O148" s="5" t="n"/>
-      <c r="P148" s="11" t="n"/>
-      <c r="Q148" s="5" t="n"/>
+      <c r="P148" s="5" t="n"/>
+      <c r="Q148" s="11" t="n"/>
       <c r="R148" s="5" t="n"/>
       <c r="S148" s="5" t="n"/>
       <c r="T148" s="5" t="n"/>
@@ -5904,8 +6082,8 @@
       <c r="M149" s="5" t="n"/>
       <c r="N149" s="5" t="n"/>
       <c r="O149" s="5" t="n"/>
-      <c r="P149" s="11" t="n"/>
-      <c r="Q149" s="5" t="n"/>
+      <c r="P149" s="5" t="n"/>
+      <c r="Q149" s="11" t="n"/>
       <c r="R149" s="5" t="n"/>
       <c r="S149" s="5" t="n"/>
       <c r="T149" s="5" t="n"/>
@@ -5931,8 +6109,8 @@
       <c r="M150" s="5" t="n"/>
       <c r="N150" s="5" t="n"/>
       <c r="O150" s="5" t="n"/>
-      <c r="P150" s="11" t="n"/>
-      <c r="Q150" s="5" t="n"/>
+      <c r="P150" s="5" t="n"/>
+      <c r="Q150" s="11" t="n"/>
       <c r="R150" s="5" t="n"/>
       <c r="S150" s="5" t="n"/>
       <c r="T150" s="5" t="n"/>
@@ -5958,8 +6136,8 @@
       <c r="M151" s="5" t="n"/>
       <c r="N151" s="5" t="n"/>
       <c r="O151" s="5" t="n"/>
-      <c r="P151" s="11" t="n"/>
-      <c r="Q151" s="5" t="n"/>
+      <c r="P151" s="5" t="n"/>
+      <c r="Q151" s="11" t="n"/>
       <c r="R151" s="5" t="n"/>
       <c r="S151" s="5" t="n"/>
       <c r="T151" s="5" t="n"/>
@@ -5985,8 +6163,8 @@
       <c r="M152" s="5" t="n"/>
       <c r="N152" s="5" t="n"/>
       <c r="O152" s="5" t="n"/>
-      <c r="P152" s="11" t="n"/>
-      <c r="Q152" s="5" t="n"/>
+      <c r="P152" s="5" t="n"/>
+      <c r="Q152" s="11" t="n"/>
       <c r="R152" s="5" t="n"/>
       <c r="S152" s="5" t="n"/>
       <c r="T152" s="5" t="n"/>
@@ -6012,8 +6190,8 @@
       <c r="M153" s="5" t="n"/>
       <c r="N153" s="5" t="n"/>
       <c r="O153" s="5" t="n"/>
-      <c r="P153" s="11" t="n"/>
-      <c r="Q153" s="5" t="n"/>
+      <c r="P153" s="5" t="n"/>
+      <c r="Q153" s="11" t="n"/>
       <c r="R153" s="5" t="n"/>
       <c r="S153" s="5" t="n"/>
       <c r="T153" s="5" t="n"/>
@@ -6039,8 +6217,8 @@
       <c r="M154" s="5" t="n"/>
       <c r="N154" s="5" t="n"/>
       <c r="O154" s="5" t="n"/>
-      <c r="P154" s="11" t="n"/>
-      <c r="Q154" s="5" t="n"/>
+      <c r="P154" s="5" t="n"/>
+      <c r="Q154" s="11" t="n"/>
       <c r="R154" s="5" t="n"/>
       <c r="S154" s="5" t="n"/>
       <c r="T154" s="5" t="n"/>
@@ -6066,8 +6244,8 @@
       <c r="M155" s="5" t="n"/>
       <c r="N155" s="5" t="n"/>
       <c r="O155" s="5" t="n"/>
-      <c r="P155" s="11" t="n"/>
-      <c r="Q155" s="5" t="n"/>
+      <c r="P155" s="5" t="n"/>
+      <c r="Q155" s="11" t="n"/>
       <c r="R155" s="5" t="n"/>
       <c r="S155" s="5" t="n"/>
       <c r="T155" s="5" t="n"/>
@@ -6093,8 +6271,8 @@
       <c r="M156" s="5" t="n"/>
       <c r="N156" s="5" t="n"/>
       <c r="O156" s="5" t="n"/>
-      <c r="P156" s="11" t="n"/>
-      <c r="Q156" s="5" t="n"/>
+      <c r="P156" s="5" t="n"/>
+      <c r="Q156" s="11" t="n"/>
       <c r="R156" s="5" t="n"/>
       <c r="S156" s="5" t="n"/>
       <c r="T156" s="5" t="n"/>
@@ -6120,8 +6298,8 @@
       <c r="M157" s="5" t="n"/>
       <c r="N157" s="5" t="n"/>
       <c r="O157" s="5" t="n"/>
-      <c r="P157" s="11" t="n"/>
-      <c r="Q157" s="5" t="n"/>
+      <c r="P157" s="5" t="n"/>
+      <c r="Q157" s="11" t="n"/>
       <c r="R157" s="5" t="n"/>
       <c r="S157" s="5" t="n"/>
       <c r="T157" s="5" t="n"/>
@@ -6147,8 +6325,8 @@
       <c r="M158" s="5" t="n"/>
       <c r="N158" s="5" t="n"/>
       <c r="O158" s="5" t="n"/>
-      <c r="P158" s="11" t="n"/>
-      <c r="Q158" s="5" t="n"/>
+      <c r="P158" s="5" t="n"/>
+      <c r="Q158" s="11" t="n"/>
       <c r="R158" s="5" t="n"/>
       <c r="S158" s="5" t="n"/>
       <c r="T158" s="5" t="n"/>
@@ -6174,8 +6352,8 @@
       <c r="M159" s="5" t="n"/>
       <c r="N159" s="5" t="n"/>
       <c r="O159" s="5" t="n"/>
-      <c r="P159" s="11" t="n"/>
-      <c r="Q159" s="5" t="n"/>
+      <c r="P159" s="5" t="n"/>
+      <c r="Q159" s="11" t="n"/>
       <c r="R159" s="5" t="n"/>
       <c r="S159" s="5" t="n"/>
       <c r="T159" s="5" t="n"/>
@@ -6201,8 +6379,8 @@
       <c r="M160" s="5" t="n"/>
       <c r="N160" s="5" t="n"/>
       <c r="O160" s="5" t="n"/>
-      <c r="P160" s="11" t="n"/>
-      <c r="Q160" s="5" t="n"/>
+      <c r="P160" s="5" t="n"/>
+      <c r="Q160" s="11" t="n"/>
       <c r="R160" s="5" t="n"/>
       <c r="S160" s="5" t="n"/>
       <c r="T160" s="5" t="n"/>
@@ -6228,8 +6406,8 @@
       <c r="M161" s="5" t="n"/>
       <c r="N161" s="5" t="n"/>
       <c r="O161" s="5" t="n"/>
-      <c r="P161" s="11" t="n"/>
-      <c r="Q161" s="5" t="n"/>
+      <c r="P161" s="5" t="n"/>
+      <c r="Q161" s="11" t="n"/>
       <c r="R161" s="5" t="n"/>
       <c r="S161" s="5" t="n"/>
       <c r="T161" s="5" t="n"/>
@@ -6255,8 +6433,8 @@
       <c r="M162" s="5" t="n"/>
       <c r="N162" s="5" t="n"/>
       <c r="O162" s="5" t="n"/>
-      <c r="P162" s="11" t="n"/>
-      <c r="Q162" s="5" t="n"/>
+      <c r="P162" s="5" t="n"/>
+      <c r="Q162" s="11" t="n"/>
       <c r="R162" s="5" t="n"/>
       <c r="S162" s="5" t="n"/>
       <c r="T162" s="5" t="n"/>
@@ -6282,8 +6460,8 @@
       <c r="M163" s="5" t="n"/>
       <c r="N163" s="5" t="n"/>
       <c r="O163" s="5" t="n"/>
-      <c r="P163" s="11" t="n"/>
-      <c r="Q163" s="5" t="n"/>
+      <c r="P163" s="5" t="n"/>
+      <c r="Q163" s="11" t="n"/>
       <c r="R163" s="5" t="n"/>
       <c r="S163" s="5" t="n"/>
       <c r="T163" s="5" t="n"/>
@@ -6309,8 +6487,8 @@
       <c r="M164" s="5" t="n"/>
       <c r="N164" s="5" t="n"/>
       <c r="O164" s="5" t="n"/>
-      <c r="P164" s="11" t="n"/>
-      <c r="Q164" s="5" t="n"/>
+      <c r="P164" s="5" t="n"/>
+      <c r="Q164" s="11" t="n"/>
       <c r="R164" s="5" t="n"/>
       <c r="S164" s="5" t="n"/>
       <c r="T164" s="5" t="n"/>
@@ -6336,8 +6514,8 @@
       <c r="M165" s="5" t="n"/>
       <c r="N165" s="5" t="n"/>
       <c r="O165" s="5" t="n"/>
-      <c r="P165" s="11" t="n"/>
-      <c r="Q165" s="5" t="n"/>
+      <c r="P165" s="5" t="n"/>
+      <c r="Q165" s="11" t="n"/>
       <c r="R165" s="5" t="n"/>
       <c r="S165" s="5" t="n"/>
       <c r="T165" s="5" t="n"/>
@@ -6363,8 +6541,8 @@
       <c r="M166" s="5" t="n"/>
       <c r="N166" s="5" t="n"/>
       <c r="O166" s="5" t="n"/>
-      <c r="P166" s="11" t="n"/>
-      <c r="Q166" s="5" t="n"/>
+      <c r="P166" s="5" t="n"/>
+      <c r="Q166" s="11" t="n"/>
       <c r="R166" s="5" t="n"/>
       <c r="S166" s="5" t="n"/>
       <c r="T166" s="5" t="n"/>
@@ -6390,8 +6568,8 @@
       <c r="M167" s="5" t="n"/>
       <c r="N167" s="5" t="n"/>
       <c r="O167" s="5" t="n"/>
-      <c r="P167" s="11" t="n"/>
-      <c r="Q167" s="5" t="n"/>
+      <c r="P167" s="5" t="n"/>
+      <c r="Q167" s="11" t="n"/>
       <c r="R167" s="5" t="n"/>
       <c r="S167" s="5" t="n"/>
       <c r="T167" s="5" t="n"/>
@@ -6417,8 +6595,8 @@
       <c r="M168" s="5" t="n"/>
       <c r="N168" s="5" t="n"/>
       <c r="O168" s="5" t="n"/>
-      <c r="P168" s="11" t="n"/>
-      <c r="Q168" s="5" t="n"/>
+      <c r="P168" s="5" t="n"/>
+      <c r="Q168" s="11" t="n"/>
       <c r="R168" s="5" t="n"/>
       <c r="S168" s="5" t="n"/>
       <c r="T168" s="5" t="n"/>
@@ -6444,8 +6622,8 @@
       <c r="M169" s="5" t="n"/>
       <c r="N169" s="5" t="n"/>
       <c r="O169" s="5" t="n"/>
-      <c r="P169" s="11" t="n"/>
-      <c r="Q169" s="5" t="n"/>
+      <c r="P169" s="5" t="n"/>
+      <c r="Q169" s="11" t="n"/>
       <c r="R169" s="5" t="n"/>
       <c r="S169" s="5" t="n"/>
       <c r="T169" s="5" t="n"/>
@@ -6471,8 +6649,8 @@
       <c r="M170" s="5" t="n"/>
       <c r="N170" s="5" t="n"/>
       <c r="O170" s="5" t="n"/>
-      <c r="P170" s="11" t="n"/>
-      <c r="Q170" s="5" t="n"/>
+      <c r="P170" s="5" t="n"/>
+      <c r="Q170" s="11" t="n"/>
       <c r="R170" s="5" t="n"/>
       <c r="S170" s="5" t="n"/>
       <c r="T170" s="5" t="n"/>
@@ -6498,8 +6676,8 @@
       <c r="M171" s="5" t="n"/>
       <c r="N171" s="5" t="n"/>
       <c r="O171" s="5" t="n"/>
-      <c r="P171" s="11" t="n"/>
-      <c r="Q171" s="5" t="n"/>
+      <c r="P171" s="5" t="n"/>
+      <c r="Q171" s="11" t="n"/>
       <c r="R171" s="5" t="n"/>
       <c r="S171" s="5" t="n"/>
       <c r="T171" s="5" t="n"/>
@@ -6525,8 +6703,8 @@
       <c r="M172" s="5" t="n"/>
       <c r="N172" s="5" t="n"/>
       <c r="O172" s="5" t="n"/>
-      <c r="P172" s="11" t="n"/>
-      <c r="Q172" s="5" t="n"/>
+      <c r="P172" s="5" t="n"/>
+      <c r="Q172" s="11" t="n"/>
       <c r="R172" s="5" t="n"/>
       <c r="S172" s="5" t="n"/>
       <c r="T172" s="5" t="n"/>
@@ -6552,8 +6730,8 @@
       <c r="M173" s="5" t="n"/>
       <c r="N173" s="5" t="n"/>
       <c r="O173" s="5" t="n"/>
-      <c r="P173" s="11" t="n"/>
-      <c r="Q173" s="5" t="n"/>
+      <c r="P173" s="5" t="n"/>
+      <c r="Q173" s="11" t="n"/>
       <c r="R173" s="5" t="n"/>
       <c r="S173" s="5" t="n"/>
       <c r="T173" s="5" t="n"/>
@@ -6579,8 +6757,8 @@
       <c r="M174" s="5" t="n"/>
       <c r="N174" s="5" t="n"/>
       <c r="O174" s="5" t="n"/>
-      <c r="P174" s="11" t="n"/>
-      <c r="Q174" s="5" t="n"/>
+      <c r="P174" s="5" t="n"/>
+      <c r="Q174" s="11" t="n"/>
       <c r="R174" s="5" t="n"/>
       <c r="S174" s="5" t="n"/>
       <c r="T174" s="5" t="n"/>
@@ -6606,8 +6784,8 @@
       <c r="M175" s="5" t="n"/>
       <c r="N175" s="5" t="n"/>
       <c r="O175" s="5" t="n"/>
-      <c r="P175" s="11" t="n"/>
-      <c r="Q175" s="5" t="n"/>
+      <c r="P175" s="5" t="n"/>
+      <c r="Q175" s="11" t="n"/>
       <c r="R175" s="5" t="n"/>
       <c r="S175" s="5" t="n"/>
       <c r="T175" s="5" t="n"/>
@@ -6633,8 +6811,8 @@
       <c r="M176" s="5" t="n"/>
       <c r="N176" s="5" t="n"/>
       <c r="O176" s="5" t="n"/>
-      <c r="P176" s="11" t="n"/>
-      <c r="Q176" s="5" t="n"/>
+      <c r="P176" s="5" t="n"/>
+      <c r="Q176" s="11" t="n"/>
       <c r="R176" s="5" t="n"/>
       <c r="S176" s="5" t="n"/>
       <c r="T176" s="5" t="n"/>
@@ -6660,8 +6838,8 @@
       <c r="M177" s="5" t="n"/>
       <c r="N177" s="5" t="n"/>
       <c r="O177" s="5" t="n"/>
-      <c r="P177" s="11" t="n"/>
-      <c r="Q177" s="5" t="n"/>
+      <c r="P177" s="5" t="n"/>
+      <c r="Q177" s="11" t="n"/>
       <c r="R177" s="5" t="n"/>
       <c r="S177" s="5" t="n"/>
       <c r="T177" s="5" t="n"/>
@@ -6687,8 +6865,8 @@
       <c r="M178" s="5" t="n"/>
       <c r="N178" s="5" t="n"/>
       <c r="O178" s="5" t="n"/>
-      <c r="P178" s="11" t="n"/>
-      <c r="Q178" s="5" t="n"/>
+      <c r="P178" s="5" t="n"/>
+      <c r="Q178" s="11" t="n"/>
       <c r="R178" s="5" t="n"/>
       <c r="S178" s="5" t="n"/>
       <c r="T178" s="5" t="n"/>
@@ -6714,8 +6892,8 @@
       <c r="M179" s="5" t="n"/>
       <c r="N179" s="5" t="n"/>
       <c r="O179" s="5" t="n"/>
-      <c r="P179" s="11" t="n"/>
-      <c r="Q179" s="5" t="n"/>
+      <c r="P179" s="5" t="n"/>
+      <c r="Q179" s="11" t="n"/>
       <c r="R179" s="5" t="n"/>
       <c r="S179" s="5" t="n"/>
       <c r="T179" s="5" t="n"/>
@@ -6741,8 +6919,8 @@
       <c r="M180" s="5" t="n"/>
       <c r="N180" s="5" t="n"/>
       <c r="O180" s="5" t="n"/>
-      <c r="P180" s="11" t="n"/>
-      <c r="Q180" s="5" t="n"/>
+      <c r="P180" s="5" t="n"/>
+      <c r="Q180" s="11" t="n"/>
       <c r="R180" s="5" t="n"/>
       <c r="S180" s="5" t="n"/>
       <c r="T180" s="5" t="n"/>
@@ -6768,8 +6946,8 @@
       <c r="M181" s="5" t="n"/>
       <c r="N181" s="5" t="n"/>
       <c r="O181" s="5" t="n"/>
-      <c r="P181" s="11" t="n"/>
-      <c r="Q181" s="5" t="n"/>
+      <c r="P181" s="5" t="n"/>
+      <c r="Q181" s="11" t="n"/>
       <c r="R181" s="5" t="n"/>
       <c r="S181" s="5" t="n"/>
       <c r="T181" s="5" t="n"/>
@@ -6795,8 +6973,8 @@
       <c r="M182" s="5" t="n"/>
       <c r="N182" s="5" t="n"/>
       <c r="O182" s="5" t="n"/>
-      <c r="P182" s="11" t="n"/>
-      <c r="Q182" s="5" t="n"/>
+      <c r="P182" s="5" t="n"/>
+      <c r="Q182" s="11" t="n"/>
       <c r="R182" s="5" t="n"/>
       <c r="S182" s="5" t="n"/>
       <c r="T182" s="5" t="n"/>
@@ -6822,8 +7000,8 @@
       <c r="M183" s="5" t="n"/>
       <c r="N183" s="5" t="n"/>
       <c r="O183" s="5" t="n"/>
-      <c r="P183" s="11" t="n"/>
-      <c r="Q183" s="5" t="n"/>
+      <c r="P183" s="5" t="n"/>
+      <c r="Q183" s="11" t="n"/>
       <c r="R183" s="5" t="n"/>
       <c r="S183" s="5" t="n"/>
       <c r="T183" s="5" t="n"/>
@@ -6849,8 +7027,8 @@
       <c r="M184" s="5" t="n"/>
       <c r="N184" s="5" t="n"/>
       <c r="O184" s="5" t="n"/>
-      <c r="P184" s="11" t="n"/>
-      <c r="Q184" s="5" t="n"/>
+      <c r="P184" s="5" t="n"/>
+      <c r="Q184" s="11" t="n"/>
       <c r="R184" s="5" t="n"/>
       <c r="S184" s="5" t="n"/>
       <c r="T184" s="5" t="n"/>
@@ -6876,8 +7054,8 @@
       <c r="M185" s="5" t="n"/>
       <c r="N185" s="5" t="n"/>
       <c r="O185" s="5" t="n"/>
-      <c r="P185" s="11" t="n"/>
-      <c r="Q185" s="5" t="n"/>
+      <c r="P185" s="5" t="n"/>
+      <c r="Q185" s="11" t="n"/>
       <c r="R185" s="5" t="n"/>
       <c r="S185" s="5" t="n"/>
       <c r="T185" s="5" t="n"/>
@@ -6903,8 +7081,8 @@
       <c r="M186" s="5" t="n"/>
       <c r="N186" s="5" t="n"/>
       <c r="O186" s="5" t="n"/>
-      <c r="P186" s="11" t="n"/>
-      <c r="Q186" s="5" t="n"/>
+      <c r="P186" s="5" t="n"/>
+      <c r="Q186" s="11" t="n"/>
       <c r="R186" s="5" t="n"/>
       <c r="S186" s="5" t="n"/>
       <c r="T186" s="5" t="n"/>
@@ -6930,8 +7108,8 @@
       <c r="M187" s="5" t="n"/>
       <c r="N187" s="5" t="n"/>
       <c r="O187" s="5" t="n"/>
-      <c r="P187" s="11" t="n"/>
-      <c r="Q187" s="5" t="n"/>
+      <c r="P187" s="5" t="n"/>
+      <c r="Q187" s="11" t="n"/>
       <c r="R187" s="5" t="n"/>
       <c r="S187" s="5" t="n"/>
       <c r="T187" s="5" t="n"/>
@@ -6957,8 +7135,8 @@
       <c r="M188" s="5" t="n"/>
       <c r="N188" s="5" t="n"/>
       <c r="O188" s="5" t="n"/>
-      <c r="P188" s="11" t="n"/>
-      <c r="Q188" s="5" t="n"/>
+      <c r="P188" s="5" t="n"/>
+      <c r="Q188" s="11" t="n"/>
       <c r="R188" s="5" t="n"/>
       <c r="S188" s="5" t="n"/>
       <c r="T188" s="5" t="n"/>
@@ -6984,8 +7162,8 @@
       <c r="M189" s="5" t="n"/>
       <c r="N189" s="5" t="n"/>
       <c r="O189" s="5" t="n"/>
-      <c r="P189" s="11" t="n"/>
-      <c r="Q189" s="5" t="n"/>
+      <c r="P189" s="5" t="n"/>
+      <c r="Q189" s="11" t="n"/>
       <c r="R189" s="5" t="n"/>
       <c r="S189" s="5" t="n"/>
       <c r="T189" s="5" t="n"/>
@@ -7011,8 +7189,8 @@
       <c r="M190" s="5" t="n"/>
       <c r="N190" s="5" t="n"/>
       <c r="O190" s="5" t="n"/>
-      <c r="P190" s="11" t="n"/>
-      <c r="Q190" s="5" t="n"/>
+      <c r="P190" s="5" t="n"/>
+      <c r="Q190" s="11" t="n"/>
       <c r="R190" s="5" t="n"/>
       <c r="S190" s="5" t="n"/>
       <c r="T190" s="5" t="n"/>
@@ -7038,8 +7216,8 @@
       <c r="M191" s="5" t="n"/>
       <c r="N191" s="5" t="n"/>
       <c r="O191" s="5" t="n"/>
-      <c r="P191" s="11" t="n"/>
-      <c r="Q191" s="5" t="n"/>
+      <c r="P191" s="5" t="n"/>
+      <c r="Q191" s="11" t="n"/>
       <c r="R191" s="5" t="n"/>
       <c r="S191" s="5" t="n"/>
       <c r="T191" s="5" t="n"/>
@@ -7065,8 +7243,8 @@
       <c r="M192" s="5" t="n"/>
       <c r="N192" s="5" t="n"/>
       <c r="O192" s="5" t="n"/>
-      <c r="P192" s="11" t="n"/>
-      <c r="Q192" s="5" t="n"/>
+      <c r="P192" s="5" t="n"/>
+      <c r="Q192" s="11" t="n"/>
       <c r="R192" s="5" t="n"/>
       <c r="S192" s="5" t="n"/>
       <c r="T192" s="5" t="n"/>
@@ -7092,8 +7270,8 @@
       <c r="M193" s="5" t="n"/>
       <c r="N193" s="5" t="n"/>
       <c r="O193" s="5" t="n"/>
-      <c r="P193" s="11" t="n"/>
-      <c r="Q193" s="5" t="n"/>
+      <c r="P193" s="5" t="n"/>
+      <c r="Q193" s="11" t="n"/>
       <c r="R193" s="5" t="n"/>
       <c r="S193" s="5" t="n"/>
       <c r="T193" s="5" t="n"/>
@@ -7119,8 +7297,8 @@
       <c r="M194" s="5" t="n"/>
       <c r="N194" s="5" t="n"/>
       <c r="O194" s="5" t="n"/>
-      <c r="P194" s="11" t="n"/>
-      <c r="Q194" s="5" t="n"/>
+      <c r="P194" s="5" t="n"/>
+      <c r="Q194" s="11" t="n"/>
       <c r="R194" s="5" t="n"/>
       <c r="S194" s="5" t="n"/>
       <c r="T194" s="5" t="n"/>
@@ -7146,8 +7324,8 @@
       <c r="M195" s="5" t="n"/>
       <c r="N195" s="5" t="n"/>
       <c r="O195" s="5" t="n"/>
-      <c r="P195" s="11" t="n"/>
-      <c r="Q195" s="5" t="n"/>
+      <c r="P195" s="5" t="n"/>
+      <c r="Q195" s="11" t="n"/>
       <c r="R195" s="5" t="n"/>
       <c r="S195" s="5" t="n"/>
       <c r="T195" s="5" t="n"/>
@@ -7173,8 +7351,8 @@
       <c r="M196" s="5" t="n"/>
       <c r="N196" s="5" t="n"/>
       <c r="O196" s="5" t="n"/>
-      <c r="P196" s="11" t="n"/>
-      <c r="Q196" s="5" t="n"/>
+      <c r="P196" s="5" t="n"/>
+      <c r="Q196" s="11" t="n"/>
       <c r="R196" s="5" t="n"/>
       <c r="S196" s="5" t="n"/>
       <c r="T196" s="5" t="n"/>
@@ -7200,8 +7378,8 @@
       <c r="M197" s="5" t="n"/>
       <c r="N197" s="5" t="n"/>
       <c r="O197" s="5" t="n"/>
-      <c r="P197" s="11" t="n"/>
-      <c r="Q197" s="5" t="n"/>
+      <c r="P197" s="5" t="n"/>
+      <c r="Q197" s="11" t="n"/>
       <c r="R197" s="5" t="n"/>
       <c r="S197" s="5" t="n"/>
       <c r="T197" s="5" t="n"/>
@@ -7227,8 +7405,8 @@
       <c r="M198" s="5" t="n"/>
       <c r="N198" s="5" t="n"/>
       <c r="O198" s="5" t="n"/>
-      <c r="P198" s="11" t="n"/>
-      <c r="Q198" s="5" t="n"/>
+      <c r="P198" s="5" t="n"/>
+      <c r="Q198" s="11" t="n"/>
       <c r="R198" s="5" t="n"/>
       <c r="S198" s="5" t="n"/>
       <c r="T198" s="5" t="n"/>
@@ -7254,8 +7432,8 @@
       <c r="M199" s="5" t="n"/>
       <c r="N199" s="5" t="n"/>
       <c r="O199" s="5" t="n"/>
-      <c r="P199" s="11" t="n"/>
-      <c r="Q199" s="5" t="n"/>
+      <c r="P199" s="5" t="n"/>
+      <c r="Q199" s="11" t="n"/>
       <c r="R199" s="5" t="n"/>
       <c r="S199" s="5" t="n"/>
       <c r="T199" s="5" t="n"/>
@@ -7281,8 +7459,8 @@
       <c r="M200" s="5" t="n"/>
       <c r="N200" s="5" t="n"/>
       <c r="O200" s="5" t="n"/>
-      <c r="P200" s="11" t="n"/>
-      <c r="Q200" s="5" t="n"/>
+      <c r="P200" s="5" t="n"/>
+      <c r="Q200" s="11" t="n"/>
       <c r="R200" s="5" t="n"/>
       <c r="S200" s="5" t="n"/>
       <c r="T200" s="5" t="n"/>
@@ -7308,8 +7486,8 @@
       <c r="M201" s="5" t="n"/>
       <c r="N201" s="5" t="n"/>
       <c r="O201" s="5" t="n"/>
-      <c r="P201" s="11" t="n"/>
-      <c r="Q201" s="5" t="n"/>
+      <c r="P201" s="5" t="n"/>
+      <c r="Q201" s="11" t="n"/>
       <c r="R201" s="5" t="n"/>
       <c r="S201" s="5" t="n"/>
       <c r="T201" s="5" t="n"/>
@@ -7335,8 +7513,8 @@
       <c r="M202" s="5" t="n"/>
       <c r="N202" s="5" t="n"/>
       <c r="O202" s="5" t="n"/>
-      <c r="P202" s="11" t="n"/>
-      <c r="Q202" s="5" t="n"/>
+      <c r="P202" s="5" t="n"/>
+      <c r="Q202" s="11" t="n"/>
       <c r="R202" s="5" t="n"/>
       <c r="S202" s="5" t="n"/>
       <c r="T202" s="5" t="n"/>
@@ -7362,8 +7540,8 @@
       <c r="M203" s="5" t="n"/>
       <c r="N203" s="5" t="n"/>
       <c r="O203" s="5" t="n"/>
-      <c r="P203" s="11" t="n"/>
-      <c r="Q203" s="5" t="n"/>
+      <c r="P203" s="5" t="n"/>
+      <c r="Q203" s="11" t="n"/>
       <c r="R203" s="5" t="n"/>
       <c r="S203" s="5" t="n"/>
       <c r="T203" s="5" t="n"/>
@@ -7389,8 +7567,8 @@
       <c r="M204" s="5" t="n"/>
       <c r="N204" s="5" t="n"/>
       <c r="O204" s="5" t="n"/>
-      <c r="P204" s="11" t="n"/>
-      <c r="Q204" s="5" t="n"/>
+      <c r="P204" s="5" t="n"/>
+      <c r="Q204" s="11" t="n"/>
       <c r="R204" s="5" t="n"/>
       <c r="S204" s="5" t="n"/>
       <c r="T204" s="5" t="n"/>
@@ -7416,8 +7594,8 @@
       <c r="M205" s="5" t="n"/>
       <c r="N205" s="5" t="n"/>
       <c r="O205" s="5" t="n"/>
-      <c r="P205" s="11" t="n"/>
-      <c r="Q205" s="5" t="n"/>
+      <c r="P205" s="5" t="n"/>
+      <c r="Q205" s="11" t="n"/>
       <c r="R205" s="5" t="n"/>
       <c r="S205" s="5" t="n"/>
       <c r="T205" s="5" t="n"/>
@@ -7443,8 +7621,8 @@
       <c r="M206" s="5" t="n"/>
       <c r="N206" s="5" t="n"/>
       <c r="O206" s="5" t="n"/>
-      <c r="P206" s="11" t="n"/>
-      <c r="Q206" s="5" t="n"/>
+      <c r="P206" s="5" t="n"/>
+      <c r="Q206" s="11" t="n"/>
       <c r="R206" s="5" t="n"/>
       <c r="S206" s="5" t="n"/>
       <c r="T206" s="5" t="n"/>
@@ -7470,8 +7648,8 @@
       <c r="M207" s="5" t="n"/>
       <c r="N207" s="5" t="n"/>
       <c r="O207" s="5" t="n"/>
-      <c r="P207" s="11" t="n"/>
-      <c r="Q207" s="5" t="n"/>
+      <c r="P207" s="5" t="n"/>
+      <c r="Q207" s="11" t="n"/>
       <c r="R207" s="5" t="n"/>
       <c r="S207" s="5" t="n"/>
       <c r="T207" s="5" t="n"/>
@@ -7497,8 +7675,8 @@
       <c r="M208" s="5" t="n"/>
       <c r="N208" s="5" t="n"/>
       <c r="O208" s="5" t="n"/>
-      <c r="P208" s="11" t="n"/>
-      <c r="Q208" s="5" t="n"/>
+      <c r="P208" s="5" t="n"/>
+      <c r="Q208" s="11" t="n"/>
       <c r="R208" s="5" t="n"/>
       <c r="S208" s="5" t="n"/>
       <c r="T208" s="5" t="n"/>
@@ -7524,8 +7702,8 @@
       <c r="M209" s="5" t="n"/>
       <c r="N209" s="5" t="n"/>
       <c r="O209" s="5" t="n"/>
-      <c r="P209" s="11" t="n"/>
-      <c r="Q209" s="5" t="n"/>
+      <c r="P209" s="5" t="n"/>
+      <c r="Q209" s="11" t="n"/>
       <c r="R209" s="5" t="n"/>
       <c r="S209" s="5" t="n"/>
       <c r="T209" s="5" t="n"/>
@@ -7551,8 +7729,8 @@
       <c r="M210" s="5" t="n"/>
       <c r="N210" s="5" t="n"/>
       <c r="O210" s="5" t="n"/>
-      <c r="P210" s="11" t="n"/>
-      <c r="Q210" s="5" t="n"/>
+      <c r="P210" s="5" t="n"/>
+      <c r="Q210" s="11" t="n"/>
       <c r="R210" s="5" t="n"/>
       <c r="S210" s="5" t="n"/>
       <c r="T210" s="5" t="n"/>
@@ -7578,8 +7756,8 @@
       <c r="M211" s="5" t="n"/>
       <c r="N211" s="5" t="n"/>
       <c r="O211" s="5" t="n"/>
-      <c r="P211" s="11" t="n"/>
-      <c r="Q211" s="5" t="n"/>
+      <c r="P211" s="5" t="n"/>
+      <c r="Q211" s="11" t="n"/>
       <c r="R211" s="5" t="n"/>
       <c r="S211" s="5" t="n"/>
       <c r="T211" s="5" t="n"/>
@@ -7605,8 +7783,8 @@
       <c r="M212" s="5" t="n"/>
       <c r="N212" s="5" t="n"/>
       <c r="O212" s="5" t="n"/>
-      <c r="P212" s="11" t="n"/>
-      <c r="Q212" s="5" t="n"/>
+      <c r="P212" s="5" t="n"/>
+      <c r="Q212" s="11" t="n"/>
       <c r="R212" s="5" t="n"/>
       <c r="S212" s="5" t="n"/>
       <c r="T212" s="5" t="n"/>
@@ -7632,8 +7810,8 @@
       <c r="M213" s="5" t="n"/>
       <c r="N213" s="5" t="n"/>
       <c r="O213" s="5" t="n"/>
-      <c r="P213" s="11" t="n"/>
-      <c r="Q213" s="5" t="n"/>
+      <c r="P213" s="5" t="n"/>
+      <c r="Q213" s="11" t="n"/>
       <c r="R213" s="5" t="n"/>
       <c r="S213" s="5" t="n"/>
       <c r="T213" s="5" t="n"/>
@@ -7659,8 +7837,8 @@
       <c r="M214" s="5" t="n"/>
       <c r="N214" s="5" t="n"/>
       <c r="O214" s="5" t="n"/>
-      <c r="P214" s="11" t="n"/>
-      <c r="Q214" s="5" t="n"/>
+      <c r="P214" s="5" t="n"/>
+      <c r="Q214" s="11" t="n"/>
       <c r="R214" s="5" t="n"/>
       <c r="S214" s="5" t="n"/>
       <c r="T214" s="5" t="n"/>
@@ -7686,8 +7864,8 @@
       <c r="M215" s="5" t="n"/>
       <c r="N215" s="5" t="n"/>
       <c r="O215" s="5" t="n"/>
-      <c r="P215" s="11" t="n"/>
-      <c r="Q215" s="5" t="n"/>
+      <c r="P215" s="5" t="n"/>
+      <c r="Q215" s="11" t="n"/>
       <c r="R215" s="5" t="n"/>
       <c r="S215" s="5" t="n"/>
       <c r="T215" s="5" t="n"/>
@@ -7713,8 +7891,8 @@
       <c r="M216" s="5" t="n"/>
       <c r="N216" s="5" t="n"/>
       <c r="O216" s="5" t="n"/>
-      <c r="P216" s="11" t="n"/>
-      <c r="Q216" s="5" t="n"/>
+      <c r="P216" s="5" t="n"/>
+      <c r="Q216" s="11" t="n"/>
       <c r="R216" s="5" t="n"/>
       <c r="S216" s="5" t="n"/>
       <c r="T216" s="5" t="n"/>
@@ -7740,8 +7918,8 @@
       <c r="M217" s="5" t="n"/>
       <c r="N217" s="5" t="n"/>
       <c r="O217" s="5" t="n"/>
-      <c r="P217" s="11" t="n"/>
-      <c r="Q217" s="5" t="n"/>
+      <c r="P217" s="5" t="n"/>
+      <c r="Q217" s="11" t="n"/>
       <c r="R217" s="5" t="n"/>
       <c r="S217" s="5" t="n"/>
       <c r="T217" s="5" t="n"/>
@@ -7767,8 +7945,8 @@
       <c r="M218" s="5" t="n"/>
       <c r="N218" s="5" t="n"/>
       <c r="O218" s="5" t="n"/>
-      <c r="P218" s="11" t="n"/>
-      <c r="Q218" s="5" t="n"/>
+      <c r="P218" s="5" t="n"/>
+      <c r="Q218" s="11" t="n"/>
       <c r="R218" s="5" t="n"/>
       <c r="S218" s="5" t="n"/>
       <c r="T218" s="5" t="n"/>
@@ -7794,8 +7972,8 @@
       <c r="M219" s="5" t="n"/>
       <c r="N219" s="5" t="n"/>
       <c r="O219" s="5" t="n"/>
-      <c r="P219" s="11" t="n"/>
-      <c r="Q219" s="5" t="n"/>
+      <c r="P219" s="5" t="n"/>
+      <c r="Q219" s="11" t="n"/>
       <c r="R219" s="5" t="n"/>
       <c r="S219" s="5" t="n"/>
       <c r="T219" s="5" t="n"/>
@@ -7821,8 +7999,8 @@
       <c r="M220" s="5" t="n"/>
       <c r="N220" s="5" t="n"/>
       <c r="O220" s="5" t="n"/>
-      <c r="P220" s="11" t="n"/>
-      <c r="Q220" s="5" t="n"/>
+      <c r="P220" s="5" t="n"/>
+      <c r="Q220" s="11" t="n"/>
       <c r="R220" s="5" t="n"/>
       <c r="S220" s="5" t="n"/>
       <c r="T220" s="5" t="n"/>
@@ -7848,8 +8026,8 @@
       <c r="M221" s="5" t="n"/>
       <c r="N221" s="5" t="n"/>
       <c r="O221" s="5" t="n"/>
-      <c r="P221" s="11" t="n"/>
-      <c r="Q221" s="5" t="n"/>
+      <c r="P221" s="5" t="n"/>
+      <c r="Q221" s="11" t="n"/>
       <c r="R221" s="5" t="n"/>
       <c r="S221" s="5" t="n"/>
       <c r="T221" s="5" t="n"/>
@@ -7875,8 +8053,8 @@
       <c r="M222" s="5" t="n"/>
       <c r="N222" s="5" t="n"/>
       <c r="O222" s="5" t="n"/>
-      <c r="P222" s="11" t="n"/>
-      <c r="Q222" s="5" t="n"/>
+      <c r="P222" s="5" t="n"/>
+      <c r="Q222" s="11" t="n"/>
       <c r="R222" s="5" t="n"/>
       <c r="S222" s="5" t="n"/>
       <c r="T222" s="5" t="n"/>
@@ -7902,8 +8080,8 @@
       <c r="M223" s="5" t="n"/>
       <c r="N223" s="5" t="n"/>
       <c r="O223" s="5" t="n"/>
-      <c r="P223" s="11" t="n"/>
-      <c r="Q223" s="5" t="n"/>
+      <c r="P223" s="5" t="n"/>
+      <c r="Q223" s="11" t="n"/>
       <c r="R223" s="5" t="n"/>
       <c r="S223" s="5" t="n"/>
       <c r="T223" s="5" t="n"/>
@@ -7929,8 +8107,8 @@
       <c r="M224" s="5" t="n"/>
       <c r="N224" s="5" t="n"/>
       <c r="O224" s="5" t="n"/>
-      <c r="P224" s="11" t="n"/>
-      <c r="Q224" s="5" t="n"/>
+      <c r="P224" s="5" t="n"/>
+      <c r="Q224" s="11" t="n"/>
       <c r="R224" s="5" t="n"/>
       <c r="S224" s="5" t="n"/>
       <c r="T224" s="5" t="n"/>
@@ -7956,8 +8134,8 @@
       <c r="M225" s="5" t="n"/>
       <c r="N225" s="5" t="n"/>
       <c r="O225" s="5" t="n"/>
-      <c r="P225" s="11" t="n"/>
-      <c r="Q225" s="5" t="n"/>
+      <c r="P225" s="5" t="n"/>
+      <c r="Q225" s="11" t="n"/>
       <c r="R225" s="5" t="n"/>
       <c r="S225" s="5" t="n"/>
       <c r="T225" s="5" t="n"/>
@@ -7983,8 +8161,8 @@
       <c r="M226" s="5" t="n"/>
       <c r="N226" s="5" t="n"/>
       <c r="O226" s="5" t="n"/>
-      <c r="P226" s="11" t="n"/>
-      <c r="Q226" s="5" t="n"/>
+      <c r="P226" s="5" t="n"/>
+      <c r="Q226" s="11" t="n"/>
       <c r="R226" s="5" t="n"/>
       <c r="S226" s="5" t="n"/>
       <c r="T226" s="5" t="n"/>
@@ -8010,8 +8188,8 @@
       <c r="M227" s="5" t="n"/>
       <c r="N227" s="5" t="n"/>
       <c r="O227" s="5" t="n"/>
-      <c r="P227" s="11" t="n"/>
-      <c r="Q227" s="5" t="n"/>
+      <c r="P227" s="5" t="n"/>
+      <c r="Q227" s="11" t="n"/>
       <c r="R227" s="5" t="n"/>
       <c r="S227" s="5" t="n"/>
       <c r="T227" s="5" t="n"/>
@@ -8037,8 +8215,8 @@
       <c r="M228" s="5" t="n"/>
       <c r="N228" s="5" t="n"/>
       <c r="O228" s="5" t="n"/>
-      <c r="P228" s="11" t="n"/>
-      <c r="Q228" s="5" t="n"/>
+      <c r="P228" s="5" t="n"/>
+      <c r="Q228" s="11" t="n"/>
       <c r="R228" s="5" t="n"/>
       <c r="S228" s="5" t="n"/>
       <c r="T228" s="5" t="n"/>
@@ -8064,8 +8242,8 @@
       <c r="M229" s="5" t="n"/>
       <c r="N229" s="5" t="n"/>
       <c r="O229" s="5" t="n"/>
-      <c r="P229" s="11" t="n"/>
-      <c r="Q229" s="5" t="n"/>
+      <c r="P229" s="5" t="n"/>
+      <c r="Q229" s="11" t="n"/>
       <c r="R229" s="5" t="n"/>
       <c r="S229" s="5" t="n"/>
       <c r="T229" s="5" t="n"/>
@@ -8091,8 +8269,8 @@
       <c r="M230" s="5" t="n"/>
       <c r="N230" s="5" t="n"/>
       <c r="O230" s="5" t="n"/>
-      <c r="P230" s="11" t="n"/>
-      <c r="Q230" s="5" t="n"/>
+      <c r="P230" s="5" t="n"/>
+      <c r="Q230" s="11" t="n"/>
       <c r="R230" s="5" t="n"/>
       <c r="S230" s="5" t="n"/>
       <c r="T230" s="5" t="n"/>
@@ -8118,8 +8296,8 @@
       <c r="M231" s="5" t="n"/>
       <c r="N231" s="5" t="n"/>
       <c r="O231" s="5" t="n"/>
-      <c r="P231" s="11" t="n"/>
-      <c r="Q231" s="5" t="n"/>
+      <c r="P231" s="5" t="n"/>
+      <c r="Q231" s="11" t="n"/>
       <c r="R231" s="5" t="n"/>
       <c r="S231" s="5" t="n"/>
       <c r="T231" s="5" t="n"/>
@@ -8145,8 +8323,8 @@
       <c r="M232" s="5" t="n"/>
       <c r="N232" s="5" t="n"/>
       <c r="O232" s="5" t="n"/>
-      <c r="P232" s="11" t="n"/>
-      <c r="Q232" s="5" t="n"/>
+      <c r="P232" s="5" t="n"/>
+      <c r="Q232" s="11" t="n"/>
       <c r="R232" s="5" t="n"/>
       <c r="S232" s="5" t="n"/>
       <c r="T232" s="5" t="n"/>
@@ -8172,8 +8350,8 @@
       <c r="M233" s="5" t="n"/>
       <c r="N233" s="5" t="n"/>
       <c r="O233" s="5" t="n"/>
-      <c r="P233" s="11" t="n"/>
-      <c r="Q233" s="5" t="n"/>
+      <c r="P233" s="5" t="n"/>
+      <c r="Q233" s="11" t="n"/>
       <c r="R233" s="5" t="n"/>
       <c r="S233" s="5" t="n"/>
       <c r="T233" s="5" t="n"/>
@@ -8199,8 +8377,8 @@
       <c r="M234" s="5" t="n"/>
       <c r="N234" s="5" t="n"/>
       <c r="O234" s="5" t="n"/>
-      <c r="P234" s="11" t="n"/>
-      <c r="Q234" s="5" t="n"/>
+      <c r="P234" s="5" t="n"/>
+      <c r="Q234" s="11" t="n"/>
       <c r="R234" s="5" t="n"/>
       <c r="S234" s="5" t="n"/>
       <c r="T234" s="5" t="n"/>
@@ -8226,8 +8404,8 @@
       <c r="M235" s="5" t="n"/>
       <c r="N235" s="5" t="n"/>
       <c r="O235" s="5" t="n"/>
-      <c r="P235" s="11" t="n"/>
-      <c r="Q235" s="5" t="n"/>
+      <c r="P235" s="5" t="n"/>
+      <c r="Q235" s="11" t="n"/>
       <c r="R235" s="5" t="n"/>
       <c r="S235" s="5" t="n"/>
       <c r="T235" s="5" t="n"/>
@@ -8253,8 +8431,8 @@
       <c r="M236" s="5" t="n"/>
       <c r="N236" s="5" t="n"/>
       <c r="O236" s="5" t="n"/>
-      <c r="P236" s="11" t="n"/>
-      <c r="Q236" s="5" t="n"/>
+      <c r="P236" s="5" t="n"/>
+      <c r="Q236" s="11" t="n"/>
       <c r="R236" s="5" t="n"/>
       <c r="S236" s="5" t="n"/>
       <c r="T236" s="5" t="n"/>
@@ -8280,8 +8458,8 @@
       <c r="M237" s="5" t="n"/>
       <c r="N237" s="5" t="n"/>
       <c r="O237" s="5" t="n"/>
-      <c r="P237" s="11" t="n"/>
-      <c r="Q237" s="5" t="n"/>
+      <c r="P237" s="5" t="n"/>
+      <c r="Q237" s="11" t="n"/>
       <c r="R237" s="5" t="n"/>
       <c r="S237" s="5" t="n"/>
       <c r="T237" s="5" t="n"/>
@@ -8307,8 +8485,8 @@
       <c r="M238" s="5" t="n"/>
       <c r="N238" s="5" t="n"/>
       <c r="O238" s="5" t="n"/>
-      <c r="P238" s="11" t="n"/>
-      <c r="Q238" s="5" t="n"/>
+      <c r="P238" s="5" t="n"/>
+      <c r="Q238" s="11" t="n"/>
       <c r="R238" s="5" t="n"/>
       <c r="S238" s="5" t="n"/>
       <c r="T238" s="5" t="n"/>
@@ -8334,8 +8512,8 @@
       <c r="M239" s="5" t="n"/>
       <c r="N239" s="5" t="n"/>
       <c r="O239" s="5" t="n"/>
-      <c r="P239" s="11" t="n"/>
-      <c r="Q239" s="5" t="n"/>
+      <c r="P239" s="5" t="n"/>
+      <c r="Q239" s="11" t="n"/>
       <c r="R239" s="5" t="n"/>
       <c r="S239" s="5" t="n"/>
       <c r="T239" s="5" t="n"/>
@@ -8361,8 +8539,8 @@
       <c r="M240" s="5" t="n"/>
       <c r="N240" s="5" t="n"/>
       <c r="O240" s="5" t="n"/>
-      <c r="P240" s="11" t="n"/>
-      <c r="Q240" s="5" t="n"/>
+      <c r="P240" s="5" t="n"/>
+      <c r="Q240" s="11" t="n"/>
       <c r="R240" s="5" t="n"/>
       <c r="S240" s="5" t="n"/>
       <c r="T240" s="5" t="n"/>
@@ -8388,8 +8566,8 @@
       <c r="M241" s="5" t="n"/>
       <c r="N241" s="5" t="n"/>
       <c r="O241" s="5" t="n"/>
-      <c r="P241" s="11" t="n"/>
-      <c r="Q241" s="5" t="n"/>
+      <c r="P241" s="5" t="n"/>
+      <c r="Q241" s="11" t="n"/>
       <c r="R241" s="5" t="n"/>
       <c r="S241" s="5" t="n"/>
       <c r="T241" s="5" t="n"/>
@@ -8415,8 +8593,8 @@
       <c r="M242" s="5" t="n"/>
       <c r="N242" s="5" t="n"/>
       <c r="O242" s="5" t="n"/>
-      <c r="P242" s="11" t="n"/>
-      <c r="Q242" s="5" t="n"/>
+      <c r="P242" s="5" t="n"/>
+      <c r="Q242" s="11" t="n"/>
       <c r="R242" s="5" t="n"/>
       <c r="S242" s="5" t="n"/>
       <c r="T242" s="5" t="n"/>
@@ -8442,8 +8620,8 @@
       <c r="M243" s="5" t="n"/>
       <c r="N243" s="5" t="n"/>
       <c r="O243" s="5" t="n"/>
-      <c r="P243" s="11" t="n"/>
-      <c r="Q243" s="5" t="n"/>
+      <c r="P243" s="5" t="n"/>
+      <c r="Q243" s="11" t="n"/>
       <c r="R243" s="5" t="n"/>
       <c r="S243" s="5" t="n"/>
       <c r="T243" s="5" t="n"/>
@@ -8469,8 +8647,8 @@
       <c r="M244" s="5" t="n"/>
       <c r="N244" s="5" t="n"/>
       <c r="O244" s="5" t="n"/>
-      <c r="P244" s="11" t="n"/>
-      <c r="Q244" s="5" t="n"/>
+      <c r="P244" s="5" t="n"/>
+      <c r="Q244" s="11" t="n"/>
       <c r="R244" s="5" t="n"/>
       <c r="S244" s="5" t="n"/>
       <c r="T244" s="5" t="n"/>
@@ -8496,8 +8674,8 @@
       <c r="M245" s="5" t="n"/>
       <c r="N245" s="5" t="n"/>
       <c r="O245" s="5" t="n"/>
-      <c r="P245" s="11" t="n"/>
-      <c r="Q245" s="5" t="n"/>
+      <c r="P245" s="5" t="n"/>
+      <c r="Q245" s="11" t="n"/>
       <c r="R245" s="5" t="n"/>
       <c r="S245" s="5" t="n"/>
       <c r="T245" s="5" t="n"/>
@@ -8523,8 +8701,8 @@
       <c r="M246" s="5" t="n"/>
       <c r="N246" s="5" t="n"/>
       <c r="O246" s="5" t="n"/>
-      <c r="P246" s="11" t="n"/>
-      <c r="Q246" s="5" t="n"/>
+      <c r="P246" s="5" t="n"/>
+      <c r="Q246" s="11" t="n"/>
       <c r="R246" s="5" t="n"/>
       <c r="S246" s="5" t="n"/>
       <c r="T246" s="5" t="n"/>
@@ -8550,8 +8728,8 @@
       <c r="M247" s="5" t="n"/>
       <c r="N247" s="5" t="n"/>
       <c r="O247" s="5" t="n"/>
-      <c r="P247" s="11" t="n"/>
-      <c r="Q247" s="5" t="n"/>
+      <c r="P247" s="5" t="n"/>
+      <c r="Q247" s="11" t="n"/>
       <c r="R247" s="5" t="n"/>
       <c r="S247" s="5" t="n"/>
       <c r="T247" s="5" t="n"/>
@@ -8577,8 +8755,8 @@
       <c r="M248" s="5" t="n"/>
       <c r="N248" s="5" t="n"/>
       <c r="O248" s="5" t="n"/>
-      <c r="P248" s="11" t="n"/>
-      <c r="Q248" s="5" t="n"/>
+      <c r="P248" s="5" t="n"/>
+      <c r="Q248" s="11" t="n"/>
       <c r="R248" s="5" t="n"/>
       <c r="S248" s="5" t="n"/>
       <c r="T248" s="5" t="n"/>
@@ -8604,8 +8782,8 @@
       <c r="M249" s="5" t="n"/>
       <c r="N249" s="5" t="n"/>
       <c r="O249" s="5" t="n"/>
-      <c r="P249" s="11" t="n"/>
-      <c r="Q249" s="5" t="n"/>
+      <c r="P249" s="5" t="n"/>
+      <c r="Q249" s="11" t="n"/>
       <c r="R249" s="5" t="n"/>
       <c r="S249" s="5" t="n"/>
       <c r="T249" s="5" t="n"/>
@@ -8631,8 +8809,8 @@
       <c r="M250" s="5" t="n"/>
       <c r="N250" s="5" t="n"/>
       <c r="O250" s="5" t="n"/>
-      <c r="P250" s="11" t="n"/>
-      <c r="Q250" s="5" t="n"/>
+      <c r="P250" s="5" t="n"/>
+      <c r="Q250" s="11" t="n"/>
       <c r="R250" s="5" t="n"/>
       <c r="S250" s="5" t="n"/>
       <c r="T250" s="5" t="n"/>
@@ -8658,8 +8836,8 @@
       <c r="M251" s="5" t="n"/>
       <c r="N251" s="5" t="n"/>
       <c r="O251" s="5" t="n"/>
-      <c r="P251" s="11" t="n"/>
-      <c r="Q251" s="5" t="n"/>
+      <c r="P251" s="5" t="n"/>
+      <c r="Q251" s="11" t="n"/>
       <c r="R251" s="5" t="n"/>
       <c r="S251" s="5" t="n"/>
       <c r="T251" s="5" t="n"/>
@@ -8685,8 +8863,8 @@
       <c r="M252" s="5" t="n"/>
       <c r="N252" s="5" t="n"/>
       <c r="O252" s="5" t="n"/>
-      <c r="P252" s="11" t="n"/>
-      <c r="Q252" s="5" t="n"/>
+      <c r="P252" s="5" t="n"/>
+      <c r="Q252" s="11" t="n"/>
       <c r="R252" s="5" t="n"/>
       <c r="S252" s="5" t="n"/>
       <c r="T252" s="5" t="n"/>
@@ -8712,8 +8890,8 @@
       <c r="M253" s="5" t="n"/>
       <c r="N253" s="5" t="n"/>
       <c r="O253" s="5" t="n"/>
-      <c r="P253" s="11" t="n"/>
-      <c r="Q253" s="5" t="n"/>
+      <c r="P253" s="5" t="n"/>
+      <c r="Q253" s="11" t="n"/>
       <c r="R253" s="5" t="n"/>
       <c r="S253" s="5" t="n"/>
       <c r="T253" s="5" t="n"/>
@@ -8739,8 +8917,8 @@
       <c r="M254" s="5" t="n"/>
       <c r="N254" s="5" t="n"/>
       <c r="O254" s="5" t="n"/>
-      <c r="P254" s="11" t="n"/>
-      <c r="Q254" s="5" t="n"/>
+      <c r="P254" s="5" t="n"/>
+      <c r="Q254" s="11" t="n"/>
       <c r="R254" s="5" t="n"/>
       <c r="S254" s="5" t="n"/>
       <c r="T254" s="5" t="n"/>
@@ -8766,8 +8944,8 @@
       <c r="M255" s="5" t="n"/>
       <c r="N255" s="5" t="n"/>
       <c r="O255" s="5" t="n"/>
-      <c r="P255" s="11" t="n"/>
-      <c r="Q255" s="5" t="n"/>
+      <c r="P255" s="5" t="n"/>
+      <c r="Q255" s="11" t="n"/>
       <c r="R255" s="5" t="n"/>
       <c r="S255" s="5" t="n"/>
       <c r="T255" s="5" t="n"/>
@@ -8793,8 +8971,8 @@
       <c r="M256" s="5" t="n"/>
       <c r="N256" s="5" t="n"/>
       <c r="O256" s="5" t="n"/>
-      <c r="P256" s="11" t="n"/>
-      <c r="Q256" s="5" t="n"/>
+      <c r="P256" s="5" t="n"/>
+      <c r="Q256" s="11" t="n"/>
       <c r="R256" s="5" t="n"/>
       <c r="S256" s="5" t="n"/>
       <c r="T256" s="5" t="n"/>
@@ -8820,8 +8998,8 @@
       <c r="M257" s="5" t="n"/>
       <c r="N257" s="5" t="n"/>
       <c r="O257" s="5" t="n"/>
-      <c r="P257" s="11" t="n"/>
-      <c r="Q257" s="5" t="n"/>
+      <c r="P257" s="5" t="n"/>
+      <c r="Q257" s="11" t="n"/>
       <c r="R257" s="5" t="n"/>
       <c r="S257" s="5" t="n"/>
       <c r="T257" s="5" t="n"/>
@@ -8847,8 +9025,8 @@
       <c r="M258" s="5" t="n"/>
       <c r="N258" s="5" t="n"/>
       <c r="O258" s="5" t="n"/>
-      <c r="P258" s="11" t="n"/>
-      <c r="Q258" s="5" t="n"/>
+      <c r="P258" s="5" t="n"/>
+      <c r="Q258" s="11" t="n"/>
       <c r="R258" s="5" t="n"/>
       <c r="S258" s="5" t="n"/>
       <c r="T258" s="5" t="n"/>
@@ -8874,8 +9052,8 @@
       <c r="M259" s="5" t="n"/>
       <c r="N259" s="5" t="n"/>
       <c r="O259" s="5" t="n"/>
-      <c r="P259" s="11" t="n"/>
-      <c r="Q259" s="5" t="n"/>
+      <c r="P259" s="5" t="n"/>
+      <c r="Q259" s="11" t="n"/>
       <c r="R259" s="5" t="n"/>
       <c r="S259" s="5" t="n"/>
       <c r="T259" s="5" t="n"/>
@@ -8901,8 +9079,8 @@
       <c r="M260" s="5" t="n"/>
       <c r="N260" s="5" t="n"/>
       <c r="O260" s="5" t="n"/>
-      <c r="P260" s="11" t="n"/>
-      <c r="Q260" s="5" t="n"/>
+      <c r="P260" s="5" t="n"/>
+      <c r="Q260" s="11" t="n"/>
       <c r="R260" s="5" t="n"/>
       <c r="S260" s="5" t="n"/>
       <c r="T260" s="5" t="n"/>
@@ -8928,8 +9106,8 @@
       <c r="M261" s="5" t="n"/>
       <c r="N261" s="5" t="n"/>
       <c r="O261" s="5" t="n"/>
-      <c r="P261" s="11" t="n"/>
-      <c r="Q261" s="5" t="n"/>
+      <c r="P261" s="5" t="n"/>
+      <c r="Q261" s="11" t="n"/>
       <c r="R261" s="5" t="n"/>
       <c r="S261" s="5" t="n"/>
       <c r="T261" s="5" t="n"/>
@@ -8955,8 +9133,8 @@
       <c r="M262" s="5" t="n"/>
       <c r="N262" s="5" t="n"/>
       <c r="O262" s="5" t="n"/>
-      <c r="P262" s="11" t="n"/>
-      <c r="Q262" s="5" t="n"/>
+      <c r="P262" s="5" t="n"/>
+      <c r="Q262" s="11" t="n"/>
       <c r="R262" s="5" t="n"/>
       <c r="S262" s="5" t="n"/>
       <c r="T262" s="5" t="n"/>
@@ -8982,8 +9160,8 @@
       <c r="M263" s="5" t="n"/>
       <c r="N263" s="5" t="n"/>
       <c r="O263" s="5" t="n"/>
-      <c r="P263" s="11" t="n"/>
-      <c r="Q263" s="5" t="n"/>
+      <c r="P263" s="5" t="n"/>
+      <c r="Q263" s="11" t="n"/>
       <c r="R263" s="5" t="n"/>
       <c r="S263" s="5" t="n"/>
       <c r="T263" s="5" t="n"/>
@@ -9009,8 +9187,8 @@
       <c r="M264" s="5" t="n"/>
       <c r="N264" s="5" t="n"/>
       <c r="O264" s="5" t="n"/>
-      <c r="P264" s="11" t="n"/>
-      <c r="Q264" s="5" t="n"/>
+      <c r="P264" s="5" t="n"/>
+      <c r="Q264" s="11" t="n"/>
       <c r="R264" s="5" t="n"/>
       <c r="S264" s="5" t="n"/>
       <c r="T264" s="5" t="n"/>
@@ -9036,8 +9214,8 @@
       <c r="M265" s="5" t="n"/>
       <c r="N265" s="5" t="n"/>
       <c r="O265" s="5" t="n"/>
-      <c r="P265" s="11" t="n"/>
-      <c r="Q265" s="5" t="n"/>
+      <c r="P265" s="5" t="n"/>
+      <c r="Q265" s="11" t="n"/>
       <c r="R265" s="5" t="n"/>
       <c r="S265" s="5" t="n"/>
       <c r="T265" s="5" t="n"/>
@@ -9063,8 +9241,8 @@
       <c r="M266" s="5" t="n"/>
       <c r="N266" s="5" t="n"/>
       <c r="O266" s="5" t="n"/>
-      <c r="P266" s="11" t="n"/>
-      <c r="Q266" s="5" t="n"/>
+      <c r="P266" s="5" t="n"/>
+      <c r="Q266" s="11" t="n"/>
       <c r="R266" s="5" t="n"/>
       <c r="S266" s="5" t="n"/>
       <c r="T266" s="5" t="n"/>
@@ -9090,8 +9268,8 @@
       <c r="M267" s="5" t="n"/>
       <c r="N267" s="5" t="n"/>
       <c r="O267" s="5" t="n"/>
-      <c r="P267" s="11" t="n"/>
-      <c r="Q267" s="5" t="n"/>
+      <c r="P267" s="5" t="n"/>
+      <c r="Q267" s="11" t="n"/>
       <c r="R267" s="5" t="n"/>
       <c r="S267" s="5" t="n"/>
       <c r="T267" s="5" t="n"/>
@@ -9117,8 +9295,8 @@
       <c r="M268" s="5" t="n"/>
       <c r="N268" s="5" t="n"/>
       <c r="O268" s="5" t="n"/>
-      <c r="P268" s="11" t="n"/>
-      <c r="Q268" s="5" t="n"/>
+      <c r="P268" s="5" t="n"/>
+      <c r="Q268" s="11" t="n"/>
       <c r="R268" s="5" t="n"/>
       <c r="S268" s="5" t="n"/>
       <c r="T268" s="5" t="n"/>
@@ -9144,8 +9322,8 @@
       <c r="M269" s="5" t="n"/>
       <c r="N269" s="5" t="n"/>
       <c r="O269" s="5" t="n"/>
-      <c r="P269" s="11" t="n"/>
-      <c r="Q269" s="5" t="n"/>
+      <c r="P269" s="5" t="n"/>
+      <c r="Q269" s="11" t="n"/>
       <c r="R269" s="5" t="n"/>
       <c r="S269" s="5" t="n"/>
       <c r="T269" s="5" t="n"/>
@@ -9171,8 +9349,8 @@
       <c r="M270" s="5" t="n"/>
       <c r="N270" s="5" t="n"/>
       <c r="O270" s="5" t="n"/>
-      <c r="P270" s="11" t="n"/>
-      <c r="Q270" s="5" t="n"/>
+      <c r="P270" s="5" t="n"/>
+      <c r="Q270" s="11" t="n"/>
       <c r="R270" s="5" t="n"/>
       <c r="S270" s="5" t="n"/>
       <c r="T270" s="5" t="n"/>
@@ -9198,8 +9376,8 @@
       <c r="M271" s="5" t="n"/>
       <c r="N271" s="5" t="n"/>
       <c r="O271" s="5" t="n"/>
-      <c r="P271" s="11" t="n"/>
-      <c r="Q271" s="5" t="n"/>
+      <c r="P271" s="5" t="n"/>
+      <c r="Q271" s="11" t="n"/>
       <c r="R271" s="5" t="n"/>
       <c r="S271" s="5" t="n"/>
       <c r="T271" s="5" t="n"/>
@@ -9225,8 +9403,8 @@
       <c r="M272" s="5" t="n"/>
       <c r="N272" s="5" t="n"/>
       <c r="O272" s="5" t="n"/>
-      <c r="P272" s="11" t="n"/>
-      <c r="Q272" s="5" t="n"/>
+      <c r="P272" s="5" t="n"/>
+      <c r="Q272" s="11" t="n"/>
       <c r="R272" s="5" t="n"/>
       <c r="S272" s="5" t="n"/>
       <c r="T272" s="5" t="n"/>
@@ -9252,8 +9430,8 @@
       <c r="M273" s="5" t="n"/>
       <c r="N273" s="5" t="n"/>
       <c r="O273" s="5" t="n"/>
-      <c r="P273" s="11" t="n"/>
-      <c r="Q273" s="5" t="n"/>
+      <c r="P273" s="5" t="n"/>
+      <c r="Q273" s="11" t="n"/>
       <c r="R273" s="5" t="n"/>
       <c r="S273" s="5" t="n"/>
       <c r="T273" s="5" t="n"/>
@@ -9279,8 +9457,8 @@
       <c r="M274" s="5" t="n"/>
       <c r="N274" s="5" t="n"/>
       <c r="O274" s="5" t="n"/>
-      <c r="P274" s="11" t="n"/>
-      <c r="Q274" s="5" t="n"/>
+      <c r="P274" s="5" t="n"/>
+      <c r="Q274" s="11" t="n"/>
       <c r="R274" s="5" t="n"/>
       <c r="S274" s="5" t="n"/>
       <c r="T274" s="5" t="n"/>
@@ -9306,8 +9484,8 @@
       <c r="M275" s="5" t="n"/>
       <c r="N275" s="5" t="n"/>
       <c r="O275" s="5" t="n"/>
-      <c r="P275" s="11" t="n"/>
-      <c r="Q275" s="5" t="n"/>
+      <c r="P275" s="5" t="n"/>
+      <c r="Q275" s="11" t="n"/>
       <c r="R275" s="5" t="n"/>
       <c r="S275" s="5" t="n"/>
       <c r="T275" s="5" t="n"/>
@@ -9333,8 +9511,8 @@
       <c r="M276" s="5" t="n"/>
       <c r="N276" s="5" t="n"/>
       <c r="O276" s="5" t="n"/>
-      <c r="P276" s="11" t="n"/>
-      <c r="Q276" s="5" t="n"/>
+      <c r="P276" s="5" t="n"/>
+      <c r="Q276" s="11" t="n"/>
       <c r="R276" s="5" t="n"/>
       <c r="S276" s="5" t="n"/>
       <c r="T276" s="5" t="n"/>
@@ -9360,8 +9538,8 @@
       <c r="M277" s="5" t="n"/>
       <c r="N277" s="5" t="n"/>
       <c r="O277" s="5" t="n"/>
-      <c r="P277" s="11" t="n"/>
-      <c r="Q277" s="5" t="n"/>
+      <c r="P277" s="5" t="n"/>
+      <c r="Q277" s="11" t="n"/>
       <c r="R277" s="5" t="n"/>
       <c r="S277" s="5" t="n"/>
       <c r="T277" s="5" t="n"/>
@@ -9387,8 +9565,8 @@
       <c r="M278" s="5" t="n"/>
       <c r="N278" s="5" t="n"/>
       <c r="O278" s="5" t="n"/>
-      <c r="P278" s="11" t="n"/>
-      <c r="Q278" s="5" t="n"/>
+      <c r="P278" s="5" t="n"/>
+      <c r="Q278" s="11" t="n"/>
       <c r="R278" s="5" t="n"/>
       <c r="S278" s="5" t="n"/>
       <c r="T278" s="5" t="n"/>
@@ -9414,8 +9592,8 @@
       <c r="M279" s="5" t="n"/>
       <c r="N279" s="5" t="n"/>
       <c r="O279" s="5" t="n"/>
-      <c r="P279" s="11" t="n"/>
-      <c r="Q279" s="5" t="n"/>
+      <c r="P279" s="5" t="n"/>
+      <c r="Q279" s="11" t="n"/>
       <c r="R279" s="5" t="n"/>
       <c r="S279" s="5" t="n"/>
       <c r="T279" s="5" t="n"/>
@@ -9441,8 +9619,8 @@
       <c r="M280" s="5" t="n"/>
       <c r="N280" s="5" t="n"/>
       <c r="O280" s="5" t="n"/>
-      <c r="P280" s="11" t="n"/>
-      <c r="Q280" s="5" t="n"/>
+      <c r="P280" s="5" t="n"/>
+      <c r="Q280" s="11" t="n"/>
       <c r="R280" s="5" t="n"/>
       <c r="S280" s="5" t="n"/>
       <c r="T280" s="5" t="n"/>
@@ -9468,8 +9646,8 @@
       <c r="M281" s="5" t="n"/>
       <c r="N281" s="5" t="n"/>
       <c r="O281" s="5" t="n"/>
-      <c r="P281" s="11" t="n"/>
-      <c r="Q281" s="5" t="n"/>
+      <c r="P281" s="5" t="n"/>
+      <c r="Q281" s="11" t="n"/>
       <c r="R281" s="5" t="n"/>
       <c r="S281" s="5" t="n"/>
       <c r="T281" s="5" t="n"/>
@@ -9495,8 +9673,8 @@
       <c r="M282" s="5" t="n"/>
       <c r="N282" s="5" t="n"/>
       <c r="O282" s="5" t="n"/>
-      <c r="P282" s="11" t="n"/>
-      <c r="Q282" s="5" t="n"/>
+      <c r="P282" s="5" t="n"/>
+      <c r="Q282" s="11" t="n"/>
       <c r="R282" s="5" t="n"/>
       <c r="S282" s="5" t="n"/>
       <c r="T282" s="5" t="n"/>
@@ -9522,8 +9700,8 @@
       <c r="M283" s="5" t="n"/>
       <c r="N283" s="5" t="n"/>
       <c r="O283" s="5" t="n"/>
-      <c r="P283" s="11" t="n"/>
-      <c r="Q283" s="5" t="n"/>
+      <c r="P283" s="5" t="n"/>
+      <c r="Q283" s="11" t="n"/>
       <c r="R283" s="5" t="n"/>
       <c r="S283" s="5" t="n"/>
       <c r="T283" s="5" t="n"/>
@@ -9549,8 +9727,8 @@
       <c r="M284" s="5" t="n"/>
       <c r="N284" s="5" t="n"/>
       <c r="O284" s="5" t="n"/>
-      <c r="P284" s="11" t="n"/>
-      <c r="Q284" s="5" t="n"/>
+      <c r="P284" s="5" t="n"/>
+      <c r="Q284" s="11" t="n"/>
       <c r="R284" s="5" t="n"/>
       <c r="S284" s="5" t="n"/>
       <c r="T284" s="5" t="n"/>
@@ -9576,8 +9754,8 @@
       <c r="M285" s="5" t="n"/>
       <c r="N285" s="5" t="n"/>
       <c r="O285" s="5" t="n"/>
-      <c r="P285" s="11" t="n"/>
-      <c r="Q285" s="5" t="n"/>
+      <c r="P285" s="5" t="n"/>
+      <c r="Q285" s="11" t="n"/>
       <c r="R285" s="5" t="n"/>
       <c r="S285" s="5" t="n"/>
       <c r="T285" s="5" t="n"/>
@@ -9603,8 +9781,8 @@
       <c r="M286" s="5" t="n"/>
       <c r="N286" s="5" t="n"/>
       <c r="O286" s="5" t="n"/>
-      <c r="P286" s="11" t="n"/>
-      <c r="Q286" s="5" t="n"/>
+      <c r="P286" s="5" t="n"/>
+      <c r="Q286" s="11" t="n"/>
       <c r="R286" s="5" t="n"/>
       <c r="S286" s="5" t="n"/>
       <c r="T286" s="5" t="n"/>
@@ -9630,8 +9808,8 @@
       <c r="M287" s="5" t="n"/>
       <c r="N287" s="5" t="n"/>
       <c r="O287" s="5" t="n"/>
-      <c r="P287" s="11" t="n"/>
-      <c r="Q287" s="5" t="n"/>
+      <c r="P287" s="5" t="n"/>
+      <c r="Q287" s="11" t="n"/>
       <c r="R287" s="5" t="n"/>
       <c r="S287" s="5" t="n"/>
       <c r="T287" s="5" t="n"/>
@@ -9657,8 +9835,8 @@
       <c r="M288" s="5" t="n"/>
       <c r="N288" s="5" t="n"/>
       <c r="O288" s="5" t="n"/>
-      <c r="P288" s="11" t="n"/>
-      <c r="Q288" s="5" t="n"/>
+      <c r="P288" s="5" t="n"/>
+      <c r="Q288" s="11" t="n"/>
       <c r="R288" s="5" t="n"/>
       <c r="S288" s="5" t="n"/>
       <c r="T288" s="5" t="n"/>
@@ -9684,8 +9862,8 @@
       <c r="M289" s="5" t="n"/>
       <c r="N289" s="5" t="n"/>
       <c r="O289" s="5" t="n"/>
-      <c r="P289" s="11" t="n"/>
-      <c r="Q289" s="5" t="n"/>
+      <c r="P289" s="5" t="n"/>
+      <c r="Q289" s="11" t="n"/>
       <c r="R289" s="5" t="n"/>
       <c r="S289" s="5" t="n"/>
       <c r="T289" s="5" t="n"/>
@@ -9711,8 +9889,8 @@
       <c r="M290" s="5" t="n"/>
       <c r="N290" s="5" t="n"/>
       <c r="O290" s="5" t="n"/>
-      <c r="P290" s="11" t="n"/>
-      <c r="Q290" s="5" t="n"/>
+      <c r="P290" s="5" t="n"/>
+      <c r="Q290" s="11" t="n"/>
       <c r="R290" s="5" t="n"/>
       <c r="S290" s="5" t="n"/>
       <c r="T290" s="5" t="n"/>
@@ -9738,8 +9916,8 @@
       <c r="M291" s="5" t="n"/>
       <c r="N291" s="5" t="n"/>
       <c r="O291" s="5" t="n"/>
-      <c r="P291" s="11" t="n"/>
-      <c r="Q291" s="5" t="n"/>
+      <c r="P291" s="5" t="n"/>
+      <c r="Q291" s="11" t="n"/>
       <c r="R291" s="5" t="n"/>
       <c r="S291" s="5" t="n"/>
       <c r="T291" s="5" t="n"/>
@@ -9765,8 +9943,8 @@
       <c r="M292" s="5" t="n"/>
       <c r="N292" s="5" t="n"/>
       <c r="O292" s="5" t="n"/>
-      <c r="P292" s="11" t="n"/>
-      <c r="Q292" s="5" t="n"/>
+      <c r="P292" s="5" t="n"/>
+      <c r="Q292" s="11" t="n"/>
       <c r="R292" s="5" t="n"/>
       <c r="S292" s="5" t="n"/>
       <c r="T292" s="5" t="n"/>
@@ -9792,8 +9970,8 @@
       <c r="M293" s="5" t="n"/>
       <c r="N293" s="5" t="n"/>
       <c r="O293" s="5" t="n"/>
-      <c r="P293" s="11" t="n"/>
-      <c r="Q293" s="5" t="n"/>
+      <c r="P293" s="5" t="n"/>
+      <c r="Q293" s="11" t="n"/>
       <c r="R293" s="5" t="n"/>
       <c r="S293" s="5" t="n"/>
       <c r="T293" s="5" t="n"/>
@@ -9819,8 +9997,8 @@
       <c r="M294" s="5" t="n"/>
       <c r="N294" s="5" t="n"/>
       <c r="O294" s="5" t="n"/>
-      <c r="P294" s="11" t="n"/>
-      <c r="Q294" s="5" t="n"/>
+      <c r="P294" s="5" t="n"/>
+      <c r="Q294" s="11" t="n"/>
       <c r="R294" s="5" t="n"/>
       <c r="S294" s="5" t="n"/>
       <c r="T294" s="5" t="n"/>
@@ -9846,8 +10024,8 @@
       <c r="M295" s="5" t="n"/>
       <c r="N295" s="5" t="n"/>
       <c r="O295" s="5" t="n"/>
-      <c r="P295" s="11" t="n"/>
-      <c r="Q295" s="5" t="n"/>
+      <c r="P295" s="5" t="n"/>
+      <c r="Q295" s="11" t="n"/>
       <c r="R295" s="5" t="n"/>
       <c r="S295" s="5" t="n"/>
       <c r="T295" s="5" t="n"/>
@@ -9873,8 +10051,8 @@
       <c r="M296" s="5" t="n"/>
       <c r="N296" s="5" t="n"/>
       <c r="O296" s="5" t="n"/>
-      <c r="P296" s="11" t="n"/>
-      <c r="Q296" s="5" t="n"/>
+      <c r="P296" s="5" t="n"/>
+      <c r="Q296" s="11" t="n"/>
       <c r="R296" s="5" t="n"/>
       <c r="S296" s="5" t="n"/>
       <c r="T296" s="5" t="n"/>
@@ -9900,8 +10078,8 @@
       <c r="M297" s="5" t="n"/>
       <c r="N297" s="5" t="n"/>
       <c r="O297" s="5" t="n"/>
-      <c r="P297" s="11" t="n"/>
-      <c r="Q297" s="5" t="n"/>
+      <c r="P297" s="5" t="n"/>
+      <c r="Q297" s="11" t="n"/>
       <c r="R297" s="5" t="n"/>
       <c r="S297" s="5" t="n"/>
       <c r="T297" s="5" t="n"/>
@@ -9927,8 +10105,8 @@
       <c r="M298" s="5" t="n"/>
       <c r="N298" s="5" t="n"/>
       <c r="O298" s="5" t="n"/>
-      <c r="P298" s="11" t="n"/>
-      <c r="Q298" s="5" t="n"/>
+      <c r="P298" s="5" t="n"/>
+      <c r="Q298" s="11" t="n"/>
       <c r="R298" s="5" t="n"/>
       <c r="S298" s="5" t="n"/>
       <c r="T298" s="5" t="n"/>
@@ -9954,8 +10132,8 @@
       <c r="M299" s="5" t="n"/>
       <c r="N299" s="5" t="n"/>
       <c r="O299" s="5" t="n"/>
-      <c r="P299" s="11" t="n"/>
-      <c r="Q299" s="5" t="n"/>
+      <c r="P299" s="5" t="n"/>
+      <c r="Q299" s="11" t="n"/>
       <c r="R299" s="5" t="n"/>
       <c r="S299" s="5" t="n"/>
       <c r="T299" s="5" t="n"/>
@@ -9981,8 +10159,8 @@
       <c r="M300" s="5" t="n"/>
       <c r="N300" s="5" t="n"/>
       <c r="O300" s="5" t="n"/>
-      <c r="P300" s="11" t="n"/>
-      <c r="Q300" s="5" t="n"/>
+      <c r="P300" s="5" t="n"/>
+      <c r="Q300" s="11" t="n"/>
       <c r="R300" s="5" t="n"/>
       <c r="S300" s="5" t="n"/>
       <c r="T300" s="5" t="n"/>
@@ -10008,8 +10186,8 @@
       <c r="M301" s="5" t="n"/>
       <c r="N301" s="5" t="n"/>
       <c r="O301" s="5" t="n"/>
-      <c r="P301" s="11" t="n"/>
-      <c r="Q301" s="5" t="n"/>
+      <c r="P301" s="5" t="n"/>
+      <c r="Q301" s="11" t="n"/>
       <c r="R301" s="5" t="n"/>
       <c r="S301" s="5" t="n"/>
       <c r="T301" s="5" t="n"/>
@@ -10035,8 +10213,8 @@
       <c r="M302" s="5" t="n"/>
       <c r="N302" s="5" t="n"/>
       <c r="O302" s="5" t="n"/>
-      <c r="P302" s="11" t="n"/>
-      <c r="Q302" s="5" t="n"/>
+      <c r="P302" s="5" t="n"/>
+      <c r="Q302" s="11" t="n"/>
       <c r="R302" s="5" t="n"/>
       <c r="S302" s="5" t="n"/>
       <c r="T302" s="5" t="n"/>
@@ -10062,8 +10240,8 @@
       <c r="M303" s="5" t="n"/>
       <c r="N303" s="5" t="n"/>
       <c r="O303" s="5" t="n"/>
-      <c r="P303" s="11" t="n"/>
-      <c r="Q303" s="5" t="n"/>
+      <c r="P303" s="5" t="n"/>
+      <c r="Q303" s="11" t="n"/>
       <c r="R303" s="5" t="n"/>
       <c r="S303" s="5" t="n"/>
       <c r="T303" s="5" t="n"/>
@@ -10089,8 +10267,8 @@
       <c r="M304" s="5" t="n"/>
       <c r="N304" s="5" t="n"/>
       <c r="O304" s="5" t="n"/>
-      <c r="P304" s="11" t="n"/>
-      <c r="Q304" s="5" t="n"/>
+      <c r="P304" s="5" t="n"/>
+      <c r="Q304" s="11" t="n"/>
       <c r="R304" s="5" t="n"/>
       <c r="S304" s="5" t="n"/>
       <c r="T304" s="5" t="n"/>
@@ -10116,8 +10294,8 @@
       <c r="M305" s="5" t="n"/>
       <c r="N305" s="5" t="n"/>
       <c r="O305" s="5" t="n"/>
-      <c r="P305" s="11" t="n"/>
-      <c r="Q305" s="5" t="n"/>
+      <c r="P305" s="5" t="n"/>
+      <c r="Q305" s="11" t="n"/>
       <c r="R305" s="5" t="n"/>
       <c r="S305" s="5" t="n"/>
       <c r="T305" s="5" t="n"/>
@@ -10143,8 +10321,8 @@
       <c r="M306" s="5" t="n"/>
       <c r="N306" s="5" t="n"/>
       <c r="O306" s="5" t="n"/>
-      <c r="P306" s="11" t="n"/>
-      <c r="Q306" s="5" t="n"/>
+      <c r="P306" s="5" t="n"/>
+      <c r="Q306" s="11" t="n"/>
       <c r="R306" s="5" t="n"/>
       <c r="S306" s="5" t="n"/>
       <c r="T306" s="5" t="n"/>
@@ -10170,8 +10348,8 @@
       <c r="M307" s="5" t="n"/>
       <c r="N307" s="5" t="n"/>
       <c r="O307" s="5" t="n"/>
-      <c r="P307" s="11" t="n"/>
-      <c r="Q307" s="5" t="n"/>
+      <c r="P307" s="5" t="n"/>
+      <c r="Q307" s="11" t="n"/>
       <c r="R307" s="5" t="n"/>
       <c r="S307" s="5" t="n"/>
       <c r="T307" s="5" t="n"/>
@@ -10197,8 +10375,8 @@
       <c r="M308" s="5" t="n"/>
       <c r="N308" s="5" t="n"/>
       <c r="O308" s="5" t="n"/>
-      <c r="P308" s="11" t="n"/>
-      <c r="Q308" s="5" t="n"/>
+      <c r="P308" s="5" t="n"/>
+      <c r="Q308" s="11" t="n"/>
       <c r="R308" s="5" t="n"/>
       <c r="S308" s="5" t="n"/>
       <c r="T308" s="5" t="n"/>
@@ -10224,8 +10402,8 @@
       <c r="M309" s="5" t="n"/>
       <c r="N309" s="5" t="n"/>
       <c r="O309" s="5" t="n"/>
-      <c r="P309" s="11" t="n"/>
-      <c r="Q309" s="5" t="n"/>
+      <c r="P309" s="5" t="n"/>
+      <c r="Q309" s="11" t="n"/>
       <c r="R309" s="5" t="n"/>
       <c r="S309" s="5" t="n"/>
       <c r="T309" s="5" t="n"/>
@@ -10251,8 +10429,8 @@
       <c r="M310" s="5" t="n"/>
       <c r="N310" s="5" t="n"/>
       <c r="O310" s="5" t="n"/>
-      <c r="P310" s="11" t="n"/>
-      <c r="Q310" s="5" t="n"/>
+      <c r="P310" s="5" t="n"/>
+      <c r="Q310" s="11" t="n"/>
       <c r="R310" s="5" t="n"/>
       <c r="S310" s="5" t="n"/>
       <c r="T310" s="5" t="n"/>
@@ -10278,8 +10456,8 @@
       <c r="M311" s="5" t="n"/>
       <c r="N311" s="5" t="n"/>
       <c r="O311" s="5" t="n"/>
-      <c r="P311" s="11" t="n"/>
-      <c r="Q311" s="5" t="n"/>
+      <c r="P311" s="5" t="n"/>
+      <c r="Q311" s="11" t="n"/>
       <c r="R311" s="5" t="n"/>
       <c r="S311" s="5" t="n"/>
       <c r="T311" s="5" t="n"/>
@@ -10305,8 +10483,8 @@
       <c r="M312" s="5" t="n"/>
       <c r="N312" s="5" t="n"/>
       <c r="O312" s="5" t="n"/>
-      <c r="P312" s="11" t="n"/>
-      <c r="Q312" s="5" t="n"/>
+      <c r="P312" s="5" t="n"/>
+      <c r="Q312" s="11" t="n"/>
       <c r="R312" s="5" t="n"/>
       <c r="S312" s="5" t="n"/>
       <c r="T312" s="5" t="n"/>
@@ -10332,8 +10510,8 @@
       <c r="M313" s="5" t="n"/>
       <c r="N313" s="5" t="n"/>
       <c r="O313" s="5" t="n"/>
-      <c r="P313" s="11" t="n"/>
-      <c r="Q313" s="5" t="n"/>
+      <c r="P313" s="5" t="n"/>
+      <c r="Q313" s="11" t="n"/>
       <c r="R313" s="5" t="n"/>
       <c r="S313" s="5" t="n"/>
       <c r="T313" s="5" t="n"/>
@@ -10359,8 +10537,8 @@
       <c r="M314" s="5" t="n"/>
       <c r="N314" s="5" t="n"/>
       <c r="O314" s="5" t="n"/>
-      <c r="P314" s="11" t="n"/>
-      <c r="Q314" s="5" t="n"/>
+      <c r="P314" s="5" t="n"/>
+      <c r="Q314" s="11" t="n"/>
       <c r="R314" s="5" t="n"/>
       <c r="S314" s="5" t="n"/>
       <c r="T314" s="5" t="n"/>
@@ -10386,8 +10564,8 @@
       <c r="M315" s="5" t="n"/>
       <c r="N315" s="5" t="n"/>
       <c r="O315" s="5" t="n"/>
-      <c r="P315" s="11" t="n"/>
-      <c r="Q315" s="5" t="n"/>
+      <c r="P315" s="5" t="n"/>
+      <c r="Q315" s="11" t="n"/>
       <c r="R315" s="5" t="n"/>
       <c r="S315" s="5" t="n"/>
       <c r="T315" s="5" t="n"/>
@@ -10413,8 +10591,8 @@
       <c r="M316" s="5" t="n"/>
       <c r="N316" s="5" t="n"/>
       <c r="O316" s="5" t="n"/>
-      <c r="P316" s="11" t="n"/>
-      <c r="Q316" s="5" t="n"/>
+      <c r="P316" s="5" t="n"/>
+      <c r="Q316" s="11" t="n"/>
       <c r="R316" s="5" t="n"/>
       <c r="S316" s="5" t="n"/>
       <c r="T316" s="5" t="n"/>
@@ -10440,8 +10618,8 @@
       <c r="M317" s="5" t="n"/>
       <c r="N317" s="5" t="n"/>
       <c r="O317" s="5" t="n"/>
-      <c r="P317" s="11" t="n"/>
-      <c r="Q317" s="5" t="n"/>
+      <c r="P317" s="5" t="n"/>
+      <c r="Q317" s="11" t="n"/>
       <c r="R317" s="5" t="n"/>
       <c r="S317" s="5" t="n"/>
       <c r="T317" s="5" t="n"/>
@@ -10467,8 +10645,8 @@
       <c r="M318" s="5" t="n"/>
       <c r="N318" s="5" t="n"/>
       <c r="O318" s="5" t="n"/>
-      <c r="P318" s="11" t="n"/>
-      <c r="Q318" s="5" t="n"/>
+      <c r="P318" s="5" t="n"/>
+      <c r="Q318" s="11" t="n"/>
       <c r="R318" s="5" t="n"/>
       <c r="S318" s="5" t="n"/>
       <c r="T318" s="5" t="n"/>
@@ -10494,8 +10672,8 @@
       <c r="M319" s="5" t="n"/>
       <c r="N319" s="5" t="n"/>
       <c r="O319" s="5" t="n"/>
-      <c r="P319" s="11" t="n"/>
-      <c r="Q319" s="5" t="n"/>
+      <c r="P319" s="5" t="n"/>
+      <c r="Q319" s="11" t="n"/>
       <c r="R319" s="5" t="n"/>
       <c r="S319" s="5" t="n"/>
       <c r="T319" s="5" t="n"/>
@@ -10521,8 +10699,8 @@
       <c r="M320" s="5" t="n"/>
       <c r="N320" s="5" t="n"/>
       <c r="O320" s="5" t="n"/>
-      <c r="P320" s="11" t="n"/>
-      <c r="Q320" s="5" t="n"/>
+      <c r="P320" s="5" t="n"/>
+      <c r="Q320" s="11" t="n"/>
       <c r="R320" s="5" t="n"/>
       <c r="S320" s="5" t="n"/>
       <c r="T320" s="5" t="n"/>
@@ -10548,8 +10726,8 @@
       <c r="M321" s="5" t="n"/>
       <c r="N321" s="5" t="n"/>
       <c r="O321" s="5" t="n"/>
-      <c r="P321" s="11" t="n"/>
-      <c r="Q321" s="5" t="n"/>
+      <c r="P321" s="5" t="n"/>
+      <c r="Q321" s="11" t="n"/>
       <c r="R321" s="5" t="n"/>
       <c r="S321" s="5" t="n"/>
       <c r="T321" s="5" t="n"/>
@@ -10575,8 +10753,8 @@
       <c r="M322" s="5" t="n"/>
       <c r="N322" s="5" t="n"/>
       <c r="O322" s="5" t="n"/>
-      <c r="P322" s="11" t="n"/>
-      <c r="Q322" s="5" t="n"/>
+      <c r="P322" s="5" t="n"/>
+      <c r="Q322" s="11" t="n"/>
       <c r="R322" s="5" t="n"/>
       <c r="S322" s="5" t="n"/>
       <c r="T322" s="5" t="n"/>
@@ -10602,8 +10780,8 @@
       <c r="M323" s="5" t="n"/>
       <c r="N323" s="5" t="n"/>
       <c r="O323" s="5" t="n"/>
-      <c r="P323" s="11" t="n"/>
-      <c r="Q323" s="5" t="n"/>
+      <c r="P323" s="5" t="n"/>
+      <c r="Q323" s="11" t="n"/>
       <c r="R323" s="5" t="n"/>
       <c r="S323" s="5" t="n"/>
       <c r="T323" s="5" t="n"/>
@@ -10629,8 +10807,8 @@
       <c r="M324" s="5" t="n"/>
       <c r="N324" s="5" t="n"/>
       <c r="O324" s="5" t="n"/>
-      <c r="P324" s="11" t="n"/>
-      <c r="Q324" s="5" t="n"/>
+      <c r="P324" s="5" t="n"/>
+      <c r="Q324" s="11" t="n"/>
       <c r="R324" s="5" t="n"/>
       <c r="S324" s="5" t="n"/>
       <c r="T324" s="5" t="n"/>
@@ -10656,8 +10834,8 @@
       <c r="M325" s="5" t="n"/>
       <c r="N325" s="5" t="n"/>
       <c r="O325" s="5" t="n"/>
-      <c r="P325" s="11" t="n"/>
-      <c r="Q325" s="5" t="n"/>
+      <c r="P325" s="5" t="n"/>
+      <c r="Q325" s="11" t="n"/>
       <c r="R325" s="5" t="n"/>
       <c r="S325" s="5" t="n"/>
       <c r="T325" s="5" t="n"/>
@@ -10683,8 +10861,8 @@
       <c r="M326" s="5" t="n"/>
       <c r="N326" s="5" t="n"/>
       <c r="O326" s="5" t="n"/>
-      <c r="P326" s="11" t="n"/>
-      <c r="Q326" s="5" t="n"/>
+      <c r="P326" s="5" t="n"/>
+      <c r="Q326" s="11" t="n"/>
       <c r="R326" s="5" t="n"/>
       <c r="S326" s="5" t="n"/>
       <c r="T326" s="5" t="n"/>
@@ -10710,8 +10888,8 @@
       <c r="M327" s="5" t="n"/>
       <c r="N327" s="5" t="n"/>
       <c r="O327" s="5" t="n"/>
-      <c r="P327" s="11" t="n"/>
-      <c r="Q327" s="5" t="n"/>
+      <c r="P327" s="5" t="n"/>
+      <c r="Q327" s="11" t="n"/>
       <c r="R327" s="5" t="n"/>
       <c r="S327" s="5" t="n"/>
       <c r="T327" s="5" t="n"/>
@@ -10737,8 +10915,8 @@
       <c r="M328" s="5" t="n"/>
       <c r="N328" s="5" t="n"/>
       <c r="O328" s="5" t="n"/>
-      <c r="P328" s="11" t="n"/>
-      <c r="Q328" s="5" t="n"/>
+      <c r="P328" s="5" t="n"/>
+      <c r="Q328" s="11" t="n"/>
       <c r="R328" s="5" t="n"/>
       <c r="S328" s="5" t="n"/>
       <c r="T328" s="5" t="n"/>
@@ -10764,8 +10942,8 @@
       <c r="M329" s="5" t="n"/>
       <c r="N329" s="5" t="n"/>
       <c r="O329" s="5" t="n"/>
-      <c r="P329" s="11" t="n"/>
-      <c r="Q329" s="5" t="n"/>
+      <c r="P329" s="5" t="n"/>
+      <c r="Q329" s="11" t="n"/>
       <c r="R329" s="5" t="n"/>
       <c r="S329" s="5" t="n"/>
       <c r="T329" s="5" t="n"/>
@@ -10791,8 +10969,8 @@
       <c r="M330" s="5" t="n"/>
       <c r="N330" s="5" t="n"/>
       <c r="O330" s="5" t="n"/>
-      <c r="P330" s="11" t="n"/>
-      <c r="Q330" s="5" t="n"/>
+      <c r="P330" s="5" t="n"/>
+      <c r="Q330" s="11" t="n"/>
       <c r="R330" s="5" t="n"/>
       <c r="S330" s="5" t="n"/>
       <c r="T330" s="5" t="n"/>
@@ -10818,8 +10996,8 @@
       <c r="M331" s="5" t="n"/>
       <c r="N331" s="5" t="n"/>
       <c r="O331" s="5" t="n"/>
-      <c r="P331" s="11" t="n"/>
-      <c r="Q331" s="5" t="n"/>
+      <c r="P331" s="5" t="n"/>
+      <c r="Q331" s="11" t="n"/>
       <c r="R331" s="5" t="n"/>
       <c r="S331" s="5" t="n"/>
       <c r="T331" s="5" t="n"/>
@@ -10845,8 +11023,8 @@
       <c r="M332" s="5" t="n"/>
       <c r="N332" s="5" t="n"/>
       <c r="O332" s="5" t="n"/>
-      <c r="P332" s="11" t="n"/>
-      <c r="Q332" s="5" t="n"/>
+      <c r="P332" s="5" t="n"/>
+      <c r="Q332" s="11" t="n"/>
       <c r="R332" s="5" t="n"/>
       <c r="S332" s="5" t="n"/>
       <c r="T332" s="5" t="n"/>
@@ -10872,8 +11050,8 @@
       <c r="M333" s="5" t="n"/>
       <c r="N333" s="5" t="n"/>
       <c r="O333" s="5" t="n"/>
-      <c r="P333" s="11" t="n"/>
-      <c r="Q333" s="5" t="n"/>
+      <c r="P333" s="5" t="n"/>
+      <c r="Q333" s="11" t="n"/>
       <c r="R333" s="5" t="n"/>
       <c r="S333" s="5" t="n"/>
       <c r="T333" s="5" t="n"/>
@@ -10899,8 +11077,8 @@
       <c r="M334" s="5" t="n"/>
       <c r="N334" s="5" t="n"/>
       <c r="O334" s="5" t="n"/>
-      <c r="P334" s="11" t="n"/>
-      <c r="Q334" s="5" t="n"/>
+      <c r="P334" s="5" t="n"/>
+      <c r="Q334" s="11" t="n"/>
       <c r="R334" s="5" t="n"/>
       <c r="S334" s="5" t="n"/>
       <c r="T334" s="5" t="n"/>
@@ -10926,8 +11104,8 @@
       <c r="M335" s="5" t="n"/>
       <c r="N335" s="5" t="n"/>
       <c r="O335" s="5" t="n"/>
-      <c r="P335" s="11" t="n"/>
-      <c r="Q335" s="5" t="n"/>
+      <c r="P335" s="5" t="n"/>
+      <c r="Q335" s="11" t="n"/>
       <c r="R335" s="5" t="n"/>
       <c r="S335" s="5" t="n"/>
       <c r="T335" s="5" t="n"/>
@@ -10953,8 +11131,8 @@
       <c r="M336" s="5" t="n"/>
       <c r="N336" s="5" t="n"/>
       <c r="O336" s="5" t="n"/>
-      <c r="P336" s="11" t="n"/>
-      <c r="Q336" s="5" t="n"/>
+      <c r="P336" s="5" t="n"/>
+      <c r="Q336" s="11" t="n"/>
       <c r="R336" s="5" t="n"/>
       <c r="S336" s="5" t="n"/>
       <c r="T336" s="5" t="n"/>
@@ -10980,8 +11158,8 @@
       <c r="M337" s="5" t="n"/>
       <c r="N337" s="5" t="n"/>
       <c r="O337" s="5" t="n"/>
-      <c r="P337" s="11" t="n"/>
-      <c r="Q337" s="5" t="n"/>
+      <c r="P337" s="5" t="n"/>
+      <c r="Q337" s="11" t="n"/>
       <c r="R337" s="5" t="n"/>
       <c r="S337" s="5" t="n"/>
       <c r="T337" s="5" t="n"/>
@@ -11007,8 +11185,8 @@
       <c r="M338" s="5" t="n"/>
       <c r="N338" s="5" t="n"/>
       <c r="O338" s="5" t="n"/>
-      <c r="P338" s="11" t="n"/>
-      <c r="Q338" s="5" t="n"/>
+      <c r="P338" s="5" t="n"/>
+      <c r="Q338" s="11" t="n"/>
       <c r="R338" s="5" t="n"/>
       <c r="S338" s="5" t="n"/>
       <c r="T338" s="5" t="n"/>
@@ -11034,8 +11212,8 @@
       <c r="M339" s="5" t="n"/>
       <c r="N339" s="5" t="n"/>
       <c r="O339" s="5" t="n"/>
-      <c r="P339" s="11" t="n"/>
-      <c r="Q339" s="5" t="n"/>
+      <c r="P339" s="5" t="n"/>
+      <c r="Q339" s="11" t="n"/>
       <c r="R339" s="5" t="n"/>
       <c r="S339" s="5" t="n"/>
       <c r="T339" s="5" t="n"/>
@@ -11061,8 +11239,8 @@
       <c r="M340" s="5" t="n"/>
       <c r="N340" s="5" t="n"/>
       <c r="O340" s="5" t="n"/>
-      <c r="P340" s="11" t="n"/>
-      <c r="Q340" s="5" t="n"/>
+      <c r="P340" s="5" t="n"/>
+      <c r="Q340" s="11" t="n"/>
       <c r="R340" s="5" t="n"/>
       <c r="S340" s="5" t="n"/>
       <c r="T340" s="5" t="n"/>
@@ -11088,8 +11266,8 @@
       <c r="M341" s="5" t="n"/>
       <c r="N341" s="5" t="n"/>
       <c r="O341" s="5" t="n"/>
-      <c r="P341" s="11" t="n"/>
-      <c r="Q341" s="5" t="n"/>
+      <c r="P341" s="5" t="n"/>
+      <c r="Q341" s="11" t="n"/>
       <c r="R341" s="5" t="n"/>
       <c r="S341" s="5" t="n"/>
       <c r="T341" s="5" t="n"/>
@@ -11115,8 +11293,8 @@
       <c r="M342" s="5" t="n"/>
       <c r="N342" s="5" t="n"/>
       <c r="O342" s="5" t="n"/>
-      <c r="P342" s="11" t="n"/>
-      <c r="Q342" s="5" t="n"/>
+      <c r="P342" s="5" t="n"/>
+      <c r="Q342" s="11" t="n"/>
       <c r="R342" s="5" t="n"/>
       <c r="S342" s="5" t="n"/>
       <c r="T342" s="5" t="n"/>
@@ -11142,8 +11320,8 @@
       <c r="M343" s="5" t="n"/>
       <c r="N343" s="5" t="n"/>
       <c r="O343" s="5" t="n"/>
-      <c r="P343" s="11" t="n"/>
-      <c r="Q343" s="5" t="n"/>
+      <c r="P343" s="5" t="n"/>
+      <c r="Q343" s="11" t="n"/>
       <c r="R343" s="5" t="n"/>
       <c r="S343" s="5" t="n"/>
       <c r="T343" s="5" t="n"/>
@@ -11169,8 +11347,8 @@
       <c r="M344" s="5" t="n"/>
       <c r="N344" s="5" t="n"/>
       <c r="O344" s="5" t="n"/>
-      <c r="P344" s="11" t="n"/>
-      <c r="Q344" s="5" t="n"/>
+      <c r="P344" s="5" t="n"/>
+      <c r="Q344" s="11" t="n"/>
       <c r="R344" s="5" t="n"/>
       <c r="S344" s="5" t="n"/>
       <c r="T344" s="5" t="n"/>
@@ -11196,8 +11374,8 @@
       <c r="M345" s="5" t="n"/>
       <c r="N345" s="5" t="n"/>
       <c r="O345" s="5" t="n"/>
-      <c r="P345" s="11" t="n"/>
-      <c r="Q345" s="5" t="n"/>
+      <c r="P345" s="5" t="n"/>
+      <c r="Q345" s="11" t="n"/>
       <c r="R345" s="5" t="n"/>
       <c r="S345" s="5" t="n"/>
       <c r="T345" s="5" t="n"/>
@@ -11223,8 +11401,8 @@
       <c r="M346" s="5" t="n"/>
       <c r="N346" s="5" t="n"/>
       <c r="O346" s="5" t="n"/>
-      <c r="P346" s="11" t="n"/>
-      <c r="Q346" s="5" t="n"/>
+      <c r="P346" s="5" t="n"/>
+      <c r="Q346" s="11" t="n"/>
       <c r="R346" s="5" t="n"/>
       <c r="S346" s="5" t="n"/>
       <c r="T346" s="5" t="n"/>
@@ -11250,8 +11428,8 @@
       <c r="M347" s="5" t="n"/>
       <c r="N347" s="5" t="n"/>
       <c r="O347" s="5" t="n"/>
-      <c r="P347" s="11" t="n"/>
-      <c r="Q347" s="5" t="n"/>
+      <c r="P347" s="5" t="n"/>
+      <c r="Q347" s="11" t="n"/>
       <c r="R347" s="5" t="n"/>
       <c r="S347" s="5" t="n"/>
       <c r="T347" s="5" t="n"/>
@@ -11277,8 +11455,8 @@
       <c r="M348" s="5" t="n"/>
       <c r="N348" s="5" t="n"/>
       <c r="O348" s="5" t="n"/>
-      <c r="P348" s="11" t="n"/>
-      <c r="Q348" s="5" t="n"/>
+      <c r="P348" s="5" t="n"/>
+      <c r="Q348" s="11" t="n"/>
       <c r="R348" s="5" t="n"/>
       <c r="S348" s="5" t="n"/>
       <c r="T348" s="5" t="n"/>
@@ -11304,8 +11482,8 @@
       <c r="M349" s="5" t="n"/>
       <c r="N349" s="5" t="n"/>
       <c r="O349" s="5" t="n"/>
-      <c r="P349" s="11" t="n"/>
-      <c r="Q349" s="5" t="n"/>
+      <c r="P349" s="5" t="n"/>
+      <c r="Q349" s="11" t="n"/>
       <c r="R349" s="5" t="n"/>
       <c r="S349" s="5" t="n"/>
       <c r="T349" s="5" t="n"/>
@@ -11331,8 +11509,8 @@
       <c r="M350" s="5" t="n"/>
       <c r="N350" s="5" t="n"/>
       <c r="O350" s="5" t="n"/>
-      <c r="P350" s="11" t="n"/>
-      <c r="Q350" s="5" t="n"/>
+      <c r="P350" s="5" t="n"/>
+      <c r="Q350" s="11" t="n"/>
       <c r="R350" s="5" t="n"/>
       <c r="S350" s="5" t="n"/>
       <c r="T350" s="5" t="n"/>
@@ -11358,8 +11536,8 @@
       <c r="M351" s="5" t="n"/>
       <c r="N351" s="5" t="n"/>
       <c r="O351" s="5" t="n"/>
-      <c r="P351" s="11" t="n"/>
-      <c r="Q351" s="5" t="n"/>
+      <c r="P351" s="5" t="n"/>
+      <c r="Q351" s="11" t="n"/>
       <c r="R351" s="5" t="n"/>
       <c r="S351" s="5" t="n"/>
       <c r="T351" s="5" t="n"/>
@@ -11385,8 +11563,8 @@
       <c r="M352" s="5" t="n"/>
       <c r="N352" s="5" t="n"/>
       <c r="O352" s="5" t="n"/>
-      <c r="P352" s="11" t="n"/>
-      <c r="Q352" s="5" t="n"/>
+      <c r="P352" s="5" t="n"/>
+      <c r="Q352" s="11" t="n"/>
       <c r="R352" s="5" t="n"/>
       <c r="S352" s="5" t="n"/>
       <c r="T352" s="5" t="n"/>
@@ -11412,8 +11590,8 @@
       <c r="M353" s="5" t="n"/>
       <c r="N353" s="5" t="n"/>
       <c r="O353" s="5" t="n"/>
-      <c r="P353" s="11" t="n"/>
-      <c r="Q353" s="5" t="n"/>
+      <c r="P353" s="5" t="n"/>
+      <c r="Q353" s="11" t="n"/>
       <c r="R353" s="5" t="n"/>
       <c r="S353" s="5" t="n"/>
       <c r="T353" s="5" t="n"/>
@@ -11439,8 +11617,8 @@
       <c r="M354" s="5" t="n"/>
       <c r="N354" s="5" t="n"/>
       <c r="O354" s="5" t="n"/>
-      <c r="P354" s="11" t="n"/>
-      <c r="Q354" s="5" t="n"/>
+      <c r="P354" s="5" t="n"/>
+      <c r="Q354" s="11" t="n"/>
       <c r="R354" s="5" t="n"/>
       <c r="S354" s="5" t="n"/>
       <c r="T354" s="5" t="n"/>
@@ -11466,8 +11644,8 @@
       <c r="M355" s="5" t="n"/>
       <c r="N355" s="5" t="n"/>
       <c r="O355" s="5" t="n"/>
-      <c r="P355" s="11" t="n"/>
-      <c r="Q355" s="5" t="n"/>
+      <c r="P355" s="5" t="n"/>
+      <c r="Q355" s="11" t="n"/>
       <c r="R355" s="5" t="n"/>
       <c r="S355" s="5" t="n"/>
       <c r="T355" s="5" t="n"/>
@@ -11493,8 +11671,8 @@
       <c r="M356" s="5" t="n"/>
       <c r="N356" s="5" t="n"/>
       <c r="O356" s="5" t="n"/>
-      <c r="P356" s="11" t="n"/>
-      <c r="Q356" s="5" t="n"/>
+      <c r="P356" s="5" t="n"/>
+      <c r="Q356" s="11" t="n"/>
       <c r="R356" s="5" t="n"/>
       <c r="S356" s="5" t="n"/>
       <c r="T356" s="5" t="n"/>
@@ -11520,8 +11698,8 @@
       <c r="M357" s="5" t="n"/>
       <c r="N357" s="5" t="n"/>
       <c r="O357" s="5" t="n"/>
-      <c r="P357" s="11" t="n"/>
-      <c r="Q357" s="5" t="n"/>
+      <c r="P357" s="5" t="n"/>
+      <c r="Q357" s="11" t="n"/>
       <c r="R357" s="5" t="n"/>
       <c r="S357" s="5" t="n"/>
       <c r="T357" s="5" t="n"/>
@@ -11547,8 +11725,8 @@
       <c r="M358" s="5" t="n"/>
       <c r="N358" s="5" t="n"/>
       <c r="O358" s="5" t="n"/>
-      <c r="P358" s="11" t="n"/>
-      <c r="Q358" s="5" t="n"/>
+      <c r="P358" s="5" t="n"/>
+      <c r="Q358" s="11" t="n"/>
       <c r="R358" s="5" t="n"/>
       <c r="S358" s="5" t="n"/>
       <c r="T358" s="5" t="n"/>
@@ -11574,8 +11752,8 @@
       <c r="M359" s="5" t="n"/>
       <c r="N359" s="5" t="n"/>
       <c r="O359" s="5" t="n"/>
-      <c r="P359" s="11" t="n"/>
-      <c r="Q359" s="5" t="n"/>
+      <c r="P359" s="5" t="n"/>
+      <c r="Q359" s="11" t="n"/>
       <c r="R359" s="5" t="n"/>
       <c r="S359" s="5" t="n"/>
       <c r="T359" s="5" t="n"/>
@@ -11601,8 +11779,8 @@
       <c r="M360" s="5" t="n"/>
       <c r="N360" s="5" t="n"/>
       <c r="O360" s="5" t="n"/>
-      <c r="P360" s="11" t="n"/>
-      <c r="Q360" s="5" t="n"/>
+      <c r="P360" s="5" t="n"/>
+      <c r="Q360" s="11" t="n"/>
       <c r="R360" s="5" t="n"/>
       <c r="S360" s="5" t="n"/>
       <c r="T360" s="5" t="n"/>
@@ -11628,8 +11806,8 @@
       <c r="M361" s="5" t="n"/>
       <c r="N361" s="5" t="n"/>
       <c r="O361" s="5" t="n"/>
-      <c r="P361" s="11" t="n"/>
-      <c r="Q361" s="5" t="n"/>
+      <c r="P361" s="5" t="n"/>
+      <c r="Q361" s="11" t="n"/>
       <c r="R361" s="5" t="n"/>
       <c r="S361" s="5" t="n"/>
       <c r="T361" s="5" t="n"/>
@@ -11655,8 +11833,8 @@
       <c r="M362" s="5" t="n"/>
       <c r="N362" s="5" t="n"/>
       <c r="O362" s="5" t="n"/>
-      <c r="P362" s="11" t="n"/>
-      <c r="Q362" s="5" t="n"/>
+      <c r="P362" s="5" t="n"/>
+      <c r="Q362" s="11" t="n"/>
       <c r="R362" s="5" t="n"/>
       <c r="S362" s="5" t="n"/>
       <c r="T362" s="5" t="n"/>
@@ -11682,8 +11860,8 @@
       <c r="M363" s="5" t="n"/>
       <c r="N363" s="5" t="n"/>
       <c r="O363" s="5" t="n"/>
-      <c r="P363" s="11" t="n"/>
-      <c r="Q363" s="5" t="n"/>
+      <c r="P363" s="5" t="n"/>
+      <c r="Q363" s="11" t="n"/>
       <c r="R363" s="5" t="n"/>
       <c r="S363" s="5" t="n"/>
       <c r="T363" s="5" t="n"/>
@@ -11709,8 +11887,8 @@
       <c r="M364" s="5" t="n"/>
       <c r="N364" s="5" t="n"/>
       <c r="O364" s="5" t="n"/>
-      <c r="P364" s="11" t="n"/>
-      <c r="Q364" s="5" t="n"/>
+      <c r="P364" s="5" t="n"/>
+      <c r="Q364" s="11" t="n"/>
       <c r="R364" s="5" t="n"/>
       <c r="S364" s="5" t="n"/>
       <c r="T364" s="5" t="n"/>
@@ -11736,8 +11914,8 @@
       <c r="M365" s="5" t="n"/>
       <c r="N365" s="5" t="n"/>
       <c r="O365" s="5" t="n"/>
-      <c r="P365" s="11" t="n"/>
-      <c r="Q365" s="5" t="n"/>
+      <c r="P365" s="5" t="n"/>
+      <c r="Q365" s="11" t="n"/>
       <c r="R365" s="5" t="n"/>
       <c r="S365" s="5" t="n"/>
       <c r="T365" s="5" t="n"/>
@@ -11763,8 +11941,8 @@
       <c r="M366" s="5" t="n"/>
       <c r="N366" s="5" t="n"/>
       <c r="O366" s="5" t="n"/>
-      <c r="P366" s="11" t="n"/>
-      <c r="Q366" s="5" t="n"/>
+      <c r="P366" s="5" t="n"/>
+      <c r="Q366" s="11" t="n"/>
       <c r="R366" s="5" t="n"/>
       <c r="S366" s="5" t="n"/>
       <c r="T366" s="5" t="n"/>
@@ -11790,8 +11968,8 @@
       <c r="M367" s="5" t="n"/>
       <c r="N367" s="5" t="n"/>
       <c r="O367" s="5" t="n"/>
-      <c r="P367" s="11" t="n"/>
-      <c r="Q367" s="5" t="n"/>
+      <c r="P367" s="5" t="n"/>
+      <c r="Q367" s="11" t="n"/>
       <c r="R367" s="5" t="n"/>
       <c r="S367" s="5" t="n"/>
       <c r="T367" s="5" t="n"/>
@@ -11817,8 +11995,8 @@
       <c r="M368" s="5" t="n"/>
       <c r="N368" s="5" t="n"/>
       <c r="O368" s="5" t="n"/>
-      <c r="P368" s="11" t="n"/>
-      <c r="Q368" s="5" t="n"/>
+      <c r="P368" s="5" t="n"/>
+      <c r="Q368" s="11" t="n"/>
       <c r="R368" s="5" t="n"/>
       <c r="S368" s="5" t="n"/>
       <c r="T368" s="5" t="n"/>
@@ -11844,8 +12022,8 @@
       <c r="M369" s="5" t="n"/>
       <c r="N369" s="5" t="n"/>
       <c r="O369" s="5" t="n"/>
-      <c r="P369" s="11" t="n"/>
-      <c r="Q369" s="5" t="n"/>
+      <c r="P369" s="5" t="n"/>
+      <c r="Q369" s="11" t="n"/>
       <c r="R369" s="5" t="n"/>
       <c r="S369" s="5" t="n"/>
       <c r="T369" s="5" t="n"/>
@@ -11871,8 +12049,8 @@
       <c r="M370" s="5" t="n"/>
       <c r="N370" s="5" t="n"/>
       <c r="O370" s="5" t="n"/>
-      <c r="P370" s="11" t="n"/>
-      <c r="Q370" s="5" t="n"/>
+      <c r="P370" s="5" t="n"/>
+      <c r="Q370" s="11" t="n"/>
       <c r="R370" s="5" t="n"/>
       <c r="S370" s="5" t="n"/>
       <c r="T370" s="5" t="n"/>
@@ -11898,8 +12076,8 @@
       <c r="M371" s="5" t="n"/>
       <c r="N371" s="5" t="n"/>
       <c r="O371" s="5" t="n"/>
-      <c r="P371" s="11" t="n"/>
-      <c r="Q371" s="5" t="n"/>
+      <c r="P371" s="5" t="n"/>
+      <c r="Q371" s="11" t="n"/>
       <c r="R371" s="5" t="n"/>
       <c r="S371" s="5" t="n"/>
       <c r="T371" s="5" t="n"/>
@@ -11925,8 +12103,8 @@
       <c r="M372" s="5" t="n"/>
       <c r="N372" s="5" t="n"/>
       <c r="O372" s="5" t="n"/>
-      <c r="P372" s="11" t="n"/>
-      <c r="Q372" s="5" t="n"/>
+      <c r="P372" s="5" t="n"/>
+      <c r="Q372" s="11" t="n"/>
       <c r="R372" s="5" t="n"/>
       <c r="S372" s="5" t="n"/>
       <c r="T372" s="5" t="n"/>
@@ -11952,8 +12130,8 @@
       <c r="M373" s="5" t="n"/>
       <c r="N373" s="5" t="n"/>
       <c r="O373" s="5" t="n"/>
-      <c r="P373" s="11" t="n"/>
-      <c r="Q373" s="5" t="n"/>
+      <c r="P373" s="5" t="n"/>
+      <c r="Q373" s="11" t="n"/>
       <c r="R373" s="5" t="n"/>
       <c r="S373" s="5" t="n"/>
       <c r="T373" s="5" t="n"/>
@@ -11979,8 +12157,8 @@
       <c r="M374" s="5" t="n"/>
       <c r="N374" s="5" t="n"/>
       <c r="O374" s="5" t="n"/>
-      <c r="P374" s="11" t="n"/>
-      <c r="Q374" s="5" t="n"/>
+      <c r="P374" s="5" t="n"/>
+      <c r="Q374" s="11" t="n"/>
       <c r="R374" s="5" t="n"/>
       <c r="S374" s="5" t="n"/>
       <c r="T374" s="5" t="n"/>
@@ -12006,8 +12184,8 @@
       <c r="M375" s="5" t="n"/>
       <c r="N375" s="5" t="n"/>
       <c r="O375" s="5" t="n"/>
-      <c r="P375" s="11" t="n"/>
-      <c r="Q375" s="5" t="n"/>
+      <c r="P375" s="5" t="n"/>
+      <c r="Q375" s="11" t="n"/>
       <c r="R375" s="5" t="n"/>
       <c r="S375" s="5" t="n"/>
       <c r="T375" s="5" t="n"/>
@@ -12033,8 +12211,8 @@
       <c r="M376" s="5" t="n"/>
       <c r="N376" s="5" t="n"/>
       <c r="O376" s="5" t="n"/>
-      <c r="P376" s="11" t="n"/>
-      <c r="Q376" s="5" t="n"/>
+      <c r="P376" s="5" t="n"/>
+      <c r="Q376" s="11" t="n"/>
       <c r="R376" s="5" t="n"/>
       <c r="S376" s="5" t="n"/>
       <c r="T376" s="5" t="n"/>
@@ -12060,8 +12238,8 @@
       <c r="M377" s="5" t="n"/>
       <c r="N377" s="5" t="n"/>
       <c r="O377" s="5" t="n"/>
-      <c r="P377" s="11" t="n"/>
-      <c r="Q377" s="5" t="n"/>
+      <c r="P377" s="5" t="n"/>
+      <c r="Q377" s="11" t="n"/>
       <c r="R377" s="5" t="n"/>
       <c r="S377" s="5" t="n"/>
       <c r="T377" s="5" t="n"/>
@@ -12087,8 +12265,8 @@
       <c r="M378" s="5" t="n"/>
       <c r="N378" s="5" t="n"/>
       <c r="O378" s="5" t="n"/>
-      <c r="P378" s="11" t="n"/>
-      <c r="Q378" s="5" t="n"/>
+      <c r="P378" s="5" t="n"/>
+      <c r="Q378" s="11" t="n"/>
       <c r="R378" s="5" t="n"/>
       <c r="S378" s="5" t="n"/>
       <c r="T378" s="5" t="n"/>
@@ -12114,8 +12292,8 @@
       <c r="M379" s="5" t="n"/>
       <c r="N379" s="5" t="n"/>
       <c r="O379" s="5" t="n"/>
-      <c r="P379" s="11" t="n"/>
-      <c r="Q379" s="5" t="n"/>
+      <c r="P379" s="5" t="n"/>
+      <c r="Q379" s="11" t="n"/>
       <c r="R379" s="5" t="n"/>
       <c r="S379" s="5" t="n"/>
       <c r="T379" s="5" t="n"/>
@@ -12141,8 +12319,8 @@
       <c r="M380" s="5" t="n"/>
       <c r="N380" s="5" t="n"/>
       <c r="O380" s="5" t="n"/>
-      <c r="P380" s="11" t="n"/>
-      <c r="Q380" s="5" t="n"/>
+      <c r="P380" s="5" t="n"/>
+      <c r="Q380" s="11" t="n"/>
       <c r="R380" s="5" t="n"/>
       <c r="S380" s="5" t="n"/>
       <c r="T380" s="5" t="n"/>
@@ -12168,8 +12346,8 @@
       <c r="M381" s="5" t="n"/>
       <c r="N381" s="5" t="n"/>
       <c r="O381" s="5" t="n"/>
-      <c r="P381" s="11" t="n"/>
-      <c r="Q381" s="5" t="n"/>
+      <c r="P381" s="5" t="n"/>
+      <c r="Q381" s="11" t="n"/>
       <c r="R381" s="5" t="n"/>
       <c r="S381" s="5" t="n"/>
       <c r="T381" s="5" t="n"/>
@@ -12195,8 +12373,8 @@
       <c r="M382" s="5" t="n"/>
       <c r="N382" s="5" t="n"/>
       <c r="O382" s="5" t="n"/>
-      <c r="P382" s="11" t="n"/>
-      <c r="Q382" s="5" t="n"/>
+      <c r="P382" s="5" t="n"/>
+      <c r="Q382" s="11" t="n"/>
       <c r="R382" s="5" t="n"/>
       <c r="S382" s="5" t="n"/>
       <c r="T382" s="5" t="n"/>
@@ -12222,8 +12400,8 @@
       <c r="M383" s="5" t="n"/>
       <c r="N383" s="5" t="n"/>
       <c r="O383" s="5" t="n"/>
-      <c r="P383" s="11" t="n"/>
-      <c r="Q383" s="5" t="n"/>
+      <c r="P383" s="5" t="n"/>
+      <c r="Q383" s="11" t="n"/>
       <c r="R383" s="5" t="n"/>
       <c r="S383" s="5" t="n"/>
       <c r="T383" s="5" t="n"/>
@@ -12249,8 +12427,8 @@
       <c r="M384" s="5" t="n"/>
       <c r="N384" s="5" t="n"/>
       <c r="O384" s="5" t="n"/>
-      <c r="P384" s="11" t="n"/>
-      <c r="Q384" s="5" t="n"/>
+      <c r="P384" s="5" t="n"/>
+      <c r="Q384" s="11" t="n"/>
       <c r="R384" s="5" t="n"/>
       <c r="S384" s="5" t="n"/>
       <c r="T384" s="5" t="n"/>
@@ -12276,8 +12454,8 @@
       <c r="M385" s="5" t="n"/>
       <c r="N385" s="5" t="n"/>
       <c r="O385" s="5" t="n"/>
-      <c r="P385" s="11" t="n"/>
-      <c r="Q385" s="5" t="n"/>
+      <c r="P385" s="5" t="n"/>
+      <c r="Q385" s="11" t="n"/>
       <c r="R385" s="5" t="n"/>
       <c r="S385" s="5" t="n"/>
       <c r="T385" s="5" t="n"/>
@@ -12303,8 +12481,8 @@
       <c r="M386" s="5" t="n"/>
       <c r="N386" s="5" t="n"/>
       <c r="O386" s="5" t="n"/>
-      <c r="P386" s="11" t="n"/>
-      <c r="Q386" s="5" t="n"/>
+      <c r="P386" s="5" t="n"/>
+      <c r="Q386" s="11" t="n"/>
       <c r="R386" s="5" t="n"/>
       <c r="S386" s="5" t="n"/>
       <c r="T386" s="5" t="n"/>
@@ -12330,8 +12508,8 @@
       <c r="M387" s="5" t="n"/>
       <c r="N387" s="5" t="n"/>
       <c r="O387" s="5" t="n"/>
-      <c r="P387" s="11" t="n"/>
-      <c r="Q387" s="5" t="n"/>
+      <c r="P387" s="5" t="n"/>
+      <c r="Q387" s="11" t="n"/>
       <c r="R387" s="5" t="n"/>
       <c r="S387" s="5" t="n"/>
       <c r="T387" s="5" t="n"/>
@@ -12357,8 +12535,8 @@
       <c r="M388" s="5" t="n"/>
       <c r="N388" s="5" t="n"/>
       <c r="O388" s="5" t="n"/>
-      <c r="P388" s="11" t="n"/>
-      <c r="Q388" s="5" t="n"/>
+      <c r="P388" s="5" t="n"/>
+      <c r="Q388" s="11" t="n"/>
       <c r="R388" s="5" t="n"/>
       <c r="S388" s="5" t="n"/>
       <c r="T388" s="5" t="n"/>
@@ -12384,8 +12562,8 @@
       <c r="M389" s="5" t="n"/>
       <c r="N389" s="5" t="n"/>
       <c r="O389" s="5" t="n"/>
-      <c r="P389" s="11" t="n"/>
-      <c r="Q389" s="5" t="n"/>
+      <c r="P389" s="5" t="n"/>
+      <c r="Q389" s="11" t="n"/>
       <c r="R389" s="5" t="n"/>
       <c r="S389" s="5" t="n"/>
       <c r="T389" s="5" t="n"/>
@@ -12411,8 +12589,8 @@
       <c r="M390" s="5" t="n"/>
       <c r="N390" s="5" t="n"/>
       <c r="O390" s="5" t="n"/>
-      <c r="P390" s="11" t="n"/>
-      <c r="Q390" s="5" t="n"/>
+      <c r="P390" s="5" t="n"/>
+      <c r="Q390" s="11" t="n"/>
       <c r="R390" s="5" t="n"/>
       <c r="S390" s="5" t="n"/>
       <c r="T390" s="5" t="n"/>
@@ -12438,8 +12616,8 @@
       <c r="M391" s="5" t="n"/>
       <c r="N391" s="5" t="n"/>
       <c r="O391" s="5" t="n"/>
-      <c r="P391" s="11" t="n"/>
-      <c r="Q391" s="5" t="n"/>
+      <c r="P391" s="5" t="n"/>
+      <c r="Q391" s="11" t="n"/>
       <c r="R391" s="5" t="n"/>
       <c r="S391" s="5" t="n"/>
       <c r="T391" s="5" t="n"/>
@@ -12465,8 +12643,8 @@
       <c r="M392" s="5" t="n"/>
       <c r="N392" s="5" t="n"/>
       <c r="O392" s="5" t="n"/>
-      <c r="P392" s="11" t="n"/>
-      <c r="Q392" s="5" t="n"/>
+      <c r="P392" s="5" t="n"/>
+      <c r="Q392" s="11" t="n"/>
       <c r="R392" s="5" t="n"/>
       <c r="S392" s="5" t="n"/>
       <c r="T392" s="5" t="n"/>
@@ -12492,8 +12670,8 @@
       <c r="M393" s="5" t="n"/>
       <c r="N393" s="5" t="n"/>
       <c r="O393" s="5" t="n"/>
-      <c r="P393" s="11" t="n"/>
-      <c r="Q393" s="5" t="n"/>
+      <c r="P393" s="5" t="n"/>
+      <c r="Q393" s="11" t="n"/>
       <c r="R393" s="5" t="n"/>
       <c r="S393" s="5" t="n"/>
       <c r="T393" s="5" t="n"/>
@@ -12519,8 +12697,8 @@
       <c r="M394" s="5" t="n"/>
       <c r="N394" s="5" t="n"/>
       <c r="O394" s="5" t="n"/>
-      <c r="P394" s="11" t="n"/>
-      <c r="Q394" s="5" t="n"/>
+      <c r="P394" s="5" t="n"/>
+      <c r="Q394" s="11" t="n"/>
       <c r="R394" s="5" t="n"/>
       <c r="S394" s="5" t="n"/>
       <c r="T394" s="5" t="n"/>
@@ -12546,8 +12724,8 @@
       <c r="M395" s="5" t="n"/>
       <c r="N395" s="5" t="n"/>
       <c r="O395" s="5" t="n"/>
-      <c r="P395" s="11" t="n"/>
-      <c r="Q395" s="5" t="n"/>
+      <c r="P395" s="5" t="n"/>
+      <c r="Q395" s="11" t="n"/>
       <c r="R395" s="5" t="n"/>
       <c r="S395" s="5" t="n"/>
       <c r="T395" s="5" t="n"/>
@@ -12573,8 +12751,8 @@
       <c r="M396" s="5" t="n"/>
       <c r="N396" s="5" t="n"/>
       <c r="O396" s="5" t="n"/>
-      <c r="P396" s="11" t="n"/>
-      <c r="Q396" s="5" t="n"/>
+      <c r="P396" s="5" t="n"/>
+      <c r="Q396" s="11" t="n"/>
       <c r="R396" s="5" t="n"/>
       <c r="S396" s="5" t="n"/>
       <c r="T396" s="5" t="n"/>
@@ -12600,8 +12778,8 @@
       <c r="M397" s="5" t="n"/>
       <c r="N397" s="5" t="n"/>
       <c r="O397" s="5" t="n"/>
-      <c r="P397" s="11" t="n"/>
-      <c r="Q397" s="5" t="n"/>
+      <c r="P397" s="5" t="n"/>
+      <c r="Q397" s="11" t="n"/>
       <c r="R397" s="5" t="n"/>
       <c r="S397" s="5" t="n"/>
       <c r="T397" s="5" t="n"/>
@@ -12627,8 +12805,8 @@
       <c r="M398" s="5" t="n"/>
       <c r="N398" s="5" t="n"/>
       <c r="O398" s="5" t="n"/>
-      <c r="P398" s="11" t="n"/>
-      <c r="Q398" s="5" t="n"/>
+      <c r="P398" s="5" t="n"/>
+      <c r="Q398" s="11" t="n"/>
       <c r="R398" s="5" t="n"/>
       <c r="S398" s="5" t="n"/>
       <c r="T398" s="5" t="n"/>
@@ -12654,8 +12832,8 @@
       <c r="M399" s="5" t="n"/>
       <c r="N399" s="5" t="n"/>
       <c r="O399" s="5" t="n"/>
-      <c r="P399" s="11" t="n"/>
-      <c r="Q399" s="5" t="n"/>
+      <c r="P399" s="5" t="n"/>
+      <c r="Q399" s="11" t="n"/>
       <c r="R399" s="5" t="n"/>
       <c r="S399" s="5" t="n"/>
       <c r="T399" s="5" t="n"/>
@@ -12681,8 +12859,8 @@
       <c r="M400" s="5" t="n"/>
       <c r="N400" s="5" t="n"/>
       <c r="O400" s="5" t="n"/>
-      <c r="P400" s="11" t="n"/>
-      <c r="Q400" s="5" t="n"/>
+      <c r="P400" s="5" t="n"/>
+      <c r="Q400" s="11" t="n"/>
       <c r="R400" s="5" t="n"/>
       <c r="S400" s="5" t="n"/>
       <c r="T400" s="5" t="n"/>
@@ -12708,8 +12886,8 @@
       <c r="M401" s="5" t="n"/>
       <c r="N401" s="5" t="n"/>
       <c r="O401" s="5" t="n"/>
-      <c r="P401" s="11" t="n"/>
-      <c r="Q401" s="5" t="n"/>
+      <c r="P401" s="5" t="n"/>
+      <c r="Q401" s="11" t="n"/>
       <c r="R401" s="5" t="n"/>
       <c r="S401" s="5" t="n"/>
       <c r="T401" s="5" t="n"/>
@@ -12735,8 +12913,8 @@
       <c r="M402" s="5" t="n"/>
       <c r="N402" s="5" t="n"/>
       <c r="O402" s="5" t="n"/>
-      <c r="P402" s="11" t="n"/>
-      <c r="Q402" s="5" t="n"/>
+      <c r="P402" s="5" t="n"/>
+      <c r="Q402" s="11" t="n"/>
       <c r="R402" s="5" t="n"/>
       <c r="S402" s="5" t="n"/>
       <c r="T402" s="5" t="n"/>
@@ -12762,8 +12940,8 @@
       <c r="M403" s="5" t="n"/>
       <c r="N403" s="5" t="n"/>
       <c r="O403" s="5" t="n"/>
-      <c r="P403" s="11" t="n"/>
-      <c r="Q403" s="5" t="n"/>
+      <c r="P403" s="5" t="n"/>
+      <c r="Q403" s="11" t="n"/>
       <c r="R403" s="5" t="n"/>
       <c r="S403" s="5" t="n"/>
       <c r="T403" s="5" t="n"/>
@@ -12789,8 +12967,8 @@
       <c r="M404" s="5" t="n"/>
       <c r="N404" s="5" t="n"/>
       <c r="O404" s="5" t="n"/>
-      <c r="P404" s="11" t="n"/>
-      <c r="Q404" s="5" t="n"/>
+      <c r="P404" s="5" t="n"/>
+      <c r="Q404" s="11" t="n"/>
       <c r="R404" s="5" t="n"/>
       <c r="S404" s="5" t="n"/>
       <c r="T404" s="5" t="n"/>
@@ -12816,8 +12994,8 @@
       <c r="M405" s="5" t="n"/>
       <c r="N405" s="5" t="n"/>
       <c r="O405" s="5" t="n"/>
-      <c r="P405" s="11" t="n"/>
-      <c r="Q405" s="5" t="n"/>
+      <c r="P405" s="5" t="n"/>
+      <c r="Q405" s="11" t="n"/>
       <c r="R405" s="5" t="n"/>
       <c r="S405" s="5" t="n"/>
       <c r="T405" s="5" t="n"/>
@@ -12843,8 +13021,8 @@
       <c r="M406" s="5" t="n"/>
       <c r="N406" s="5" t="n"/>
       <c r="O406" s="5" t="n"/>
-      <c r="P406" s="11" t="n"/>
-      <c r="Q406" s="5" t="n"/>
+      <c r="P406" s="5" t="n"/>
+      <c r="Q406" s="11" t="n"/>
       <c r="R406" s="5" t="n"/>
       <c r="S406" s="5" t="n"/>
       <c r="T406" s="5" t="n"/>
@@ -12870,8 +13048,8 @@
       <c r="M407" s="5" t="n"/>
       <c r="N407" s="5" t="n"/>
       <c r="O407" s="5" t="n"/>
-      <c r="P407" s="11" t="n"/>
-      <c r="Q407" s="5" t="n"/>
+      <c r="P407" s="5" t="n"/>
+      <c r="Q407" s="11" t="n"/>
       <c r="R407" s="5" t="n"/>
       <c r="S407" s="5" t="n"/>
       <c r="T407" s="5" t="n"/>
@@ -12897,8 +13075,8 @@
       <c r="M408" s="5" t="n"/>
       <c r="N408" s="5" t="n"/>
       <c r="O408" s="5" t="n"/>
-      <c r="P408" s="11" t="n"/>
-      <c r="Q408" s="5" t="n"/>
+      <c r="P408" s="5" t="n"/>
+      <c r="Q408" s="11" t="n"/>
       <c r="R408" s="5" t="n"/>
       <c r="S408" s="5" t="n"/>
       <c r="T408" s="5" t="n"/>
@@ -12924,8 +13102,8 @@
       <c r="M409" s="5" t="n"/>
       <c r="N409" s="5" t="n"/>
       <c r="O409" s="5" t="n"/>
-      <c r="P409" s="11" t="n"/>
-      <c r="Q409" s="5" t="n"/>
+      <c r="P409" s="5" t="n"/>
+      <c r="Q409" s="11" t="n"/>
       <c r="R409" s="5" t="n"/>
       <c r="S409" s="5" t="n"/>
       <c r="T409" s="5" t="n"/>
@@ -12951,8 +13129,8 @@
       <c r="M410" s="5" t="n"/>
       <c r="N410" s="5" t="n"/>
       <c r="O410" s="5" t="n"/>
-      <c r="P410" s="11" t="n"/>
-      <c r="Q410" s="5" t="n"/>
+      <c r="P410" s="5" t="n"/>
+      <c r="Q410" s="11" t="n"/>
       <c r="R410" s="5" t="n"/>
       <c r="S410" s="5" t="n"/>
       <c r="T410" s="5" t="n"/>
@@ -12978,8 +13156,8 @@
       <c r="M411" s="5" t="n"/>
       <c r="N411" s="5" t="n"/>
       <c r="O411" s="5" t="n"/>
-      <c r="P411" s="11" t="n"/>
-      <c r="Q411" s="5" t="n"/>
+      <c r="P411" s="5" t="n"/>
+      <c r="Q411" s="11" t="n"/>
       <c r="R411" s="5" t="n"/>
       <c r="S411" s="5" t="n"/>
       <c r="T411" s="5" t="n"/>
@@ -13005,8 +13183,8 @@
       <c r="M412" s="5" t="n"/>
       <c r="N412" s="5" t="n"/>
       <c r="O412" s="5" t="n"/>
-      <c r="P412" s="11" t="n"/>
-      <c r="Q412" s="5" t="n"/>
+      <c r="P412" s="5" t="n"/>
+      <c r="Q412" s="11" t="n"/>
       <c r="R412" s="5" t="n"/>
       <c r="S412" s="5" t="n"/>
       <c r="T412" s="5" t="n"/>
@@ -13032,8 +13210,8 @@
       <c r="M413" s="5" t="n"/>
       <c r="N413" s="5" t="n"/>
       <c r="O413" s="5" t="n"/>
-      <c r="P413" s="11" t="n"/>
-      <c r="Q413" s="5" t="n"/>
+      <c r="P413" s="5" t="n"/>
+      <c r="Q413" s="11" t="n"/>
       <c r="R413" s="5" t="n"/>
       <c r="S413" s="5" t="n"/>
       <c r="T413" s="5" t="n"/>
@@ -13059,8 +13237,8 @@
       <c r="M414" s="5" t="n"/>
       <c r="N414" s="5" t="n"/>
       <c r="O414" s="5" t="n"/>
-      <c r="P414" s="11" t="n"/>
-      <c r="Q414" s="5" t="n"/>
+      <c r="P414" s="5" t="n"/>
+      <c r="Q414" s="11" t="n"/>
       <c r="R414" s="5" t="n"/>
       <c r="S414" s="5" t="n"/>
       <c r="T414" s="5" t="n"/>
@@ -13086,8 +13264,8 @@
       <c r="M415" s="5" t="n"/>
       <c r="N415" s="5" t="n"/>
       <c r="O415" s="5" t="n"/>
-      <c r="P415" s="11" t="n"/>
-      <c r="Q415" s="5" t="n"/>
+      <c r="P415" s="5" t="n"/>
+      <c r="Q415" s="11" t="n"/>
       <c r="R415" s="5" t="n"/>
       <c r="S415" s="5" t="n"/>
       <c r="T415" s="5" t="n"/>
@@ -13113,8 +13291,8 @@
       <c r="M416" s="5" t="n"/>
       <c r="N416" s="5" t="n"/>
       <c r="O416" s="5" t="n"/>
-      <c r="P416" s="11" t="n"/>
-      <c r="Q416" s="5" t="n"/>
+      <c r="P416" s="5" t="n"/>
+      <c r="Q416" s="11" t="n"/>
       <c r="R416" s="5" t="n"/>
       <c r="S416" s="5" t="n"/>
       <c r="T416" s="5" t="n"/>
@@ -13140,8 +13318,8 @@
       <c r="M417" s="5" t="n"/>
       <c r="N417" s="5" t="n"/>
       <c r="O417" s="5" t="n"/>
-      <c r="P417" s="11" t="n"/>
-      <c r="Q417" s="5" t="n"/>
+      <c r="P417" s="5" t="n"/>
+      <c r="Q417" s="11" t="n"/>
       <c r="R417" s="5" t="n"/>
       <c r="S417" s="5" t="n"/>
       <c r="T417" s="5" t="n"/>
@@ -13167,8 +13345,8 @@
       <c r="M418" s="5" t="n"/>
       <c r="N418" s="5" t="n"/>
       <c r="O418" s="5" t="n"/>
-      <c r="P418" s="11" t="n"/>
-      <c r="Q418" s="5" t="n"/>
+      <c r="P418" s="5" t="n"/>
+      <c r="Q418" s="11" t="n"/>
       <c r="R418" s="5" t="n"/>
       <c r="S418" s="5" t="n"/>
       <c r="T418" s="5" t="n"/>
@@ -13194,8 +13372,8 @@
       <c r="M419" s="5" t="n"/>
       <c r="N419" s="5" t="n"/>
       <c r="O419" s="5" t="n"/>
-      <c r="P419" s="11" t="n"/>
-      <c r="Q419" s="5" t="n"/>
+      <c r="P419" s="5" t="n"/>
+      <c r="Q419" s="11" t="n"/>
       <c r="R419" s="5" t="n"/>
       <c r="S419" s="5" t="n"/>
       <c r="T419" s="5" t="n"/>
@@ -13221,8 +13399,8 @@
       <c r="M420" s="5" t="n"/>
       <c r="N420" s="5" t="n"/>
       <c r="O420" s="5" t="n"/>
-      <c r="P420" s="11" t="n"/>
-      <c r="Q420" s="5" t="n"/>
+      <c r="P420" s="5" t="n"/>
+      <c r="Q420" s="11" t="n"/>
       <c r="R420" s="5" t="n"/>
       <c r="S420" s="5" t="n"/>
       <c r="T420" s="5" t="n"/>
@@ -13248,8 +13426,8 @@
       <c r="M421" s="5" t="n"/>
       <c r="N421" s="5" t="n"/>
       <c r="O421" s="5" t="n"/>
-      <c r="P421" s="11" t="n"/>
-      <c r="Q421" s="5" t="n"/>
+      <c r="P421" s="5" t="n"/>
+      <c r="Q421" s="11" t="n"/>
       <c r="R421" s="5" t="n"/>
       <c r="S421" s="5" t="n"/>
       <c r="T421" s="5" t="n"/>
@@ -13275,8 +13453,8 @@
       <c r="M422" s="5" t="n"/>
       <c r="N422" s="5" t="n"/>
       <c r="O422" s="5" t="n"/>
-      <c r="P422" s="11" t="n"/>
-      <c r="Q422" s="5" t="n"/>
+      <c r="P422" s="5" t="n"/>
+      <c r="Q422" s="11" t="n"/>
       <c r="R422" s="5" t="n"/>
       <c r="S422" s="5" t="n"/>
       <c r="T422" s="5" t="n"/>
@@ -13302,8 +13480,8 @@
       <c r="M423" s="5" t="n"/>
       <c r="N423" s="5" t="n"/>
       <c r="O423" s="5" t="n"/>
-      <c r="P423" s="11" t="n"/>
-      <c r="Q423" s="5" t="n"/>
+      <c r="P423" s="5" t="n"/>
+      <c r="Q423" s="11" t="n"/>
       <c r="R423" s="5" t="n"/>
       <c r="S423" s="5" t="n"/>
       <c r="T423" s="5" t="n"/>
@@ -13329,8 +13507,8 @@
       <c r="M424" s="5" t="n"/>
       <c r="N424" s="5" t="n"/>
       <c r="O424" s="5" t="n"/>
-      <c r="P424" s="11" t="n"/>
-      <c r="Q424" s="5" t="n"/>
+      <c r="P424" s="5" t="n"/>
+      <c r="Q424" s="11" t="n"/>
       <c r="R424" s="5" t="n"/>
       <c r="S424" s="5" t="n"/>
       <c r="T424" s="5" t="n"/>
@@ -13356,8 +13534,8 @@
       <c r="M425" s="5" t="n"/>
       <c r="N425" s="5" t="n"/>
       <c r="O425" s="5" t="n"/>
-      <c r="P425" s="11" t="n"/>
-      <c r="Q425" s="5" t="n"/>
+      <c r="P425" s="5" t="n"/>
+      <c r="Q425" s="11" t="n"/>
       <c r="R425" s="5" t="n"/>
       <c r="S425" s="5" t="n"/>
       <c r="T425" s="5" t="n"/>
@@ -13383,8 +13561,8 @@
       <c r="M426" s="5" t="n"/>
       <c r="N426" s="5" t="n"/>
       <c r="O426" s="5" t="n"/>
-      <c r="P426" s="11" t="n"/>
-      <c r="Q426" s="5" t="n"/>
+      <c r="P426" s="5" t="n"/>
+      <c r="Q426" s="11" t="n"/>
       <c r="R426" s="5" t="n"/>
       <c r="S426" s="5" t="n"/>
       <c r="T426" s="5" t="n"/>
@@ -13410,8 +13588,8 @@
       <c r="M427" s="5" t="n"/>
       <c r="N427" s="5" t="n"/>
       <c r="O427" s="5" t="n"/>
-      <c r="P427" s="11" t="n"/>
-      <c r="Q427" s="5" t="n"/>
+      <c r="P427" s="5" t="n"/>
+      <c r="Q427" s="11" t="n"/>
       <c r="R427" s="5" t="n"/>
       <c r="S427" s="5" t="n"/>
       <c r="T427" s="5" t="n"/>
@@ -13437,8 +13615,8 @@
       <c r="M428" s="5" t="n"/>
       <c r="N428" s="5" t="n"/>
       <c r="O428" s="5" t="n"/>
-      <c r="P428" s="11" t="n"/>
-      <c r="Q428" s="5" t="n"/>
+      <c r="P428" s="5" t="n"/>
+      <c r="Q428" s="11" t="n"/>
       <c r="R428" s="5" t="n"/>
       <c r="S428" s="5" t="n"/>
       <c r="T428" s="5" t="n"/>
@@ -13464,8 +13642,8 @@
       <c r="M429" s="5" t="n"/>
       <c r="N429" s="5" t="n"/>
       <c r="O429" s="5" t="n"/>
-      <c r="P429" s="11" t="n"/>
-      <c r="Q429" s="5" t="n"/>
+      <c r="P429" s="5" t="n"/>
+      <c r="Q429" s="11" t="n"/>
       <c r="R429" s="5" t="n"/>
       <c r="S429" s="5" t="n"/>
       <c r="T429" s="5" t="n"/>
@@ -13491,8 +13669,8 @@
       <c r="M430" s="5" t="n"/>
       <c r="N430" s="5" t="n"/>
       <c r="O430" s="5" t="n"/>
-      <c r="P430" s="11" t="n"/>
-      <c r="Q430" s="5" t="n"/>
+      <c r="P430" s="5" t="n"/>
+      <c r="Q430" s="11" t="n"/>
       <c r="R430" s="5" t="n"/>
       <c r="S430" s="5" t="n"/>
       <c r="T430" s="5" t="n"/>
@@ -13518,8 +13696,8 @@
       <c r="M431" s="5" t="n"/>
       <c r="N431" s="5" t="n"/>
       <c r="O431" s="5" t="n"/>
-      <c r="P431" s="11" t="n"/>
-      <c r="Q431" s="5" t="n"/>
+      <c r="P431" s="5" t="n"/>
+      <c r="Q431" s="11" t="n"/>
       <c r="R431" s="5" t="n"/>
       <c r="S431" s="5" t="n"/>
       <c r="T431" s="5" t="n"/>
@@ -13545,8 +13723,8 @@
       <c r="M432" s="5" t="n"/>
       <c r="N432" s="5" t="n"/>
       <c r="O432" s="5" t="n"/>
-      <c r="P432" s="11" t="n"/>
-      <c r="Q432" s="5" t="n"/>
+      <c r="P432" s="5" t="n"/>
+      <c r="Q432" s="11" t="n"/>
       <c r="R432" s="5" t="n"/>
       <c r="S432" s="5" t="n"/>
       <c r="T432" s="5" t="n"/>
@@ -13572,8 +13750,8 @@
       <c r="M433" s="5" t="n"/>
       <c r="N433" s="5" t="n"/>
       <c r="O433" s="5" t="n"/>
-      <c r="P433" s="11" t="n"/>
-      <c r="Q433" s="5" t="n"/>
+      <c r="P433" s="5" t="n"/>
+      <c r="Q433" s="11" t="n"/>
       <c r="R433" s="5" t="n"/>
       <c r="S433" s="5" t="n"/>
       <c r="T433" s="5" t="n"/>
@@ -13599,8 +13777,8 @@
       <c r="M434" s="5" t="n"/>
       <c r="N434" s="5" t="n"/>
       <c r="O434" s="5" t="n"/>
-      <c r="P434" s="11" t="n"/>
-      <c r="Q434" s="5" t="n"/>
+      <c r="P434" s="5" t="n"/>
+      <c r="Q434" s="11" t="n"/>
       <c r="R434" s="5" t="n"/>
       <c r="S434" s="5" t="n"/>
       <c r="T434" s="5" t="n"/>
@@ -13626,8 +13804,8 @@
       <c r="M435" s="5" t="n"/>
       <c r="N435" s="5" t="n"/>
       <c r="O435" s="5" t="n"/>
-      <c r="P435" s="11" t="n"/>
-      <c r="Q435" s="5" t="n"/>
+      <c r="P435" s="5" t="n"/>
+      <c r="Q435" s="11" t="n"/>
       <c r="R435" s="5" t="n"/>
       <c r="S435" s="5" t="n"/>
       <c r="T435" s="5" t="n"/>
@@ -13653,8 +13831,8 @@
       <c r="M436" s="5" t="n"/>
       <c r="N436" s="5" t="n"/>
       <c r="O436" s="5" t="n"/>
-      <c r="P436" s="11" t="n"/>
-      <c r="Q436" s="5" t="n"/>
+      <c r="P436" s="5" t="n"/>
+      <c r="Q436" s="11" t="n"/>
       <c r="R436" s="5" t="n"/>
       <c r="S436" s="5" t="n"/>
       <c r="T436" s="5" t="n"/>
@@ -13680,8 +13858,8 @@
       <c r="M437" s="5" t="n"/>
       <c r="N437" s="5" t="n"/>
       <c r="O437" s="5" t="n"/>
-      <c r="P437" s="11" t="n"/>
-      <c r="Q437" s="5" t="n"/>
+      <c r="P437" s="5" t="n"/>
+      <c r="Q437" s="11" t="n"/>
       <c r="R437" s="5" t="n"/>
       <c r="S437" s="5" t="n"/>
       <c r="T437" s="5" t="n"/>
@@ -13707,8 +13885,8 @@
       <c r="M438" s="5" t="n"/>
       <c r="N438" s="5" t="n"/>
       <c r="O438" s="5" t="n"/>
-      <c r="P438" s="11" t="n"/>
-      <c r="Q438" s="5" t="n"/>
+      <c r="P438" s="5" t="n"/>
+      <c r="Q438" s="11" t="n"/>
       <c r="R438" s="5" t="n"/>
       <c r="S438" s="5" t="n"/>
       <c r="T438" s="5" t="n"/>
@@ -13734,8 +13912,8 @@
       <c r="M439" s="5" t="n"/>
       <c r="N439" s="5" t="n"/>
       <c r="O439" s="5" t="n"/>
-      <c r="P439" s="11" t="n"/>
-      <c r="Q439" s="5" t="n"/>
+      <c r="P439" s="5" t="n"/>
+      <c r="Q439" s="11" t="n"/>
       <c r="R439" s="5" t="n"/>
       <c r="S439" s="5" t="n"/>
       <c r="T439" s="5" t="n"/>
@@ -13761,8 +13939,8 @@
       <c r="M440" s="5" t="n"/>
       <c r="N440" s="5" t="n"/>
       <c r="O440" s="5" t="n"/>
-      <c r="P440" s="11" t="n"/>
-      <c r="Q440" s="5" t="n"/>
+      <c r="P440" s="5" t="n"/>
+      <c r="Q440" s="11" t="n"/>
       <c r="R440" s="5" t="n"/>
       <c r="S440" s="5" t="n"/>
       <c r="T440" s="5" t="n"/>
@@ -13788,8 +13966,8 @@
       <c r="M441" s="5" t="n"/>
       <c r="N441" s="5" t="n"/>
       <c r="O441" s="5" t="n"/>
-      <c r="P441" s="11" t="n"/>
-      <c r="Q441" s="5" t="n"/>
+      <c r="P441" s="5" t="n"/>
+      <c r="Q441" s="11" t="n"/>
       <c r="R441" s="5" t="n"/>
       <c r="S441" s="5" t="n"/>
       <c r="T441" s="5" t="n"/>
@@ -13815,8 +13993,8 @@
       <c r="M442" s="5" t="n"/>
       <c r="N442" s="5" t="n"/>
       <c r="O442" s="5" t="n"/>
-      <c r="P442" s="11" t="n"/>
-      <c r="Q442" s="5" t="n"/>
+      <c r="P442" s="5" t="n"/>
+      <c r="Q442" s="11" t="n"/>
       <c r="R442" s="5" t="n"/>
       <c r="S442" s="5" t="n"/>
       <c r="T442" s="5" t="n"/>
@@ -13842,8 +14020,8 @@
       <c r="M443" s="5" t="n"/>
       <c r="N443" s="5" t="n"/>
       <c r="O443" s="5" t="n"/>
-      <c r="P443" s="11" t="n"/>
-      <c r="Q443" s="5" t="n"/>
+      <c r="P443" s="5" t="n"/>
+      <c r="Q443" s="11" t="n"/>
       <c r="R443" s="5" t="n"/>
       <c r="S443" s="5" t="n"/>
       <c r="T443" s="5" t="n"/>
@@ -13869,8 +14047,8 @@
       <c r="M444" s="5" t="n"/>
       <c r="N444" s="5" t="n"/>
       <c r="O444" s="5" t="n"/>
-      <c r="P444" s="11" t="n"/>
-      <c r="Q444" s="5" t="n"/>
+      <c r="P444" s="5" t="n"/>
+      <c r="Q444" s="11" t="n"/>
       <c r="R444" s="5" t="n"/>
       <c r="S444" s="5" t="n"/>
       <c r="T444" s="5" t="n"/>
@@ -13896,8 +14074,8 @@
       <c r="M445" s="5" t="n"/>
       <c r="N445" s="5" t="n"/>
       <c r="O445" s="5" t="n"/>
-      <c r="P445" s="11" t="n"/>
-      <c r="Q445" s="5" t="n"/>
+      <c r="P445" s="5" t="n"/>
+      <c r="Q445" s="11" t="n"/>
       <c r="R445" s="5" t="n"/>
       <c r="S445" s="5" t="n"/>
       <c r="T445" s="5" t="n"/>
@@ -13923,8 +14101,8 @@
       <c r="M446" s="5" t="n"/>
       <c r="N446" s="5" t="n"/>
       <c r="O446" s="5" t="n"/>
-      <c r="P446" s="11" t="n"/>
-      <c r="Q446" s="5" t="n"/>
+      <c r="P446" s="5" t="n"/>
+      <c r="Q446" s="11" t="n"/>
       <c r="R446" s="5" t="n"/>
       <c r="S446" s="5" t="n"/>
       <c r="T446" s="5" t="n"/>
@@ -13950,8 +14128,8 @@
       <c r="M447" s="5" t="n"/>
       <c r="N447" s="5" t="n"/>
       <c r="O447" s="5" t="n"/>
-      <c r="P447" s="11" t="n"/>
-      <c r="Q447" s="5" t="n"/>
+      <c r="P447" s="5" t="n"/>
+      <c r="Q447" s="11" t="n"/>
       <c r="R447" s="5" t="n"/>
       <c r="S447" s="5" t="n"/>
       <c r="T447" s="5" t="n"/>
@@ -13977,8 +14155,8 @@
       <c r="M448" s="5" t="n"/>
       <c r="N448" s="5" t="n"/>
       <c r="O448" s="5" t="n"/>
-      <c r="P448" s="11" t="n"/>
-      <c r="Q448" s="5" t="n"/>
+      <c r="P448" s="5" t="n"/>
+      <c r="Q448" s="11" t="n"/>
       <c r="R448" s="5" t="n"/>
       <c r="S448" s="5" t="n"/>
       <c r="T448" s="5" t="n"/>
@@ -14004,8 +14182,8 @@
       <c r="M449" s="5" t="n"/>
       <c r="N449" s="5" t="n"/>
       <c r="O449" s="5" t="n"/>
-      <c r="P449" s="11" t="n"/>
-      <c r="Q449" s="5" t="n"/>
+      <c r="P449" s="5" t="n"/>
+      <c r="Q449" s="11" t="n"/>
       <c r="R449" s="5" t="n"/>
       <c r="S449" s="5" t="n"/>
       <c r="T449" s="5" t="n"/>
@@ -14031,8 +14209,8 @@
       <c r="M450" s="5" t="n"/>
       <c r="N450" s="5" t="n"/>
       <c r="O450" s="5" t="n"/>
-      <c r="P450" s="11" t="n"/>
-      <c r="Q450" s="5" t="n"/>
+      <c r="P450" s="5" t="n"/>
+      <c r="Q450" s="11" t="n"/>
       <c r="R450" s="5" t="n"/>
       <c r="S450" s="5" t="n"/>
       <c r="T450" s="5" t="n"/>
@@ -14058,8 +14236,8 @@
       <c r="M451" s="5" t="n"/>
       <c r="N451" s="5" t="n"/>
       <c r="O451" s="5" t="n"/>
-      <c r="P451" s="11" t="n"/>
-      <c r="Q451" s="5" t="n"/>
+      <c r="P451" s="5" t="n"/>
+      <c r="Q451" s="11" t="n"/>
       <c r="R451" s="5" t="n"/>
       <c r="S451" s="5" t="n"/>
       <c r="T451" s="5" t="n"/>
@@ -14085,8 +14263,8 @@
       <c r="M452" s="5" t="n"/>
       <c r="N452" s="5" t="n"/>
       <c r="O452" s="5" t="n"/>
-      <c r="P452" s="11" t="n"/>
-      <c r="Q452" s="5" t="n"/>
+      <c r="P452" s="5" t="n"/>
+      <c r="Q452" s="11" t="n"/>
       <c r="R452" s="5" t="n"/>
       <c r="S452" s="5" t="n"/>
       <c r="T452" s="5" t="n"/>
@@ -14112,8 +14290,8 @@
       <c r="M453" s="5" t="n"/>
       <c r="N453" s="5" t="n"/>
       <c r="O453" s="5" t="n"/>
-      <c r="P453" s="11" t="n"/>
-      <c r="Q453" s="5" t="n"/>
+      <c r="P453" s="5" t="n"/>
+      <c r="Q453" s="11" t="n"/>
       <c r="R453" s="5" t="n"/>
       <c r="S453" s="5" t="n"/>
       <c r="T453" s="5" t="n"/>
@@ -14139,8 +14317,8 @@
       <c r="M454" s="5" t="n"/>
       <c r="N454" s="5" t="n"/>
       <c r="O454" s="5" t="n"/>
-      <c r="P454" s="11" t="n"/>
-      <c r="Q454" s="5" t="n"/>
+      <c r="P454" s="5" t="n"/>
+      <c r="Q454" s="11" t="n"/>
       <c r="R454" s="5" t="n"/>
       <c r="S454" s="5" t="n"/>
       <c r="T454" s="5" t="n"/>
@@ -14166,8 +14344,8 @@
       <c r="M455" s="5" t="n"/>
       <c r="N455" s="5" t="n"/>
       <c r="O455" s="5" t="n"/>
-      <c r="P455" s="11" t="n"/>
-      <c r="Q455" s="5" t="n"/>
+      <c r="P455" s="5" t="n"/>
+      <c r="Q455" s="11" t="n"/>
       <c r="R455" s="5" t="n"/>
       <c r="S455" s="5" t="n"/>
       <c r="T455" s="5" t="n"/>
@@ -14193,8 +14371,8 @@
       <c r="M456" s="5" t="n"/>
       <c r="N456" s="5" t="n"/>
       <c r="O456" s="5" t="n"/>
-      <c r="P456" s="11" t="n"/>
-      <c r="Q456" s="5" t="n"/>
+      <c r="P456" s="5" t="n"/>
+      <c r="Q456" s="11" t="n"/>
       <c r="R456" s="5" t="n"/>
       <c r="S456" s="5" t="n"/>
       <c r="T456" s="5" t="n"/>
@@ -14220,8 +14398,8 @@
       <c r="M457" s="5" t="n"/>
       <c r="N457" s="5" t="n"/>
       <c r="O457" s="5" t="n"/>
-      <c r="P457" s="11" t="n"/>
-      <c r="Q457" s="5" t="n"/>
+      <c r="P457" s="5" t="n"/>
+      <c r="Q457" s="11" t="n"/>
       <c r="R457" s="5" t="n"/>
       <c r="S457" s="5" t="n"/>
       <c r="T457" s="5" t="n"/>
@@ -14247,8 +14425,8 @@
       <c r="M458" s="5" t="n"/>
       <c r="N458" s="5" t="n"/>
       <c r="O458" s="5" t="n"/>
-      <c r="P458" s="11" t="n"/>
-      <c r="Q458" s="5" t="n"/>
+      <c r="P458" s="5" t="n"/>
+      <c r="Q458" s="11" t="n"/>
       <c r="R458" s="5" t="n"/>
       <c r="S458" s="5" t="n"/>
       <c r="T458" s="5" t="n"/>
@@ -14274,8 +14452,8 @@
       <c r="M459" s="5" t="n"/>
       <c r="N459" s="5" t="n"/>
       <c r="O459" s="5" t="n"/>
-      <c r="P459" s="11" t="n"/>
-      <c r="Q459" s="5" t="n"/>
+      <c r="P459" s="5" t="n"/>
+      <c r="Q459" s="11" t="n"/>
       <c r="R459" s="5" t="n"/>
       <c r="S459" s="5" t="n"/>
       <c r="T459" s="5" t="n"/>
@@ -14301,8 +14479,8 @@
       <c r="M460" s="5" t="n"/>
       <c r="N460" s="5" t="n"/>
       <c r="O460" s="5" t="n"/>
-      <c r="P460" s="11" t="n"/>
-      <c r="Q460" s="5" t="n"/>
+      <c r="P460" s="5" t="n"/>
+      <c r="Q460" s="11" t="n"/>
       <c r="R460" s="5" t="n"/>
       <c r="S460" s="5" t="n"/>
       <c r="T460" s="5" t="n"/>
@@ -14328,8 +14506,8 @@
       <c r="M461" s="5" t="n"/>
       <c r="N461" s="5" t="n"/>
       <c r="O461" s="5" t="n"/>
-      <c r="P461" s="11" t="n"/>
-      <c r="Q461" s="5" t="n"/>
+      <c r="P461" s="5" t="n"/>
+      <c r="Q461" s="11" t="n"/>
       <c r="R461" s="5" t="n"/>
       <c r="S461" s="5" t="n"/>
       <c r="T461" s="5" t="n"/>
@@ -14355,8 +14533,8 @@
       <c r="M462" s="5" t="n"/>
       <c r="N462" s="5" t="n"/>
       <c r="O462" s="5" t="n"/>
-      <c r="P462" s="11" t="n"/>
-      <c r="Q462" s="5" t="n"/>
+      <c r="P462" s="5" t="n"/>
+      <c r="Q462" s="11" t="n"/>
       <c r="R462" s="5" t="n"/>
       <c r="S462" s="5" t="n"/>
       <c r="T462" s="5" t="n"/>
@@ -14382,8 +14560,8 @@
       <c r="M463" s="5" t="n"/>
       <c r="N463" s="5" t="n"/>
       <c r="O463" s="5" t="n"/>
-      <c r="P463" s="11" t="n"/>
-      <c r="Q463" s="5" t="n"/>
+      <c r="P463" s="5" t="n"/>
+      <c r="Q463" s="11" t="n"/>
       <c r="R463" s="5" t="n"/>
       <c r="S463" s="5" t="n"/>
       <c r="T463" s="5" t="n"/>
@@ -14409,8 +14587,8 @@
       <c r="M464" s="5" t="n"/>
       <c r="N464" s="5" t="n"/>
       <c r="O464" s="5" t="n"/>
-      <c r="P464" s="11" t="n"/>
-      <c r="Q464" s="5" t="n"/>
+      <c r="P464" s="5" t="n"/>
+      <c r="Q464" s="11" t="n"/>
       <c r="R464" s="5" t="n"/>
       <c r="S464" s="5" t="n"/>
       <c r="T464" s="5" t="n"/>
@@ -14436,8 +14614,8 @@
       <c r="M465" s="5" t="n"/>
       <c r="N465" s="5" t="n"/>
       <c r="O465" s="5" t="n"/>
-      <c r="P465" s="11" t="n"/>
-      <c r="Q465" s="5" t="n"/>
+      <c r="P465" s="5" t="n"/>
+      <c r="Q465" s="11" t="n"/>
       <c r="R465" s="5" t="n"/>
       <c r="S465" s="5" t="n"/>
       <c r="T465" s="5" t="n"/>
@@ -14463,8 +14641,8 @@
       <c r="M466" s="5" t="n"/>
       <c r="N466" s="5" t="n"/>
       <c r="O466" s="5" t="n"/>
-      <c r="P466" s="11" t="n"/>
-      <c r="Q466" s="5" t="n"/>
+      <c r="P466" s="5" t="n"/>
+      <c r="Q466" s="11" t="n"/>
       <c r="R466" s="5" t="n"/>
       <c r="S466" s="5" t="n"/>
       <c r="T466" s="5" t="n"/>
@@ -14490,8 +14668,8 @@
       <c r="M467" s="5" t="n"/>
       <c r="N467" s="5" t="n"/>
       <c r="O467" s="5" t="n"/>
-      <c r="P467" s="11" t="n"/>
-      <c r="Q467" s="5" t="n"/>
+      <c r="P467" s="5" t="n"/>
+      <c r="Q467" s="11" t="n"/>
       <c r="R467" s="5" t="n"/>
       <c r="S467" s="5" t="n"/>
       <c r="T467" s="5" t="n"/>
@@ -14517,8 +14695,8 @@
       <c r="M468" s="5" t="n"/>
       <c r="N468" s="5" t="n"/>
       <c r="O468" s="5" t="n"/>
-      <c r="P468" s="11" t="n"/>
-      <c r="Q468" s="5" t="n"/>
+      <c r="P468" s="5" t="n"/>
+      <c r="Q468" s="11" t="n"/>
       <c r="R468" s="5" t="n"/>
       <c r="S468" s="5" t="n"/>
       <c r="T468" s="5" t="n"/>
@@ -14544,8 +14722,8 @@
       <c r="M469" s="5" t="n"/>
       <c r="N469" s="5" t="n"/>
       <c r="O469" s="5" t="n"/>
-      <c r="P469" s="11" t="n"/>
-      <c r="Q469" s="5" t="n"/>
+      <c r="P469" s="5" t="n"/>
+      <c r="Q469" s="11" t="n"/>
       <c r="R469" s="5" t="n"/>
       <c r="S469" s="5" t="n"/>
       <c r="T469" s="5" t="n"/>
@@ -14571,8 +14749,8 @@
       <c r="M470" s="5" t="n"/>
       <c r="N470" s="5" t="n"/>
       <c r="O470" s="5" t="n"/>
-      <c r="P470" s="11" t="n"/>
-      <c r="Q470" s="5" t="n"/>
+      <c r="P470" s="5" t="n"/>
+      <c r="Q470" s="11" t="n"/>
       <c r="R470" s="5" t="n"/>
       <c r="S470" s="5" t="n"/>
       <c r="T470" s="5" t="n"/>
@@ -14598,8 +14776,8 @@
       <c r="M471" s="5" t="n"/>
       <c r="N471" s="5" t="n"/>
       <c r="O471" s="5" t="n"/>
-      <c r="P471" s="11" t="n"/>
-      <c r="Q471" s="5" t="n"/>
+      <c r="P471" s="5" t="n"/>
+      <c r="Q471" s="11" t="n"/>
       <c r="R471" s="5" t="n"/>
       <c r="S471" s="5" t="n"/>
       <c r="T471" s="5" t="n"/>
@@ -14625,8 +14803,8 @@
       <c r="M472" s="5" t="n"/>
       <c r="N472" s="5" t="n"/>
       <c r="O472" s="5" t="n"/>
-      <c r="P472" s="11" t="n"/>
-      <c r="Q472" s="5" t="n"/>
+      <c r="P472" s="5" t="n"/>
+      <c r="Q472" s="11" t="n"/>
       <c r="R472" s="5" t="n"/>
       <c r="S472" s="5" t="n"/>
       <c r="T472" s="5" t="n"/>
@@ -14652,8 +14830,8 @@
       <c r="M473" s="5" t="n"/>
       <c r="N473" s="5" t="n"/>
       <c r="O473" s="5" t="n"/>
-      <c r="P473" s="11" t="n"/>
-      <c r="Q473" s="5" t="n"/>
+      <c r="P473" s="5" t="n"/>
+      <c r="Q473" s="11" t="n"/>
       <c r="R473" s="5" t="n"/>
       <c r="S473" s="5" t="n"/>
       <c r="T473" s="5" t="n"/>
@@ -14679,8 +14857,8 @@
       <c r="M474" s="5" t="n"/>
       <c r="N474" s="5" t="n"/>
       <c r="O474" s="5" t="n"/>
-      <c r="P474" s="11" t="n"/>
-      <c r="Q474" s="5" t="n"/>
+      <c r="P474" s="5" t="n"/>
+      <c r="Q474" s="11" t="n"/>
       <c r="R474" s="5" t="n"/>
       <c r="S474" s="5" t="n"/>
       <c r="T474" s="5" t="n"/>
@@ -14706,8 +14884,8 @@
       <c r="M475" s="5" t="n"/>
       <c r="N475" s="5" t="n"/>
       <c r="O475" s="5" t="n"/>
-      <c r="P475" s="11" t="n"/>
-      <c r="Q475" s="5" t="n"/>
+      <c r="P475" s="5" t="n"/>
+      <c r="Q475" s="11" t="n"/>
       <c r="R475" s="5" t="n"/>
       <c r="S475" s="5" t="n"/>
       <c r="T475" s="5" t="n"/>
@@ -14733,8 +14911,8 @@
       <c r="M476" s="5" t="n"/>
       <c r="N476" s="5" t="n"/>
       <c r="O476" s="5" t="n"/>
-      <c r="P476" s="11" t="n"/>
-      <c r="Q476" s="5" t="n"/>
+      <c r="P476" s="5" t="n"/>
+      <c r="Q476" s="11" t="n"/>
       <c r="R476" s="5" t="n"/>
       <c r="S476" s="5" t="n"/>
       <c r="T476" s="5" t="n"/>
@@ -14760,8 +14938,8 @@
       <c r="M477" s="5" t="n"/>
       <c r="N477" s="5" t="n"/>
       <c r="O477" s="5" t="n"/>
-      <c r="P477" s="11" t="n"/>
-      <c r="Q477" s="5" t="n"/>
+      <c r="P477" s="5" t="n"/>
+      <c r="Q477" s="11" t="n"/>
       <c r="R477" s="5" t="n"/>
       <c r="S477" s="5" t="n"/>
       <c r="T477" s="5" t="n"/>
@@ -14787,8 +14965,8 @@
       <c r="M478" s="5" t="n"/>
       <c r="N478" s="5" t="n"/>
       <c r="O478" s="5" t="n"/>
-      <c r="P478" s="11" t="n"/>
-      <c r="Q478" s="5" t="n"/>
+      <c r="P478" s="5" t="n"/>
+      <c r="Q478" s="11" t="n"/>
       <c r="R478" s="5" t="n"/>
       <c r="S478" s="5" t="n"/>
       <c r="T478" s="5" t="n"/>
@@ -14814,8 +14992,8 @@
       <c r="M479" s="5" t="n"/>
       <c r="N479" s="5" t="n"/>
       <c r="O479" s="5" t="n"/>
-      <c r="P479" s="11" t="n"/>
-      <c r="Q479" s="5" t="n"/>
+      <c r="P479" s="5" t="n"/>
+      <c r="Q479" s="11" t="n"/>
       <c r="R479" s="5" t="n"/>
       <c r="S479" s="5" t="n"/>
       <c r="T479" s="5" t="n"/>
@@ -14841,8 +15019,8 @@
       <c r="M480" s="5" t="n"/>
       <c r="N480" s="5" t="n"/>
       <c r="O480" s="5" t="n"/>
-      <c r="P480" s="11" t="n"/>
-      <c r="Q480" s="5" t="n"/>
+      <c r="P480" s="5" t="n"/>
+      <c r="Q480" s="11" t="n"/>
       <c r="R480" s="5" t="n"/>
       <c r="S480" s="5" t="n"/>
       <c r="T480" s="5" t="n"/>
@@ -14868,8 +15046,8 @@
       <c r="M481" s="5" t="n"/>
       <c r="N481" s="5" t="n"/>
       <c r="O481" s="5" t="n"/>
-      <c r="P481" s="11" t="n"/>
-      <c r="Q481" s="5" t="n"/>
+      <c r="P481" s="5" t="n"/>
+      <c r="Q481" s="11" t="n"/>
       <c r="R481" s="5" t="n"/>
       <c r="S481" s="5" t="n"/>
       <c r="T481" s="5" t="n"/>
@@ -14895,8 +15073,8 @@
       <c r="M482" s="5" t="n"/>
       <c r="N482" s="5" t="n"/>
       <c r="O482" s="5" t="n"/>
-      <c r="P482" s="11" t="n"/>
-      <c r="Q482" s="5" t="n"/>
+      <c r="P482" s="5" t="n"/>
+      <c r="Q482" s="11" t="n"/>
       <c r="R482" s="5" t="n"/>
       <c r="S482" s="5" t="n"/>
       <c r="T482" s="5" t="n"/>
@@ -14922,8 +15100,8 @@
       <c r="M483" s="5" t="n"/>
       <c r="N483" s="5" t="n"/>
       <c r="O483" s="5" t="n"/>
-      <c r="P483" s="11" t="n"/>
-      <c r="Q483" s="5" t="n"/>
+      <c r="P483" s="5" t="n"/>
+      <c r="Q483" s="11" t="n"/>
       <c r="R483" s="5" t="n"/>
       <c r="S483" s="5" t="n"/>
       <c r="T483" s="5" t="n"/>
@@ -14949,8 +15127,8 @@
       <c r="M484" s="5" t="n"/>
       <c r="N484" s="5" t="n"/>
       <c r="O484" s="5" t="n"/>
-      <c r="P484" s="11" t="n"/>
-      <c r="Q484" s="5" t="n"/>
+      <c r="P484" s="5" t="n"/>
+      <c r="Q484" s="11" t="n"/>
       <c r="R484" s="5" t="n"/>
       <c r="S484" s="5" t="n"/>
       <c r="T484" s="5" t="n"/>
@@ -14976,8 +15154,8 @@
       <c r="M485" s="5" t="n"/>
       <c r="N485" s="5" t="n"/>
       <c r="O485" s="5" t="n"/>
-      <c r="P485" s="11" t="n"/>
-      <c r="Q485" s="5" t="n"/>
+      <c r="P485" s="5" t="n"/>
+      <c r="Q485" s="11" t="n"/>
       <c r="R485" s="5" t="n"/>
       <c r="S485" s="5" t="n"/>
       <c r="T485" s="5" t="n"/>
@@ -15003,8 +15181,8 @@
       <c r="M486" s="5" t="n"/>
       <c r="N486" s="5" t="n"/>
       <c r="O486" s="5" t="n"/>
-      <c r="P486" s="11" t="n"/>
-      <c r="Q486" s="5" t="n"/>
+      <c r="P486" s="5" t="n"/>
+      <c r="Q486" s="11" t="n"/>
       <c r="R486" s="5" t="n"/>
       <c r="S486" s="5" t="n"/>
       <c r="T486" s="5" t="n"/>
@@ -15030,8 +15208,8 @@
       <c r="M487" s="5" t="n"/>
       <c r="N487" s="5" t="n"/>
       <c r="O487" s="5" t="n"/>
-      <c r="P487" s="11" t="n"/>
-      <c r="Q487" s="5" t="n"/>
+      <c r="P487" s="5" t="n"/>
+      <c r="Q487" s="11" t="n"/>
       <c r="R487" s="5" t="n"/>
       <c r="S487" s="5" t="n"/>
       <c r="T487" s="5" t="n"/>
@@ -15057,8 +15235,8 @@
       <c r="M488" s="5" t="n"/>
       <c r="N488" s="5" t="n"/>
       <c r="O488" s="5" t="n"/>
-      <c r="P488" s="11" t="n"/>
-      <c r="Q488" s="5" t="n"/>
+      <c r="P488" s="5" t="n"/>
+      <c r="Q488" s="11" t="n"/>
       <c r="R488" s="5" t="n"/>
       <c r="S488" s="5" t="n"/>
       <c r="T488" s="5" t="n"/>
@@ -15084,8 +15262,8 @@
       <c r="M489" s="5" t="n"/>
       <c r="N489" s="5" t="n"/>
       <c r="O489" s="5" t="n"/>
-      <c r="P489" s="11" t="n"/>
-      <c r="Q489" s="5" t="n"/>
+      <c r="P489" s="5" t="n"/>
+      <c r="Q489" s="11" t="n"/>
       <c r="R489" s="5" t="n"/>
       <c r="S489" s="5" t="n"/>
       <c r="T489" s="5" t="n"/>
@@ -15111,8 +15289,8 @@
       <c r="M490" s="5" t="n"/>
       <c r="N490" s="5" t="n"/>
       <c r="O490" s="5" t="n"/>
-      <c r="P490" s="11" t="n"/>
-      <c r="Q490" s="5" t="n"/>
+      <c r="P490" s="5" t="n"/>
+      <c r="Q490" s="11" t="n"/>
       <c r="R490" s="5" t="n"/>
       <c r="S490" s="5" t="n"/>
       <c r="T490" s="5" t="n"/>
@@ -15138,8 +15316,8 @@
       <c r="M491" s="5" t="n"/>
       <c r="N491" s="5" t="n"/>
       <c r="O491" s="5" t="n"/>
-      <c r="P491" s="11" t="n"/>
-      <c r="Q491" s="5" t="n"/>
+      <c r="P491" s="5" t="n"/>
+      <c r="Q491" s="11" t="n"/>
       <c r="R491" s="5" t="n"/>
       <c r="S491" s="5" t="n"/>
       <c r="T491" s="5" t="n"/>
@@ -15165,8 +15343,8 @@
       <c r="M492" s="5" t="n"/>
       <c r="N492" s="5" t="n"/>
       <c r="O492" s="5" t="n"/>
-      <c r="P492" s="11" t="n"/>
-      <c r="Q492" s="5" t="n"/>
+      <c r="P492" s="5" t="n"/>
+      <c r="Q492" s="11" t="n"/>
       <c r="R492" s="5" t="n"/>
       <c r="S492" s="5" t="n"/>
       <c r="T492" s="5" t="n"/>
@@ -15192,8 +15370,8 @@
       <c r="M493" s="5" t="n"/>
       <c r="N493" s="5" t="n"/>
       <c r="O493" s="5" t="n"/>
-      <c r="P493" s="11" t="n"/>
-      <c r="Q493" s="5" t="n"/>
+      <c r="P493" s="5" t="n"/>
+      <c r="Q493" s="11" t="n"/>
       <c r="R493" s="5" t="n"/>
       <c r="S493" s="5" t="n"/>
       <c r="T493" s="5" t="n"/>
@@ -15219,8 +15397,8 @@
       <c r="M494" s="5" t="n"/>
       <c r="N494" s="5" t="n"/>
       <c r="O494" s="5" t="n"/>
-      <c r="P494" s="11" t="n"/>
-      <c r="Q494" s="5" t="n"/>
+      <c r="P494" s="5" t="n"/>
+      <c r="Q494" s="11" t="n"/>
       <c r="R494" s="5" t="n"/>
       <c r="S494" s="5" t="n"/>
       <c r="T494" s="5" t="n"/>
@@ -15246,8 +15424,8 @@
       <c r="M495" s="5" t="n"/>
       <c r="N495" s="5" t="n"/>
       <c r="O495" s="5" t="n"/>
-      <c r="P495" s="11" t="n"/>
-      <c r="Q495" s="5" t="n"/>
+      <c r="P495" s="5" t="n"/>
+      <c r="Q495" s="11" t="n"/>
       <c r="R495" s="5" t="n"/>
       <c r="S495" s="5" t="n"/>
       <c r="T495" s="5" t="n"/>
@@ -15273,8 +15451,8 @@
       <c r="M496" s="5" t="n"/>
       <c r="N496" s="5" t="n"/>
       <c r="O496" s="5" t="n"/>
-      <c r="P496" s="11" t="n"/>
-      <c r="Q496" s="5" t="n"/>
+      <c r="P496" s="5" t="n"/>
+      <c r="Q496" s="11" t="n"/>
       <c r="R496" s="5" t="n"/>
       <c r="S496" s="5" t="n"/>
       <c r="T496" s="5" t="n"/>
@@ -15300,8 +15478,8 @@
       <c r="M497" s="5" t="n"/>
       <c r="N497" s="5" t="n"/>
       <c r="O497" s="5" t="n"/>
-      <c r="P497" s="11" t="n"/>
-      <c r="Q497" s="5" t="n"/>
+      <c r="P497" s="5" t="n"/>
+      <c r="Q497" s="11" t="n"/>
       <c r="R497" s="5" t="n"/>
       <c r="S497" s="5" t="n"/>
       <c r="T497" s="5" t="n"/>
@@ -15327,8 +15505,8 @@
       <c r="M498" s="5" t="n"/>
       <c r="N498" s="5" t="n"/>
       <c r="O498" s="5" t="n"/>
-      <c r="P498" s="11" t="n"/>
-      <c r="Q498" s="5" t="n"/>
+      <c r="P498" s="5" t="n"/>
+      <c r="Q498" s="11" t="n"/>
       <c r="R498" s="5" t="n"/>
       <c r="S498" s="5" t="n"/>
       <c r="T498" s="5" t="n"/>
@@ -15354,8 +15532,8 @@
       <c r="M499" s="5" t="n"/>
       <c r="N499" s="5" t="n"/>
       <c r="O499" s="5" t="n"/>
-      <c r="P499" s="11" t="n"/>
-      <c r="Q499" s="5" t="n"/>
+      <c r="P499" s="5" t="n"/>
+      <c r="Q499" s="11" t="n"/>
       <c r="R499" s="5" t="n"/>
       <c r="S499" s="5" t="n"/>
       <c r="T499" s="5" t="n"/>
@@ -15381,8 +15559,8 @@
       <c r="M500" s="5" t="n"/>
       <c r="N500" s="5" t="n"/>
       <c r="O500" s="5" t="n"/>
-      <c r="P500" s="11" t="n"/>
-      <c r="Q500" s="5" t="n"/>
+      <c r="P500" s="5" t="n"/>
+      <c r="Q500" s="11" t="n"/>
       <c r="R500" s="5" t="n"/>
       <c r="S500" s="5" t="n"/>
       <c r="T500" s="5" t="n"/>
@@ -15399,7 +15577,7 @@
       <formula>$Y2="SIM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="7">
+  <dataValidations count="6">
     <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor não permitido" error="Escolha SIM ou NÃO." type="list">
       <formula1>"SIM,NÃO"</formula1>
     </dataValidation>
@@ -15411,9 +15589,6 @@
     </dataValidation>
     <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor não permitido" error="Escolha uma região da lista." type="list">
       <formula1>=Listas!$C$2:$C$45</formula1>
-    </dataValidation>
-    <dataValidation sqref="V2:V500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor não permitido" error="Escolha SIM ou NÃO." type="list">
-      <formula1>"SIM,NÃO"</formula1>
     </dataValidation>
     <dataValidation sqref="X2:X500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor não permitido" error="Escolha SIM ou NÃO." type="list">
       <formula1>"SIM,NÃO"</formula1>
@@ -17797,11 +17972,321 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>publicar</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>uf</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>selo</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>legenda</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>imagem</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>id_local</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Festa</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Festa Neon</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sexta · 23h · Pinheiros</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>assets/destaques/exemplo/2.svg</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>gds-sp-002</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Casa Exemplo Veludo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sexta e sábado · Moema</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>assets/destaques/exemplo/1.svg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>gds-sp-001</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Evento</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Noite dos Casais</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quinta · 22h · Moema</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>assets/destaques/exemplo/3.svg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>gds-sp-001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Casa Exemplo Mirante</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sábado · Santo André</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>assets/destaques/exemplo/4.svg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>gds-sp-006</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Evento</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Domingo na piscina</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Domingo · 16h · Santo André</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>assets/destaques/exemplo/1.svg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>gds-sp-006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Balada</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Balada Exemplo Aurora</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sexta e sábado · Santo Amaro</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>assets/destaques/exemplo/3.svg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>gds-sp-007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H7"/>
+  <dataValidations count="4">
+    <dataValidation sqref="A2:A100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor não permitido" error="Escolha SIM ou NÃO." type="list">
+      <formula1>"SIM,NÃO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor não permitido" error="Use a sigla do estado (ex.: SP)." type="list">
+      <formula1>=Listas!$B$2:$B$28</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Selo" error="Você pode usar outro texto se quiser." type="list" errorStyle="information">
+      <formula1>=Listas!$F$2:$F$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor não permitido" error="Escolha um id que exista na aba Locais." type="list">
+      <formula1>=Locais!$B$2:$B$500</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00AAAAAA"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -17809,6 +18294,7 @@
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17837,6 +18323,11 @@
           <t>tipo_horario</t>
         </is>
       </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>selos</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17864,6 +18355,11 @@
           <t>funcionamento</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Balada</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17891,6 +18387,11 @@
           <t>festa</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Festa</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17913,6 +18414,11 @@
           <t>atendimento</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Evento</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17930,6 +18436,11 @@
           <t>Zona Oeste</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17947,6 +18458,11 @@
           <t>Centro</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Clube</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17962,6 +18478,11 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>ABC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Destaque</t>
         </is>
       </c>
     </row>

--- a/dados/guia-de-swing.xlsx
+++ b/dados/guia-de-swing.xlsx
@@ -412,7 +412,7 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Imagem horizontal ~800 x 500 px, sem pessoas. Ex.: assets/destaques/festa.jpg</t>
+        <t>Imagem horizontal 800 x 400 px, sem pessoas. Ex.: assets/destaques/festa.jpg</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
@@ -961,7 +961,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Imagem horizontal (~800 x 500 px, até 300 KB), sem pessoas. Ex.: assets/destaques/festa-neon.jpg. Sem imagem, usa a 1ª foto da casa ou um fundo padrão.</t>
+          <t>Imagem horizontal (800 x 400 px, até 300 KB), sem pessoas. Ex.: assets/destaques/festa-neon.jpg. Sem imagem, usa a 1ª foto da casa ou um fundo padrão.</t>
         </is>
       </c>
     </row>

--- a/dados/guia-de-swing.xlsx
+++ b/dados/guia-de-swing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b51a6397e977f0d1/Documentos/Guia/site/v3/atualizacao/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D386E5050D2850F2F96D822C04E41022CE695483" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8E8AABC-2CAD-45DB-88CC-5A81E5606486}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_D386E5050D2850F2F96D822C04E41022CE695483" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5708DD6-AD11-4830-9B34-CD667BFA3DDB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -582,7 +582,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="316">
   <si>
     <t>Guia de Swing — planilha de cadastro</t>
   </si>
@@ -1155,27 +1155,12 @@
     <t>festa</t>
   </si>
   <si>
-    <t>qui</t>
-  </si>
-  <si>
-    <t>22:00-03:00</t>
-  </si>
-  <si>
     <t>Noite dos Casais</t>
   </si>
   <si>
     <t>atendimento</t>
   </si>
   <si>
-    <t>seg-sex</t>
-  </si>
-  <si>
-    <t>14:00-20:00</t>
-  </si>
-  <si>
-    <t>Reservas pelo WhatsApp</t>
-  </si>
-  <si>
     <t>qui-sab</t>
   </si>
   <si>
@@ -1507,9 +1492,6 @@
   </si>
   <si>
     <t>Rua Henri Dunant, 862 - Sto Amaro - São Paulo</t>
-  </si>
-  <si>
-    <t>assets/logos/perfil-transparente.png</t>
   </si>
   <si>
     <t>Ala Social; Mezanino; Ala Privativa; Onibus do prazer; Glory Hole; Octógono; Sala dos véus; Banheiro; Estacionamento; Fumódromo; Bar; Pista; Chapelaria;</t>
@@ -1568,14 +1550,23 @@
     <t>assets/fotos/entrada.jpg; assets/fotos/Bar.jpg; assets/fotos/Pista.jpg; assets/fotos/Banheiro.jpg; assets/fotos/Mezanino.jpg; assets/fotos/Cabines.jpg; assets/fotos/Octogono.jpg; assets/fotos/Onibus.jpg; assets/fotos/cinema.jpg</t>
   </si>
   <si>
-    <t>00/10/2026</t>
+    <t>Inner Club</t>
+  </si>
+  <si>
+    <t>ter-qui</t>
+  </si>
+  <si>
+    <t>21:00-06:00</t>
+  </si>
+  <si>
+    <t>assets/logos/exemplo/Perfil.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1631,6 +1622,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1663,7 +1662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1697,6 +1696,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2583,7 +2585,7 @@
         <v>107</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>108</v>
+        <v>312</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>109</v>
@@ -2595,53 +2597,53 @@
         <v>111</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>112</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="Q2" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>308</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>314</v>
       </c>
       <c r="S2" s="5"/>
       <c r="T2" s="16" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="U2" s="16" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>318</v>
+        <v>311</v>
+      </c>
+      <c r="W2" s="12">
+        <v>46325</v>
       </c>
       <c r="X2" s="5" t="s">
         <v>106</v>
@@ -16345,7 +16347,8 @@
     <hyperlink ref="U2" r:id="rId2" xr:uid="{1F612D4B-E675-4121-9D87-41A54627FD71}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -16410,10 +16413,10 @@
         <v>184</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>185</v>
+        <v>313</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -16421,16 +16424,13 @@
         <v>107</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E3" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -16438,16 +16438,13 @@
         <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>192</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -16458,10 +16455,10 @@
         <v>184</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -16472,13 +16469,13 @@
         <v>184</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -16489,13 +16486,13 @@
         <v>187</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E7" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -16509,7 +16506,7 @@
         <v>185</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -16520,10 +16517,10 @@
         <v>184</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -16534,13 +16531,13 @@
         <v>187</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E10" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -16551,10 +16548,10 @@
         <v>184</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -16565,7 +16562,7 @@
         <v>184</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>186</v>
@@ -16579,10 +16576,10 @@
         <v>184</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -16593,13 +16590,13 @@
         <v>187</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E14" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -16613,7 +16610,7 @@
         <v>185</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -16624,13 +16621,13 @@
         <v>184</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E16" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.25">
@@ -18643,16 +18640,16 @@
         <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G2" t="s">
         <v>114</v>
@@ -18666,16 +18663,16 @@
         <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D3" t="s">
         <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G3" t="s">
         <v>107</v>
@@ -18689,16 +18686,16 @@
         <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G4" t="s">
         <v>107</v>
@@ -18712,16 +18709,16 @@
         <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D5" t="s">
         <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G5" t="s">
         <v>156</v>
@@ -18735,16 +18732,16 @@
         <v>110</v>
       </c>
       <c r="C6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E6" t="s">
         <v>223</v>
       </c>
-      <c r="D6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E6" t="s">
-        <v>228</v>
-      </c>
       <c r="F6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G6" t="s">
         <v>156</v>
@@ -18758,16 +18755,16 @@
         <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D7" t="s">
         <v>168</v>
       </c>
       <c r="E7" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G7" t="s">
         <v>167</v>
@@ -18822,22 +18819,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -18857,7 +18854,7 @@
         <v>184</v>
       </c>
       <c r="F2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -18865,19 +18862,19 @@
         <v>116</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
         <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E3" t="s">
         <v>187</v>
       </c>
       <c r="F3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -18885,16 +18882,16 @@
         <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
         <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -18902,13 +18899,13 @@
         <v>138</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C5" t="s">
         <v>118</v>
       </c>
       <c r="F5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -18916,13 +18913,13 @@
         <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C6" t="s">
         <v>150</v>
       </c>
       <c r="F6" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -18930,21 +18927,21 @@
         <v>177</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C7" t="s">
         <v>160</v>
       </c>
       <c r="F7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C8" t="s">
         <v>178</v>
@@ -18952,247 +18949,247 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C9" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C10" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C13" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C14" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C15" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C16" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C17" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C18" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C20" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C21" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C22" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C23" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C24" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C25" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C26" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C27" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C28" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="41" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="44" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="45" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/dados/guia-de-swing.xlsx
+++ b/dados/guia-de-swing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b51a6397e977f0d1/Documentos/Guia/site/v3/atualizacao/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_D386E5050D2850F2F96D822C04E41022CE695483" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5708DD6-AD11-4830-9B34-CD667BFA3DDB}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_D386E5050D2850F2F96D822C04E41022CE695483" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{192DD9C2-0CFD-4D0E-9005-56D44188161A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1520,15 +1520,6 @@
 CASAIS – Para acessar as áreas privativas o casal (H+M) deve estar sempre acompanhado do parceiro(a).</t>
   </si>
   <si>
-    <t>INNER CLUB – Casa de Swing Tradicional em São Paulo
-Mais de 25 anos de tradição no universo liberal e swinger.
-O Inner Club é uma tradicional casa de swing em São Paulo, com mais de 25 anos de história e reconhecimento entre os casais liberais. Sua estrutura diferenciada, atendimento e credibilidade fazem do clube uma referência para quem busca viver o estilo de vida swinger com conforto, segurança e discrição.
-Pioneiro na criação de ambientes temáticos e espaços privativos, o Inner Club mantém sua essência de verdadeiro clube de swing, preservando a proposta tradicional de troca de casais, sem perder a capacidade de inovar. A casa recebe desde iniciantes e curiosos até casais experientes no universo liberal, além de homens e mulheres desacompanhados.
-Aberto de terça a domingo, inclusive feriados, o Inner oferece música de diferentes estilos, drinks especiais e diversos ambientes aconchegantes para socializar, conhecer pessoas e explorar novas experiências. Entre as fantasias que fazem parte do universo da casa estão swing (troca de casais), menage a trois, exibicionismo, voyeurismo, cuckold e gang bang.
-No Inner Club, cada pessoa decide até onde deseja ir. Nada é obrigatório e o não é não. O respeito aos limites individuais, o bem-estar e a privacidade dos frequentadores são prioridades. Para preservar a identidade de todos, não são permitidos registros de fotos ou vídeos no interior da casa.
-Se você procura uma casa de swing em São Paulo que valoriza a tradição swinger, a liberdade de escolha e o respeito entre seus frequentadores, conheça o Inner Club e descubra uma experiência completa no universo liberal.</t>
-  </si>
-  <si>
     <t>Inner Club: casa de swing em São Paulo com mais de 25 anos de tradição, ambientes privativos, música, drinks e experiências liberais com respeito e discrição.</t>
   </si>
   <si>
@@ -1560,6 +1551,35 @@
   </si>
   <si>
     <t>assets/logos/exemplo/Perfil.png</t>
+  </si>
+  <si>
+    <t>&lt;div style="text-align: center; font-family: 'Trebuchet MS', sans-serif; color: #333333; line-height: 26px;"&gt;
+  &lt;h1 style="font-size: 26px; font-weight: 700; margin: 10px 0; color: #a00;"&gt;
+    INNER CLUB – Casa de Swing Tradicional em São Paulo
+  &lt;/h1&gt;
+  &lt;p style="font-size: 22px; font-weight: 500; margin: 5px 0; color: #666;"&gt;
+    Mais de 25 anos de tradição no universo liberal e swinger.
+  &lt;/p&gt;
+  &lt;p style="font-size: 20px; font-weight: 400; margin: 15px 0;"&gt;
+    O &lt;strong&gt;Inner Club&lt;/strong&gt; é uma tradicional &lt;strong&gt;casa de swing em São Paulo&lt;/strong&gt;, com mais de 25 anos de história e reconhecimento entre os casais liberais. Sua estrutura diferenciada, atendimento e credibilidade fazem do clube uma referência para quem busca viver o estilo de vida swinger com conforto, segurança e discrição.
+  &lt;/p&gt;
+  &lt;p style="font-size: 20px; font-weight: 400; margin: 20px 0;"&gt;
+    Pioneiro na criação de &lt;strong&gt;ambientes temáticos e espaços privativos&lt;/strong&gt;, o Inner Club mantém sua essência de verdadeiro clube de swing, preservando a proposta tradicional de troca de casais, sem perder a capacidade de inovar. A casa recebe desde iniciantes e curiosos até casais experientes no universo liberal, além de homens e mulheres desacompanhados.
+  &lt;/p&gt;
+  &lt;p style="font-size: 20px; font-weight: 400; margin: 20px 0;"&gt;
+    Aberto de &lt;strong&gt;terça a domingo, inclusive feriados&lt;/strong&gt;, o Inner oferece música de diferentes estilos, drinks especiais e diversos ambientes aconchegantes para socializar, conhecer pessoas e explorar novas experiências. Entre as fantasias que fazem parte do universo da casa estão &lt;strong&gt;swing (troca de casais), menage a trois, exibicionismo, voyeurismo, cuckold e gang bang&lt;/strong&gt;.
+  &lt;/p&gt;
+  &lt;p style="font-size: 20px; font-weight: 400; margin: 20px 0;"&gt;
+    No Inner Club, cada pessoa decide até onde deseja ir. &lt;strong&gt;Nada é obrigatório e o não é não.&lt;/strong&gt; O respeito aos limites individuais, o bem-estar e a privacidade dos frequentadores são prioridades. Para preservar a identidade de todos, não são permitidos registros de fotos ou vídeos no interior da casa.
+  &lt;/p&gt;
+  &lt;p style="font-size: 20px; font-weight: 400; margin: 20px 0;"&gt;
+    Se você procura uma &lt;strong&gt;casa de swing em São Paulo&lt;/strong&gt; que valoriza a tradição swinger, a liberdade de escolha e o respeito entre seus frequentadores, conheça o &lt;strong&gt;Inner Club&lt;/strong&gt; e descubra uma experiência completa no universo liberal.
+  &lt;/p&gt;
+  &lt;hr style="border: none; border-top: 1px solid #ccc; width: 60%; margin: 25px auto;" /&gt;
+  &lt;p style="font-size: 22px; font-weight: 600; margin: 10px 0;"&gt;
+    TRADIÇÃO • RESPEITO • DISCRIÇÃO
+  &lt;/p&gt;
+&lt;/div&gt;</t>
   </si>
 </sst>
 </file>
@@ -2585,7 +2605,7 @@
         <v>107</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>109</v>
@@ -2606,7 +2626,7 @@
         <v>300</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>301</v>
@@ -2618,29 +2638,29 @@
         <v>303</v>
       </c>
       <c r="N2" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="R2" s="5" t="s">
         <v>307</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>308</v>
       </c>
       <c r="S2" s="5"/>
       <c r="T2" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="U2" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="U2" s="16" t="s">
+      <c r="V2" s="5" t="s">
         <v>310</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>311</v>
       </c>
       <c r="W2" s="12">
         <v>46325</v>
@@ -16413,7 +16433,7 @@
         <v>184</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>198</v>
@@ -16430,7 +16450,7 @@
         <v>185</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
